--- a/results/job_matches_2026-04-23.xlsx
+++ b/results/job_matches_2026-04-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G132"/>
+  <dimension ref="A1:G185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AWS DevOps Engineer</t>
+          <t>Senior Software Engineer (Cloud &amp; Data Platforms)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Glacier Analytics LLC</t>
+          <t>Customized Energy Solutions</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,34 +521,34 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Unity Catalog, Spark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f2c6e67bc23530</t>
+          <t>https://www.indeed.com/viewjob?jk=14e471621c544ca6</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DOW</t>
+          <t>Glacier Analytics LLC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e6f52d2577111f6</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f2c6e67bc23530</t>
         </is>
       </c>
     </row>
@@ -578,47 +578,47 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FocusKPI Inc.</t>
+          <t>DOW</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, SQS, SNS, RDS, Hive, Spark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad314dbf5fcf61a2</t>
+          <t>https://www.indeed.com/viewjob?jk=0e6f52d2577111f6</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer/ Architecture (ADF &amp; Databricks)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>United Vein &amp; Vascular Centers</t>
+          <t>FocusKPI Inc.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, SQS, SNS, RDS, Hive, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=443e4c4dac7242b8</t>
+          <t>https://www.indeed.com/viewjob?jk=ad314dbf5fcf61a2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AWS Architect with AI + Automation</t>
+          <t>Senior Data Engineer/ Architecture (ADF &amp; Databricks)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ERP Initiatives Group Inc.</t>
+          <t>United Vein &amp; Vascular Centers</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Clarksburg, MD, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46058fb33ffd00c5</t>
+          <t>https://www.indeed.com/viewjob?jk=443e4c4dac7242b8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Applications Developer</t>
+          <t>AWS Architect with AI + Automation</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Texas Regional Physicians</t>
+          <t>ERP Initiatives Group Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Clarksburg, MD, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MongoDB, ETL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=507d9cc374179ef8</t>
+          <t>https://www.indeed.com/viewjob?jk=46058fb33ffd00c5</t>
         </is>
       </c>
     </row>
@@ -993,17 +993,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Java CI/CD Automation Engineer</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83b240190f37e48e</t>
+          <t>https://www.indeed.com/viewjob?jk=0672f1d449c9d9e2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Java CI/CD Automation Engineer</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a0ee2ebd6b94c60</t>
+          <t>https://www.indeed.com/viewjob?jk=96a88c14093ccdaf</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Capp</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Databricks, Kafka, Splunk, MLflow</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5005229862766ee1</t>
+          <t>https://www.indeed.com/viewjob?jk=14f80cb5b125e7cc</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Azure, Databricks, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,207 +1126,207 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ede735cbdf2b63e0</t>
+          <t>https://www.indeed.com/viewjob?jk=ca6623928abe2730</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Axle</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Frederick, MD, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=353f08220bc3960e</t>
+          <t>https://www.indeed.com/viewjob?jk=46e364170a7ee29f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer | The Points Guy</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Red Ventures</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec2d5686f500c7c1</t>
+          <t>https://www.indeed.com/viewjob?jk=0e67913bb063b4e1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer | The Points Guy</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Red Ventures</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac5793781d1c8a3c</t>
+          <t>https://www.indeed.com/viewjob?jk=03e6278fa86f66b6</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Data Modeling, ETL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3a17b22e5142267</t>
+          <t>https://www.indeed.com/viewjob?jk=a417258c27e6884b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (Data Modeling &amp; BI)</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Keeper Security</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b319560288703a69</t>
+          <t>https://www.indeed.com/viewjob?jk=68ff6a6e54c5bb38</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, clustering keys, PostgreSQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,67 +1336,67 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53f7dd47c3f8803c</t>
+          <t>https://www.indeed.com/viewjob?jk=b864420111578783</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior PS Sales Solutions Architect</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfc1ac7dc950d681</t>
+          <t>https://www.indeed.com/viewjob?jk=90020927d62d9e32</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CA IAM Engineer</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Redshift, IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Snowflake, Tableau, Tableau Server</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a8d75516142a508</t>
+          <t>https://www.indeed.com/viewjob?jk=e6445ef98b11402a</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Engineering</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Verse</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, S3, RDS, Databricks, GCP, BigQuery, Hadoop, Hive, HBase</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,67 +1441,67 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2169de43fedb76d3</t>
+          <t>https://www.indeed.com/viewjob?jk=63c85699934dff6e</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SambaNova Systems</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=564c2131c7a47b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=26b24994302869a9</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr. Platform Engineering</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>archer</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,242 +1511,242 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e910893e7900f872</t>
+          <t>https://www.indeed.com/viewjob?jk=06b0116b71837d13</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Computer Programmer</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Axle</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3f8d985ccebf8fe</t>
+          <t>https://www.indeed.com/viewjob?jk=8120526ad261b6a4</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. Data Platform Engineer</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, Azure, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d863f11ee6e4e4a6</t>
+          <t>https://www.indeed.com/viewjob?jk=71be0c8c221ee567</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3728e8079e1309fa</t>
+          <t>https://www.indeed.com/viewjob?jk=ee059ac44d2277d6</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb9acfcb385fd29f</t>
+          <t>https://www.indeed.com/viewjob?jk=af1a0c944d7d687c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer, Analytics &amp; Machine Learning Enablement</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Keeper Security</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, BigQuery, Scala, Snowflake</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b569d0296983d6a1</t>
+          <t>https://www.indeed.com/viewjob?jk=a757acecac7ae896</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5239f6ce7d60780b</t>
+          <t>https://www.indeed.com/viewjob?jk=46cdcaa9c274907d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SIGNITIVES</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>16</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccbfb275c784c26b</t>
+          <t>https://www.indeed.com/viewjob?jk=0c545200255ccd75</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>16</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,102 +1791,102 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b67c42af6bdf7f4d</t>
+          <t>https://www.indeed.com/viewjob?jk=99c6d56e1e9ecbd9</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>16</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ed12a9528f47173</t>
+          <t>https://www.indeed.com/viewjob?jk=ec2268853b5e3d32</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer | The Points Guy</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Red Ventures</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>16</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa160af377aea6a2</t>
+          <t>https://www.indeed.com/viewjob?jk=cc317ad96269ff6c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Specialist Software Engineering</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>16</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, API Gateway, ECS, Event Hubs, Zookeeper, Kafka, CI/CD, Jenkins</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,137 +1896,137 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f8131b391d620e</t>
+          <t>https://www.indeed.com/viewjob?jk=2c59791ffa8037e0</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Python Engineer</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>N-iX</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>16</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Cloud Storage, Vertex AI, Scala, PostgreSQL, MySQL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=365bb0b9ec3ce321</t>
+          <t>https://www.indeed.com/viewjob?jk=93c00120a22fd95f</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Development Engineer - Credential API</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>16</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4c302fda1f6ae84</t>
+          <t>https://www.indeed.com/viewjob?jk=e5fd76a0505c1f45</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Focus Financial Partners</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>16</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Dask, Snowflake</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc6ec804cfff5642</t>
+          <t>https://www.indeed.com/viewjob?jk=52bda57a7eae91d3</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Gates Foundation</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, ELT</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0e09f867e58f64d</t>
+          <t>https://www.indeed.com/viewjob?jk=8d79924b7c683266</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management-Cloud Engineer-Associate-Dallas</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Scala, NoSQL, CI/CD, Jenkins, AWS CodePipeline, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,242 +2071,242 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd9663ecc56297d4</t>
+          <t>https://www.indeed.com/viewjob?jk=18b51a17582c12e7</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Azure Engineer</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Witherite Law Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d4c16398c048d9f</t>
+          <t>https://www.indeed.com/viewjob?jk=c239cf58c8fa1c71</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Contributory Network</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, ECS, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a1c158c64508404</t>
+          <t>https://www.indeed.com/viewjob?jk=d5a42ec359480e0d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE) - AI Platform &amp; Cloud</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Spark, Kafka, Snowflake, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67434a699408c40f</t>
+          <t>https://www.indeed.com/viewjob?jk=5ed6224d65d164cb</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f4b1c757ee83233</t>
+          <t>https://www.indeed.com/viewjob?jk=ffcd6c03d59f6052</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Health-E Commerce</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b75ba4eaa7e2f72</t>
+          <t>https://www.indeed.com/viewjob?jk=ddc6dd123946c0df</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure, Engineer II</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Trinity Logistics</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Seaford, DE, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e66613c1418d016b</t>
+          <t>https://www.indeed.com/viewjob?jk=2b026195b5394344</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Kitsap Credit Union</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bremerton, WA, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, SonarQube</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,172 +2316,172 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=150b9708ae649096</t>
+          <t>https://www.indeed.com/viewjob?jk=9ffe2cd40b6dd0e7</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back-End (Java &amp; Spring Boot)</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PlanOmatic HQ</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4197b722f1b29f84</t>
+          <t>https://www.indeed.com/viewjob?jk=2581b6e435257226</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AI Engineer - Insurance Domain - HYBRID</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Warren, NJ, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeda85e53ae1234a</t>
+          <t>https://www.indeed.com/viewjob?jk=de24f7419929c1bf</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AI Engineer - Insurance Domain - HYBRID</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Warren, NJ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31b5a55badae894d</t>
+          <t>https://www.indeed.com/viewjob?jk=5380c72e36e9ef3d</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Integration Developer</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>AlayaCare</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d6930b008143758</t>
+          <t>https://www.indeed.com/viewjob?jk=43d4c68e7e9e2fef</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr Systems Engineer</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CEI Services</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Fargo, ND, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>16</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f846bcd41f966d19</t>
+          <t>https://www.indeed.com/viewjob?jk=7a8557481e61c905</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr Systems Engineer</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MasTec Inc</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Fargo, ND, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>16</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba06f08c24782d2d</t>
+          <t>https://www.indeed.com/viewjob?jk=af8a69205565050f</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>DevOps with IoT focus</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Intellimation LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>16</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, IAM, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f64235fd5c4fac6</t>
+          <t>https://www.indeed.com/viewjob?jk=dfedec5986433f19</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>16</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=458f2e64ebd817f0</t>
+          <t>https://www.indeed.com/viewjob?jk=dadc73e392f990d3</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>16</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dc21140836b0e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=df6f8697322180c6</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>16</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=903bc43e147b726e</t>
+          <t>https://www.indeed.com/viewjob?jk=b407a88f3a1f87f8</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>16</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3666758a830bafe1</t>
+          <t>https://www.indeed.com/viewjob?jk=ce6e6d7e4f41a3e8</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>16</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d2dccb9477bbad2</t>
+          <t>https://www.indeed.com/viewjob?jk=1662c7096eaa5c34</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Capp</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>16</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,137 +2771,137 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e3afe7a50298373</t>
+          <t>https://www.indeed.com/viewjob?jk=9b54c062fe208581</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>RapidSOS</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>16</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, IAM, Scala, Kafka, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c059e9218f7e23d</t>
+          <t>https://www.indeed.com/viewjob?jk=3ca77008309e43be</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>RapidSOS</t>
+          <t>Capp</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>16</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, IAM, Scala, Kafka, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Databricks, Kafka, Splunk, MLflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3986c9d7e69f169</t>
+          <t>https://www.indeed.com/viewjob?jk=5005229862766ee1</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Gen AI Platform &amp; Deployment Engineer</t>
+          <t>Java CI/CD Automation Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>16</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ad5e385a9b79a74</t>
+          <t>https://www.indeed.com/viewjob?jk=83b240190f37e48e</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Java CI/CD Automation Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Voya Financial</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Braintree, MA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>16</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, Kafka, Oracle, MySQL, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f0f1071f3e2b14</t>
+          <t>https://www.indeed.com/viewjob?jk=9a0ee2ebd6b94c60</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Trust/Security Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Autodesk</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>15.3</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Redshift, S3, Azure, Databricks, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,159 +2946,159 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4254814d062ad92d</t>
+          <t>https://www.indeed.com/viewjob?jk=ede735cbdf2b63e0</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Axle</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Frederick, MD, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>15.3</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Snowflake, Data Modeling, ETL, ELT, Jenkins, Maven, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=842f8f1cf0d90520</t>
+          <t>https://www.indeed.com/viewjob?jk=353f08220bc3960e</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer | The Points Guy</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Red Ventures</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>15.3</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Azure, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=facf27c6b3631798</t>
+          <t>https://www.indeed.com/viewjob?jk=ec2d5686f500c7c1</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Backend Engineer II</t>
+          <t>Data Engineer | The Points Guy</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>HackerRank Careers</t>
+          <t>Red Ventures</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>15.3</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4979e4cfe40ed8d</t>
+          <t>https://www.indeed.com/viewjob?jk=ac5793781d1c8a3c</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>15.3</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d356cba46c60202</t>
+          <t>https://www.indeed.com/viewjob?jk=e3a17b22e5142267</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer</t>
+          <t>Senior Analytics Engineer (Data Modeling &amp; BI)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Fueled</t>
+          <t>Keeper Security</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3107,46 +3107,46 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>15.3</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9642665184944e11</t>
+          <t>https://www.indeed.com/viewjob?jk=b319560288703a69</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>15.3</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, clustering keys, PostgreSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1de30f12b78fca01</t>
+          <t>https://www.indeed.com/viewjob?jk=53f7dd47c3f8803c</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>CA IAM Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>15.3</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>Redshift, IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Snowflake, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88b23e7d0b05c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=1a8d75516142a508</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>DevOps / Platform Engineer</t>
+          <t>Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Vivacity Tech PBC</t>
+          <t>Verse</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>Kinesis, Redshift, S3, RDS, Databricks, GCP, BigQuery, Hadoop, Hive, HBase</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,67 +3226,67 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed1d3fe1d3532916</t>
+          <t>https://www.indeed.com/viewjob?jk=2169de43fedb76d3</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Illumio</t>
+          <t>SambaNova Systems</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cad79b56c244d0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=564c2131c7a47b4e</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS)</t>
+          <t>Sr. Platform Engineering</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Capnexus</t>
+          <t>archer</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Scala, DynamoDB, Data Modeling</t>
+          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,102 +3296,102 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a7b11ddd229f030</t>
+          <t>https://www.indeed.com/viewjob?jk=e910893e7900f872</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Computer Programmer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>PropertyPilot</t>
+          <t>Axle</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Manasquan, NJ, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dab1f6a4231dbe32</t>
+          <t>https://www.indeed.com/viewjob?jk=b3f8d985ccebf8fe</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>BI Engineer I (Hybrid)</t>
+          <t>Data Engineer (AIA)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>NEUMO</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Fort Wayne, IN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d2a5858f9149296</t>
+          <t>https://www.indeed.com/viewjob?jk=422b5002f3c92e96</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Engineer, Ads Infra - Serving and Foundation</t>
+          <t>Data Engineer (AIA)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hive, Spark, Scala, Kafka, Data Modeling, ETL, Airflow, Git</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e26cb9e516d559dc</t>
+          <t>https://www.indeed.com/viewjob?jk=4ca947b911b13d47</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>AI-ML Engineer 1</t>
+          <t>Data Engineer (AIA)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Universal Avionics Systems Corporation</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Tucson, AZ, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Hadoop, Spark, Scala, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,137 +3436,137 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3e0f3955fde63ec</t>
+          <t>https://www.indeed.com/viewjob?jk=2762492ad7551efe</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Engineer - DevSecOps (Associate, Experienced or Senior)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afe37944ff3c78ea</t>
+          <t>https://www.indeed.com/viewjob?jk=cb9acfcb385fd29f</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Software Intern</t>
+          <t>Data Engineer, Analytics &amp; Machine Learning Enablement</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Keeper Security</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Azure, PostgreSQL, DynamoDB, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afbd60d97bfacc60</t>
+          <t>https://www.indeed.com/viewjob?jk=b569d0296983d6a1</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Gametime United</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24a25e68a1bd6d4f</t>
+          <t>https://www.indeed.com/viewjob?jk=5239f6ce7d60780b</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Warranty Data Analyst / Data Scientist</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>SIGNITIVES</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e9bb1ef1dd7ba48</t>
+          <t>https://www.indeed.com/viewjob?jk=ccbfb275c784c26b</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Warranty Data Analyst / Data Scientist</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ffd491a76c9fa66</t>
+          <t>https://www.indeed.com/viewjob?jk=b67c42af6bdf7f4d</t>
         </is>
       </c>
     </row>
@@ -3623,90 +3623,90 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Headspace</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbb7191dcfe18f53</t>
+          <t>https://www.indeed.com/viewjob?jk=5ed12a9528f47173</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Data Engineer | The Points Guy</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>Red Ventures</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, S3, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=672dba9cce12de5f</t>
+          <t>https://www.indeed.com/viewjob?jk=aa160af377aea6a2</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Specialist Software Engineering</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Trepp</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, Spark, Scala, Data Modeling, CI/CD, Git</t>
+          <t>AWS, Kinesis, S3, API Gateway, ECS, Event Hubs, Zookeeper, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,417 +3716,417 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d561d8c2375dd6b1</t>
+          <t>https://www.indeed.com/viewjob?jk=66f8131b391d620e</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer-Azure Data &amp; Analytics Engineer - State National</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Markel Corporation</t>
+          <t>Focus Financial Partners</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Bedford, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Dask, Snowflake</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94507e2995b9ee29</t>
+          <t>https://www.indeed.com/viewjob?jk=dc6ec804cfff5642</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Engineer II - Information Technology</t>
+          <t>Senior Full-Stack Python Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Board of Governors of the Federal Reserve System</t>
+          <t>N-iX</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, PostgreSQL, NoSQL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Cloud Storage, Vertex AI, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b222160bc0c2b3e3</t>
+          <t>https://www.indeed.com/viewjob?jk=365bb0b9ec3ce321</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Development Engineer - Credential API</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>nSCALE</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Barstow, TX, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc6c300d9777dc4b</t>
+          <t>https://www.indeed.com/viewjob?jk=a4c302fda1f6ae84</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Engineer - Seattle, WA</t>
+          <t>Senior DevOps Engineer II</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>nSCALE</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=894fb5b066595659</t>
+          <t>https://www.indeed.com/viewjob?jk=3af6a74b61fd0779</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Solution Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>SimilarWeb</t>
+          <t>Gates Foundation</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, ELT</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e039b4fcb467133</t>
+          <t>https://www.indeed.com/viewjob?jk=d0e09f867e58f64d</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Engineer, Developer Platform (Cloud Apps)</t>
+          <t>Asset &amp; Wealth Management-Cloud Engineer-Associate-Dallas</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Motional</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, NoSQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Scala, NoSQL, CI/CD, Jenkins, AWS CodePipeline, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a10c8d4659b2bc91</t>
+          <t>https://www.indeed.com/viewjob?jk=fd9663ecc56297d4</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Azure Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Envoy global</t>
+          <t>Witherite Law Group</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, Scala, SQL Server, Splunk, CI/CD, Azure DevOps, Terraform, AKS, Git</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d81e4212199a1a8</t>
+          <t>https://www.indeed.com/viewjob?jk=2d4c16398c048d9f</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Software Engineer - Contributory Network</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Envoy global</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, Scala, SQL Server, Splunk, CI/CD, Azure DevOps, Terraform, AKS, Git</t>
+          <t>AWS, ECS, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d276b3164ac33893</t>
+          <t>https://www.indeed.com/viewjob?jk=9a1c158c64508404</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>SQL Engineer</t>
+          <t>Site Reliability Engineer (SRE) - AI Platform &amp; Cloud</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Mechanical Licensing Collective</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Athena, RDS, Scala, Oracle, PostgreSQL, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, Spark, Kafka, Snowflake, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3db429a534810fa</t>
+          <t>https://www.indeed.com/viewjob?jk=67434a699408c40f</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Alpaca</t>
+          <t>Health-E Commerce</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Spark, Scala, ETL, ELT, dbt, CI/CD, Airflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cf5cd1df0f54fe6</t>
+          <t>https://www.indeed.com/viewjob?jk=2b75ba4eaa7e2f72</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
+          <t>Cloud Infrastructure, Engineer II</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>Trinity Logistics</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seaford, DE, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ae2d7c352959fb2</t>
+          <t>https://www.indeed.com/viewjob?jk=e66613c1418d016b</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>University of Maryland Medical System</t>
+          <t>Kitsap Credit Union</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>North Bethesda, MD, US USA</t>
+          <t>Bremerton, WA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, MapReduce, Spark, Scala, Oracle, PostgreSQL, MongoDB</t>
+          <t>RDS, Azure, Event Hubs, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, SonarQube</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4188adfee24d1373</t>
+          <t>https://www.indeed.com/viewjob?jk=150b9708ae649096</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Technical Operations Engineer</t>
+          <t>AI Engineer - Insurance Domain - HYBRID</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Codoxo</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Warren, NJ, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, NoSQL, ETL, Airflow, Bitbucket, CloudWatch</t>
+          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,102 +4171,102 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e78a417a0f4410ac</t>
+          <t>https://www.indeed.com/viewjob?jk=aeda85e53ae1234a</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Quality Platform Engineer</t>
+          <t>Senior Software Engineer, Back-End (Java &amp; Spring Boot)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Circle.so</t>
+          <t>PlanOmatic HQ</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3752971091aeeac9</t>
+          <t>https://www.indeed.com/viewjob?jk=4197b722f1b29f84</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform &amp; Product</t>
+          <t>Senior Integration Developer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Ware Malcomb</t>
+          <t>AlayaCare</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aed0adf2e92986f6</t>
+          <t>https://www.indeed.com/viewjob?jk=2d6930b008143758</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Sr Systems Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>CEI Services</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Fargo, ND, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab7793f0a792b417</t>
+          <t>https://www.indeed.com/viewjob?jk=f846bcd41f966d19</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Sr Systems Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>MasTec Inc</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Fargo, ND, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=650677ad14cf645f</t>
+          <t>https://www.indeed.com/viewjob?jk=ba06f08c24782d2d</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Platform</t>
+          <t>DevOps with IoT focus</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Ramp</t>
+          <t>Intellimation LLC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Terraform, Airflow</t>
+          <t>AWS, IAM, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,14 +4346,14 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45e12b77b9565199</t>
+          <t>https://www.indeed.com/viewjob?jk=3f64235fd5c4fac6</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4363,15 +4363,15 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Azure, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,14 +4381,14 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff779f0dce63ada3</t>
+          <t>https://www.indeed.com/viewjob?jk=458f2e64ebd817f0</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4398,15 +4398,15 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Azure, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,32 +4416,32 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb55e9f7a6dc231</t>
+          <t>https://www.indeed.com/viewjob?jk=3dc21140836b0e1a</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Empirx Health</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Blob Storage, GCP, Scala, Kafka, CI/CD, Azure DevOps, Git</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,242 +4451,242 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c08697ee3f4bc0ba</t>
+          <t>https://www.indeed.com/viewjob?jk=903bc43e147b726e</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Health-E Commerce</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, Scala, Data Modeling, ETL, Azure DevOps, Python</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56afd442294fd678</t>
+          <t>https://www.indeed.com/viewjob?jk=3666758a830bafe1</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Go Outdoors Payments</t>
+          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Brandt Information Services, Inc.</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f9736f5f852f3d</t>
+          <t>https://www.indeed.com/viewjob?jk=8d2dccb9477bbad2</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Go Outdoors Payments</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Brandt Information Services, Inc.</t>
+          <t>Capp</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e66c9de7a81a7d66</t>
+          <t>https://www.indeed.com/viewjob?jk=4e3afe7a50298373</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Fairlife, LLC</t>
+          <t>RapidSOS</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Star Schema, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, SQS, SNS, ECS, IAM, Scala, Kafka, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f203c334e20f61e9</t>
+          <t>https://www.indeed.com/viewjob?jk=6c059e9218f7e23d</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Enterprise AI Architect</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Capp</t>
+          <t>RapidSOS</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, SQS, SNS, ECS, IAM, Scala, Kafka, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a69902c54cdf2463</t>
+          <t>https://www.indeed.com/viewjob?jk=d3986c9d7e69f169</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Engineer</t>
+          <t>Gen AI Platform &amp; Deployment Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Mission Produce</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Oxnard, CA, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adb3f80bc7a0023f</t>
+          <t>https://www.indeed.com/viewjob?jk=7ad5e385a9b79a74</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Java Compliance &amp; Governance Developer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Voya Financial</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Braintree, MA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
+          <t>Azure, Databricks, Spark, Kafka, Oracle, MySQL, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,32 +4696,32 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=243990c269c56673</t>
+          <t>https://www.indeed.com/viewjob?jk=06f0f1071f3e2b14</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Java Compliance &amp; Governance Developer</t>
+          <t>Senior Trust/Security Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Autodesk</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,32 +4731,32 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9d53f3c6ff20349</t>
+          <t>https://www.indeed.com/viewjob?jk=4254814d062ad92d</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Java Compliance &amp; Governance Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
+          <t>AWS, S3, IAM, Snowflake, Data Modeling, ETL, ELT, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,32 +4766,32 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14d0312c67f01746</t>
+          <t>https://www.indeed.com/viewjob?jk=842f8f1cf0d90520</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+          <t>AWS, S3, ECS, IAM, Azure, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,67 +4801,67 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd98e6c90182dad1</t>
+          <t>https://www.indeed.com/viewjob?jk=facf27c6b3631798</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Backend Engineer II</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>HackerRank Careers</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1188cf2ae8e587af</t>
+          <t>https://www.indeed.com/viewjob?jk=d4979e4cfe40ed8d</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,67 +4871,67 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec0dc8f9f8c8d698</t>
+          <t>https://www.indeed.com/viewjob?jk=3d356cba46c60202</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Solution Engineer - Data Engineering Specialist (FSI)</t>
+          <t>AI Engineer (AIA)</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Hadoop, Hive, Spark, PySpark, Spark Streaming, Kafka, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d35a9b6aca584743</t>
+          <t>https://www.indeed.com/viewjob?jk=620262fd8bc038be</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>AI Engineer (AIA)</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,32 +4941,32 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d2728ef533caf7a</t>
+          <t>https://www.indeed.com/viewjob?jk=4c87da22babbe085</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>AI Engineer (AIA)</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Yarmouth, ME, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,32 +4976,32 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68f623995aa05734</t>
+          <t>https://www.indeed.com/viewjob?jk=537fe809ab41770d</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>AI Engineer (AIA)</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,40 +5011,1895 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ef46c3d4fd66d6a</t>
+          <t>https://www.indeed.com/viewjob?jk=3776f71cd705f403</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
+          <t>AI Engineer (AIA)</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>MO, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57e40902475718d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Senior Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Fueled</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9642665184944e11</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>DriveTime Automotive Group</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1de30f12b78fca01</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>DriveTime Automotive Group</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b88b23e7d0b05c8f</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>DevOps / Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Vivacity Tech PBC</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ed1d3fe1d3532916</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Sr. Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Illumio</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cad79b56c244d0fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer (AWS)</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Capnexus</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Scala, DynamoDB, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a7b11ddd229f030</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>BI Engineer I (Hybrid)</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>NEUMO</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Fort Wayne, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9d2a5858f9149296</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Software Engineer, Ads Infra - Serving and Foundation</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Hive, Spark, Scala, Kafka, Data Modeling, ETL, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e26cb9e516d559dc</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>AI-ML Engineer 1</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Universal Avionics Systems Corporation</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Tucson, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Hadoop, Spark, Scala, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e3e0f3955fde63ec</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Warranty Data Analyst / Data Scientist</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Stellantis</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Auburn Hills, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2e9bb1ef1dd7ba48</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Warranty Data Analyst / Data Scientist</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Stellantis</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Auburn Hills, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2ffd491a76c9fa66</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Headspace</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cbb7191dcfe18f53</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Software Engineer - DevSecOps (Associate, Experienced or Senior)</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Boeing</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=afe37944ff3c78ea</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Software Intern</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Thermo Fisher Scientific</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Pleasanton, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Redshift, S3, RDS, Azure, PostgreSQL, DynamoDB, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=afbd60d97bfacc60</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Gametime United</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=24a25e68a1bd6d4f</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Data Engineer III</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Simplot Company</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Boise, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=672dba9cce12de5f</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Trepp</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>AWS, Glue, EMR, Lambda, S3, Spark, Scala, Data Modeling, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d561d8c2375dd6b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Senior Infrastructure Engineer-Azure Data &amp; Analytics Engineer - State National</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Markel Corporation</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Bedford, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=94507e2995b9ee29</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Data Engineer II - Information Technology</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Board of Governors of the Federal Reserve System</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, PostgreSQL, NoSQL</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b222160bc0c2b3e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>nSCALE</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Barstow, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc6c300d9777dc4b</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Data Engineer - Seattle, WA</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>nSCALE</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=894fb5b066595659</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Data Solution Engineer</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>SimilarWeb</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8e039b4fcb467133</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Engineer, Developer Platform (Cloud Apps)</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Motional</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, NoSQL, CI/CD, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a10c8d4659b2bc91</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Envoy global</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Azure, Blob Storage, Scala, SQL Server, Splunk, CI/CD, Azure DevOps, Terraform, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d81e4212199a1a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Envoy global</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Azure, Blob Storage, Scala, SQL Server, Splunk, CI/CD, Azure DevOps, Terraform, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d276b3164ac33893</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>SQL Engineer</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Mechanical Licensing Collective</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>AWS, Athena, RDS, Scala, Oracle, PostgreSQL, Data Modeling, Star Schema, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e3db429a534810fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Alpaca</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, Spark, Scala, ETL, ELT, dbt, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8cf5cd1df0f54fe6</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>jamf</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2ae2d7c352959fb2</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Sr Data Engineer</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>University of Maryland Medical System</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>North Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, HDFS, Hive, MapReduce, Spark, Scala, Oracle, PostgreSQL, MongoDB</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4188adfee24d1373</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Technical Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Codoxo</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, RDS, Scala, NoSQL, ETL, Airflow, Bitbucket, CloudWatch</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e78a417a0f4410ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Senior Quality Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Circle.so</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3752971091aeeac9</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Platform &amp; Product</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Ware Malcomb</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aed0adf2e92986f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Senior Engineer - .NET</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ab7793f0a792b417</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Senior Engineer - .NET</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=650677ad14cf645f</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Software Engineer, Data Platform</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Terraform, Airflow</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=45e12b77b9565199</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Empirx Health</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Blob Storage, GCP, Scala, Kafka, CI/CD, Azure DevOps, Git</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c08697ee3f4bc0ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Enterprise AI Architect</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Capp</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Willingboro, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a69902c54cdf2463</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>AI Integration Engineer (Java + AI)</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Azure, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ff779f0dce63ada3</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>AI Integration Engineer (Java + AI)</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Azure, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9eb55e9f7a6dc231</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Health-E Commerce</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, Scala, Data Modeling, ETL, Azure DevOps, Python</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=56afd442294fd678</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer Go Outdoors Payments</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Brandt Information Services, Inc.</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f1f9736f5f852f3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer Go Outdoors Payments</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Brandt Information Services, Inc.</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Tallahassee, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e66c9de7a81a7d66</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Sr. Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Fairlife, LLC</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Spark, Scala, Star Schema, ELT, Power BI, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f203c334e20f61e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Metropolis</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cd98e6c90182dad1</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Metropolis</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1188cf2ae8e587af</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Metropolis</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ec0dc8f9f8c8d698</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Java Compliance &amp; Governance Developer</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>NC, US USA</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=243990c269c56673</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Java Compliance &amp; Governance Developer</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>NC, US USA</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e9d53f3c6ff20349</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Java Compliance &amp; Governance Developer</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=14d0312c67f01746</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
           <t>Cloud Engineer</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
+      <c r="B182" t="inlineStr">
         <is>
           <t>Tyler Technologies</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr">
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Herndon, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9d2728ef533caf7a</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Tyler Technologies</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Yarmouth, ME, US USA</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=68f623995aa05734</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Tyler Technologies</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Troy, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ef46c3d4fd66d6a</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Tyler Technologies</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
         <is>
           <t>Overland Park, KS, US USA</t>
         </is>
       </c>
-      <c r="D132" t="n">
+      <c r="D185" t="n">
         <v>10.4</v>
       </c>
-      <c r="E132" t="inlineStr">
+      <c r="E185" t="inlineStr">
         <is>
           <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=f7c890c6597a8569</t>
         </is>

--- a/results/job_matches_2026-04-23.xlsx
+++ b/results/job_matches_2026-04-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G185"/>
+  <dimension ref="A1:G192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer/ Architecture (ADF &amp; Databricks)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FocusKPI Inc.</t>
+          <t>United Vein &amp; Vascular Centers</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, SQS, SNS, RDS, Hive, Spark</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad314dbf5fcf61a2</t>
+          <t>https://www.indeed.com/viewjob?jk=443e4c4dac7242b8</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer/ Architecture (ADF &amp; Databricks)</t>
+          <t>AWS Architect with AI + Automation</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>United Vein &amp; Vascular Centers</t>
+          <t>ERP Initiatives Group Inc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Clarksburg, MD, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,42 +661,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=443e4c4dac7242b8</t>
+          <t>https://www.indeed.com/viewjob?jk=46058fb33ffd00c5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AWS Architect with AI + Automation</t>
+          <t>Associate Data and AI Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ERP Initiatives Group Inc.</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Clarksburg, MD, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server</t>
+          <t>AWS, EMR, Kinesis, Redshift, S3, RDS, GCP, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46058fb33ffd00c5</t>
+          <t>https://www.indeed.com/viewjob?jk=718af7ca01e94aee</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=718af7ca01e94aee</t>
+          <t>https://www.indeed.com/viewjob?jk=10c4f60d661f5f00</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10c4f60d661f5f00</t>
+          <t>https://www.indeed.com/viewjob?jk=6f971eeb79a21180</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f971eeb79a21180</t>
+          <t>https://www.indeed.com/viewjob?jk=cfbf52f31ea2e787</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Associate Data and AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Climate First Bank</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, S3, RDS, GCP, Hadoop, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfbf52f31ea2e787</t>
+          <t>https://www.indeed.com/viewjob?jk=32602a30e2eae4db</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Engineer - Remote US</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Climate First Bank</t>
+          <t>Smile Digital Health</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, GCP, Cloud Storage, Scala, Kafka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,19 +881,19 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32602a30e2eae4db</t>
+          <t>https://www.indeed.com/viewjob?jk=3c0faea77dd1e82a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Remote US</t>
+          <t>Senior DevOps Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Smile Digital Health</t>
+          <t>eClinical Solutions, LLC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -906,29 +906,29 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, GCP, Cloud Storage, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c0faea77dd1e82a</t>
+          <t>https://www.indeed.com/viewjob?jk=bc6ebe88367f5090</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior DevOps Software Engineer</t>
+          <t>Senior Platform Engineer (DataOps)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>eClinical Solutions, LLC</t>
+          <t>Black Canyon Consulting</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, MLOps, MLflow</t>
+          <t>AWS, Kinesis, RDS, Azure, Google Cloud Platform, GCP, Flume, Spark, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc6ebe88367f5090</t>
+          <t>https://www.indeed.com/viewjob?jk=298c77dba97763b9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (DataOps)</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Black Canyon Consulting</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,17 +976,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Google Cloud Platform, GCP, Flume, Spark, Spark Streaming, Kafka</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=298c77dba97763b9</t>
+          <t>https://www.indeed.com/viewjob?jk=0672f1d449c9d9e2</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0672f1d449c9d9e2</t>
+          <t>https://www.indeed.com/viewjob?jk=96a88c14093ccdaf</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96a88c14093ccdaf</t>
+          <t>https://www.indeed.com/viewjob?jk=14f80cb5b125e7cc</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f80cb5b125e7cc</t>
+          <t>https://www.indeed.com/viewjob?jk=ca6623928abe2730</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca6623928abe2730</t>
+          <t>https://www.indeed.com/viewjob?jk=46e364170a7ee29f</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46e364170a7ee29f</t>
+          <t>https://www.indeed.com/viewjob?jk=0e67913bb063b4e1</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e67913bb063b4e1</t>
+          <t>https://www.indeed.com/viewjob?jk=03e6278fa86f66b6</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e6278fa86f66b6</t>
+          <t>https://www.indeed.com/viewjob?jk=a417258c27e6884b</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a417258c27e6884b</t>
+          <t>https://www.indeed.com/viewjob?jk=68ff6a6e54c5bb38</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68ff6a6e54c5bb38</t>
+          <t>https://www.indeed.com/viewjob?jk=b864420111578783</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b864420111578783</t>
+          <t>https://www.indeed.com/viewjob?jk=90020927d62d9e32</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90020927d62d9e32</t>
+          <t>https://www.indeed.com/viewjob?jk=e6445ef98b11402a</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6445ef98b11402a</t>
+          <t>https://www.indeed.com/viewjob?jk=63c85699934dff6e</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63c85699934dff6e</t>
+          <t>https://www.indeed.com/viewjob?jk=26b24994302869a9</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26b24994302869a9</t>
+          <t>https://www.indeed.com/viewjob?jk=06b0116b71837d13</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06b0116b71837d13</t>
+          <t>https://www.indeed.com/viewjob?jk=8120526ad261b6a4</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8120526ad261b6a4</t>
+          <t>https://www.indeed.com/viewjob?jk=71be0c8c221ee567</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71be0c8c221ee567</t>
+          <t>https://www.indeed.com/viewjob?jk=ee059ac44d2277d6</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee059ac44d2277d6</t>
+          <t>https://www.indeed.com/viewjob?jk=af1a0c944d7d687c</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af1a0c944d7d687c</t>
+          <t>https://www.indeed.com/viewjob?jk=a757acecac7ae896</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a757acecac7ae896</t>
+          <t>https://www.indeed.com/viewjob?jk=46cdcaa9c274907d</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46cdcaa9c274907d</t>
+          <t>https://www.indeed.com/viewjob?jk=0c545200255ccd75</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c545200255ccd75</t>
+          <t>https://www.indeed.com/viewjob?jk=99c6d56e1e9ecbd9</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99c6d56e1e9ecbd9</t>
+          <t>https://www.indeed.com/viewjob?jk=ec2268853b5e3d32</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec2268853b5e3d32</t>
+          <t>https://www.indeed.com/viewjob?jk=cc317ad96269ff6c</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc317ad96269ff6c</t>
+          <t>https://www.indeed.com/viewjob?jk=2c59791ffa8037e0</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c59791ffa8037e0</t>
+          <t>https://www.indeed.com/viewjob?jk=93c00120a22fd95f</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93c00120a22fd95f</t>
+          <t>https://www.indeed.com/viewjob?jk=e5fd76a0505c1f45</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5fd76a0505c1f45</t>
+          <t>https://www.indeed.com/viewjob?jk=52bda57a7eae91d3</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52bda57a7eae91d3</t>
+          <t>https://www.indeed.com/viewjob?jk=8d79924b7c683266</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d79924b7c683266</t>
+          <t>https://www.indeed.com/viewjob?jk=18b51a17582c12e7</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18b51a17582c12e7</t>
+          <t>https://www.indeed.com/viewjob?jk=c239cf58c8fa1c71</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c239cf58c8fa1c71</t>
+          <t>https://www.indeed.com/viewjob?jk=d5a42ec359480e0d</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5a42ec359480e0d</t>
+          <t>https://www.indeed.com/viewjob?jk=5ed6224d65d164cb</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ed6224d65d164cb</t>
+          <t>https://www.indeed.com/viewjob?jk=ffcd6c03d59f6052</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffcd6c03d59f6052</t>
+          <t>https://www.indeed.com/viewjob?jk=ddc6dd123946c0df</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddc6dd123946c0df</t>
+          <t>https://www.indeed.com/viewjob?jk=2b026195b5394344</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b026195b5394344</t>
+          <t>https://www.indeed.com/viewjob?jk=9ffe2cd40b6dd0e7</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ffe2cd40b6dd0e7</t>
+          <t>https://www.indeed.com/viewjob?jk=2581b6e435257226</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2581b6e435257226</t>
+          <t>https://www.indeed.com/viewjob?jk=de24f7419929c1bf</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de24f7419929c1bf</t>
+          <t>https://www.indeed.com/viewjob?jk=5380c72e36e9ef3d</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5380c72e36e9ef3d</t>
+          <t>https://www.indeed.com/viewjob?jk=43d4c68e7e9e2fef</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43d4c68e7e9e2fef</t>
+          <t>https://www.indeed.com/viewjob?jk=7a8557481e61c905</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a8557481e61c905</t>
+          <t>https://www.indeed.com/viewjob?jk=af8a69205565050f</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af8a69205565050f</t>
+          <t>https://www.indeed.com/viewjob?jk=dfedec5986433f19</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfedec5986433f19</t>
+          <t>https://www.indeed.com/viewjob?jk=dadc73e392f990d3</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dadc73e392f990d3</t>
+          <t>https://www.indeed.com/viewjob?jk=df6f8697322180c6</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df6f8697322180c6</t>
+          <t>https://www.indeed.com/viewjob?jk=b407a88f3a1f87f8</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b407a88f3a1f87f8</t>
+          <t>https://www.indeed.com/viewjob?jk=ce6e6d7e4f41a3e8</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce6e6d7e4f41a3e8</t>
+          <t>https://www.indeed.com/viewjob?jk=1662c7096eaa5c34</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1662c7096eaa5c34</t>
+          <t>https://www.indeed.com/viewjob?jk=9b54c062fe208581</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b54c062fe208581</t>
+          <t>https://www.indeed.com/viewjob?jk=3ca77008309e43be</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capp</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Databricks, Kafka, Splunk, MLflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ca77008309e43be</t>
+          <t>https://www.indeed.com/viewjob?jk=5005229862766ee1</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Java CI/CD Automation Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Capp</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Databricks, Kafka, Splunk, MLflow</t>
+          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5005229862766ee1</t>
+          <t>https://www.indeed.com/viewjob?jk=83b240190f37e48e</t>
         </is>
       </c>
     </row>
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83b240190f37e48e</t>
+          <t>https://www.indeed.com/viewjob?jk=9a0ee2ebd6b94c60</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Java CI/CD Automation Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Redshift, S3, Azure, Databricks, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a0ee2ebd6b94c60</t>
+          <t>https://www.indeed.com/viewjob?jk=ede735cbdf2b63e0</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Axle</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Frederick, MD, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Azure, Databricks, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ede735cbdf2b63e0</t>
+          <t>https://www.indeed.com/viewjob?jk=353f08220bc3960e</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Engineer | The Points Guy</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Axle</t>
+          <t>Red Ventures</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Frederick, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,17 +2971,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=353f08220bc3960e</t>
+          <t>https://www.indeed.com/viewjob?jk=ec2d5686f500c7c1</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,19 +3016,19 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec2d5686f500c7c1</t>
+          <t>https://www.indeed.com/viewjob?jk=ac5793781d1c8a3c</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer | The Points Guy</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Red Ventures</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac5793781d1c8a3c</t>
+          <t>https://www.indeed.com/viewjob?jk=e3a17b22e5142267</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Analytics Engineer (Data Modeling &amp; BI)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Keeper Security</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3a17b22e5142267</t>
+          <t>https://www.indeed.com/viewjob?jk=b319560288703a69</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (Data Modeling &amp; BI)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Keeper Security</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, clustering keys, PostgreSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b319560288703a69</t>
+          <t>https://www.indeed.com/viewjob?jk=53f7dd47c3f8803c</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>CA IAM Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, clustering keys, PostgreSQL, Data Modeling, Dimensional Modeling</t>
+          <t>Redshift, IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Snowflake, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53f7dd47c3f8803c</t>
+          <t>https://www.indeed.com/viewjob?jk=1a8d75516142a508</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>CA IAM Engineer</t>
+          <t>Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Verse</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Redshift, IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Snowflake, Tableau, Tableau Server</t>
+          <t>Kinesis, Redshift, S3, RDS, Databricks, GCP, BigQuery, Hadoop, Hive, HBase</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a8d75516142a508</t>
+          <t>https://www.indeed.com/viewjob?jk=2169de43fedb76d3</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Engineering</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Verse</t>
+          <t>SambaNova Systems</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, S3, RDS, Databricks, GCP, BigQuery, Hadoop, Hive, HBase</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2169de43fedb76d3</t>
+          <t>https://www.indeed.com/viewjob?jk=564c2131c7a47b4e</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Sr. Platform Engineering</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SambaNova Systems</t>
+          <t>archer</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=564c2131c7a47b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=e910893e7900f872</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr. Platform Engineering</t>
+          <t>Computer Programmer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>archer</t>
+          <t>Axle</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,52 +3286,52 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e910893e7900f872</t>
+          <t>https://www.indeed.com/viewjob?jk=b3f8d985ccebf8fe</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Computer Programmer</t>
+          <t>Data Engineer (AIA)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Axle</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3f8d985ccebf8fe</t>
+          <t>https://www.indeed.com/viewjob?jk=422b5002f3c92e96</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=422b5002f3c92e96</t>
+          <t>https://www.indeed.com/viewjob?jk=4ca947b911b13d47</t>
         </is>
       </c>
     </row>
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ca947b911b13d47</t>
+          <t>https://www.indeed.com/viewjob?jk=2762492ad7551efe</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Engineer (AIA)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2762492ad7551efe</t>
+          <t>https://www.indeed.com/viewjob?jk=cb9acfcb385fd29f</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer, Analytics &amp; Machine Learning Enablement</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Keeper Security</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb9acfcb385fd29f</t>
+          <t>https://www.indeed.com/viewjob?jk=b569d0296983d6a1</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer, Analytics &amp; Machine Learning Enablement</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Keeper Security</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,17 +3496,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b569d0296983d6a1</t>
+          <t>https://www.indeed.com/viewjob?jk=6a924e0d6d13cba9</t>
         </is>
       </c>
     </row>
@@ -4143,17 +4143,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>AI Engineer - Insurance Domain - HYBRID</t>
+          <t>Business Data Scientist, Marketing Analytics</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Warren, NJ, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Spark, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeda85e53ae1234a</t>
+          <t>https://www.indeed.com/viewjob?jk=af7dae27066ed5bc</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back-End (Java &amp; Spring Boot)</t>
+          <t>AI Engineer - Insurance Domain - HYBRID</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>PlanOmatic HQ</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Warren, NJ, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4197b722f1b29f84</t>
+          <t>https://www.indeed.com/viewjob?jk=aeda85e53ae1234a</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Integration Developer</t>
+          <t>Senior Software Engineer, Back-End (Java &amp; Spring Boot)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>AlayaCare</t>
+          <t>PlanOmatic HQ</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,69 +4231,69 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d6930b008143758</t>
+          <t>https://www.indeed.com/viewjob?jk=4197b722f1b29f84</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Sr Systems Engineer</t>
+          <t>Senior Integration Developer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>CEI Services</t>
+          <t>AlayaCare</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Fargo, ND, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f846bcd41f966d19</t>
+          <t>https://www.indeed.com/viewjob?jk=2d6930b008143758</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Sr Systems Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>MasTec Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Fargo, ND, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba06f08c24782d2d</t>
+          <t>https://www.indeed.com/viewjob?jk=75e319e5ec133537</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>DevOps with IoT focus</t>
+          <t>Sr Systems Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Intellimation LLC</t>
+          <t>CEI Services</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fargo, ND, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, IAM, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f64235fd5c4fac6</t>
+          <t>https://www.indeed.com/viewjob?jk=f846bcd41f966d19</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Sr Systems Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>MasTec Inc</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Fargo, ND, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=458f2e64ebd817f0</t>
+          <t>https://www.indeed.com/viewjob?jk=ba06f08c24782d2d</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>DevOps with IoT focus</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Intellimation LLC</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, IAM, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dc21140836b0e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=3f64235fd5c4fac6</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=903bc43e147b726e</t>
+          <t>https://www.indeed.com/viewjob?jk=458f2e64ebd817f0</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3666758a830bafe1</t>
+          <t>https://www.indeed.com/viewjob?jk=3dc21140836b0e1a</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d2dccb9477bbad2</t>
+          <t>https://www.indeed.com/viewjob?jk=903bc43e147b726e</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Capp</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e3afe7a50298373</t>
+          <t>https://www.indeed.com/viewjob?jk=3666758a830bafe1</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>RapidSOS</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, IAM, Scala, Kafka, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c059e9218f7e23d</t>
+          <t>https://www.indeed.com/viewjob?jk=8d2dccb9477bbad2</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>RapidSOS</t>
+          <t>Capp</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, IAM, Scala, Kafka, CI/CD, Jenkins, Terraform</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3986c9d7e69f169</t>
+          <t>https://www.indeed.com/viewjob?jk=4e3afe7a50298373</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Gen AI Platform &amp; Deployment Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>RapidSOS</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, SQS, SNS, ECS, IAM, Scala, Kafka, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ad5e385a9b79a74</t>
+          <t>https://www.indeed.com/viewjob?jk=6c059e9218f7e23d</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Voya Financial</t>
+          <t>RapidSOS</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Braintree, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, Kafka, Oracle, MySQL, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, SQS, SNS, ECS, IAM, Scala, Kafka, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f0f1071f3e2b14</t>
+          <t>https://www.indeed.com/viewjob?jk=d3986c9d7e69f169</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Trust/Security Engineer</t>
+          <t>Gen AI Platform &amp; Deployment Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Autodesk</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4254814d062ad92d</t>
+          <t>https://www.indeed.com/viewjob?jk=7ad5e385a9b79a74</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Voya Financial</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Braintree, MA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Snowflake, Data Modeling, ETL, ELT, Jenkins, Maven, Docker</t>
+          <t>Azure, Databricks, Spark, Kafka, Oracle, MySQL, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=842f8f1cf0d90520</t>
+          <t>https://www.indeed.com/viewjob?jk=06f0f1071f3e2b14</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Azure, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, S3, IAM, Snowflake, Data Modeling, ETL, ELT, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=facf27c6b3631798</t>
+          <t>https://www.indeed.com/viewjob?jk=842f8f1cf0d90520</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Backend Engineer II</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>HackerRank Careers</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, S3, ECS, IAM, Azure, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4979e4cfe40ed8d</t>
+          <t>https://www.indeed.com/viewjob?jk=facf27c6b3631798</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
+          <t>Backend Engineer II</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>HackerRank Careers</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d356cba46c60202</t>
+          <t>https://www.indeed.com/viewjob?jk=d4979e4cfe40ed8d</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>AI Engineer (AIA)</t>
+          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=620262fd8bc038be</t>
+          <t>https://www.indeed.com/viewjob?jk=3d356cba46c60202</t>
         </is>
       </c>
     </row>
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c87da22babbe085</t>
+          <t>https://www.indeed.com/viewjob?jk=620262fd8bc038be</t>
         </is>
       </c>
     </row>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=537fe809ab41770d</t>
+          <t>https://www.indeed.com/viewjob?jk=4c87da22babbe085</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3776f71cd705f403</t>
+          <t>https://www.indeed.com/viewjob?jk=537fe809ab41770d</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,32 +5046,32 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57e40902475718d3</t>
+          <t>https://www.indeed.com/viewjob?jk=3776f71cd705f403</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer</t>
+          <t>AI Engineer (AIA)</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Fueled</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,32 +5081,32 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9642665184944e11</t>
+          <t>https://www.indeed.com/viewjob?jk=57e40902475718d3</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Senior Trust/Security Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Autodesk</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1de30f12b78fca01</t>
+          <t>https://www.indeed.com/viewjob?jk=4254814d062ad92d</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Multi-Cloud Networking Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, IAM, RDS, Scala, Oracle, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,19 +5151,19 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88b23e7d0b05c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=7ff8e0f386ef907b</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>DevOps / Platform Engineer</t>
+          <t>Senior Systems Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Vivacity Tech PBC</t>
+          <t>Fueled</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed1d3fe1d3532916</t>
+          <t>https://www.indeed.com/viewjob?jk=9642665184944e11</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Illumio</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cad79b56c244d0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=1de30f12b78fca01</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS)</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Capnexus</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Scala, DynamoDB, Data Modeling</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a7b11ddd229f030</t>
+          <t>https://www.indeed.com/viewjob?jk=b88b23e7d0b05c8f</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>BI Engineer I (Hybrid)</t>
+          <t>DevOps / Platform Engineer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>NEUMO</t>
+          <t>Vivacity Tech PBC</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Fort Wayne, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,34 +5281,34 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d2a5858f9149296</t>
+          <t>https://www.indeed.com/viewjob?jk=ed1d3fe1d3532916</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Software Engineer, Ads Infra - Serving and Foundation</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Illumio</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hive, Spark, Scala, Kafka, Data Modeling, ETL, Airflow, Git</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e26cb9e516d559dc</t>
+          <t>https://www.indeed.com/viewjob?jk=cad79b56c244d0fa</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>AI-ML Engineer 1</t>
+          <t>Senior Data Engineer (AWS)</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Universal Avionics Systems Corporation</t>
+          <t>Capnexus</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Tucson, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Hadoop, Spark, Scala, Docker, Kubernetes, Git</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Scala, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3e0f3955fde63ec</t>
+          <t>https://www.indeed.com/viewjob?jk=5a7b11ddd229f030</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Warranty Data Analyst / Data Scientist</t>
+          <t>BI Engineer I (Hybrid)</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>NEUMO</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Fort Wayne, IN, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,34 +5386,34 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e9bb1ef1dd7ba48</t>
+          <t>https://www.indeed.com/viewjob?jk=9d2a5858f9149296</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Warranty Data Analyst / Data Scientist</t>
+          <t>Software Engineer, Ads Infra - Serving and Foundation</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Hive, Spark, Scala, Kafka, Data Modeling, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ffd491a76c9fa66</t>
+          <t>https://www.indeed.com/viewjob?jk=e26cb9e516d559dc</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI-ML Engineer 1</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Headspace</t>
+          <t>Universal Avionics Systems Corporation</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tucson, AZ, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,34 +5456,34 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, S3, Azure, GCP, Hadoop, Spark, Scala, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbb7191dcfe18f53</t>
+          <t>https://www.indeed.com/viewjob?jk=e3e0f3955fde63ec</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Software Engineer - DevSecOps (Associate, Experienced or Senior)</t>
+          <t>DevOps Engineer, Senior</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Mister Car Wash</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Tucson, AZ, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,34 +5491,34 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afe37944ff3c78ea</t>
+          <t>https://www.indeed.com/viewjob?jk=414fb4f6d3a8dcd9</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Software Intern</t>
+          <t>Software Engineer III (CJIS)</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>County of San Luis Obispo</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,34 +5526,34 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Azure, PostgreSQL, DynamoDB, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, GCP, SQL Server, MySQL, DynamoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afbd60d97bfacc60</t>
+          <t>https://www.indeed.com/viewjob?jk=2cda7602e4b5904c</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Warranty Data Analyst / Data Scientist</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Gametime United</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,42 +5561,42 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24a25e68a1bd6d4f</t>
+          <t>https://www.indeed.com/viewjob?jk=2e9bb1ef1dd7ba48</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Warranty Data Analyst / Data Scientist</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,67 +5606,67 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=672dba9cce12de5f</t>
+          <t>https://www.indeed.com/viewjob?jk=2ffd491a76c9fa66</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Trepp</t>
+          <t>Headspace</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, Spark, Scala, Data Modeling, CI/CD, Git</t>
+          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d561d8c2375dd6b1</t>
+          <t>https://www.indeed.com/viewjob?jk=cbb7191dcfe18f53</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer-Azure Data &amp; Analytics Engineer - State National</t>
+          <t>Software Engineer - DevSecOps (Associate, Experienced or Senior)</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Markel Corporation</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Bedford, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,59 +5676,59 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94507e2995b9ee29</t>
+          <t>https://www.indeed.com/viewjob?jk=afe37944ff3c78ea</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Data Engineer II - Information Technology</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Board of Governors of the Federal Reserve System</t>
+          <t>Gametime United</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, PostgreSQL, NoSQL</t>
+          <t>AWS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b222160bc0c2b3e3</t>
+          <t>https://www.indeed.com/viewjob?jk=24a25e68a1bd6d4f</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>nSCALE</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Barstow, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,34 +5736,34 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
+          <t>AWS, Glue, Lambda, Redshift, IAM, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc6c300d9777dc4b</t>
+          <t>https://www.indeed.com/viewjob?jk=a2f5cef76808163a</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Data Engineer - Seattle, WA</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>nSCALE</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,29 +5771,29 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=894fb5b066595659</t>
+          <t>https://www.indeed.com/viewjob?jk=672dba9cce12de5f</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Data Solution Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>SimilarWeb</t>
+          <t>Trepp</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5806,34 +5806,34 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, S3, Spark, Scala, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e039b4fcb467133</t>
+          <t>https://www.indeed.com/viewjob?jk=d561d8c2375dd6b1</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Engineer, Developer Platform (Cloud Apps)</t>
+          <t>Senior Infrastructure Engineer-Azure Data &amp; Analytics Engineer - State National</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Motional</t>
+          <t>Markel Corporation</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Bedford, TX, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,34 +5841,34 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, NoSQL, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a10c8d4659b2bc91</t>
+          <t>https://www.indeed.com/viewjob?jk=94507e2995b9ee29</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Engineer II - Information Technology</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Envoy global</t>
+          <t>Board of Governors of the Federal Reserve System</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,34 +5876,34 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, Scala, SQL Server, Splunk, CI/CD, Azure DevOps, Terraform, AKS, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d81e4212199a1a8</t>
+          <t>https://www.indeed.com/viewjob?jk=b222160bc0c2b3e3</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Envoy global</t>
+          <t>nSCALE</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Barstow, TX, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,34 +5911,34 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, Scala, SQL Server, Splunk, CI/CD, Azure DevOps, Terraform, AKS, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d276b3164ac33893</t>
+          <t>https://www.indeed.com/viewjob?jk=bc6c300d9777dc4b</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>SQL Engineer</t>
+          <t>Data Engineer - Seattle, WA</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Mechanical Licensing Collective</t>
+          <t>nSCALE</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,34 +5946,34 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AWS, Athena, RDS, Scala, Oracle, PostgreSQL, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3db429a534810fa</t>
+          <t>https://www.indeed.com/viewjob?jk=894fb5b066595659</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Solution Engineer</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Alpaca</t>
+          <t>SimilarWeb</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5981,34 +5981,34 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Spark, Scala, ETL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cf5cd1df0f54fe6</t>
+          <t>https://www.indeed.com/viewjob?jk=8e039b4fcb467133</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
+          <t>Engineer, Developer Platform (Cloud Apps)</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>Motional</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6016,34 +6016,34 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, NoSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ae2d7c352959fb2</t>
+          <t>https://www.indeed.com/viewjob?jk=a10c8d4659b2bc91</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>University of Maryland Medical System</t>
+          <t>Envoy global</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>North Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6051,34 +6051,34 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, MapReduce, Spark, Scala, Oracle, PostgreSQL, MongoDB</t>
+          <t>Azure, Blob Storage, Scala, SQL Server, Splunk, CI/CD, Azure DevOps, Terraform, AKS, Git</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4188adfee24d1373</t>
+          <t>https://www.indeed.com/viewjob?jk=3d81e4212199a1a8</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Technical Operations Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Codoxo</t>
+          <t>Envoy global</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6086,34 +6086,34 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, NoSQL, ETL, Airflow, Bitbucket, CloudWatch</t>
+          <t>Azure, Blob Storage, Scala, SQL Server, Splunk, CI/CD, Azure DevOps, Terraform, AKS, Git</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e78a417a0f4410ac</t>
+          <t>https://www.indeed.com/viewjob?jk=d276b3164ac33893</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Senior Quality Platform Engineer</t>
+          <t>SQL Engineer</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Circle.so</t>
+          <t>Mechanical Licensing Collective</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6121,34 +6121,34 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
+          <t>AWS, Athena, RDS, Scala, Oracle, PostgreSQL, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3752971091aeeac9</t>
+          <t>https://www.indeed.com/viewjob?jk=e3db429a534810fa</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform &amp; Product</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Ware Malcomb</t>
+          <t>Alpaca</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6156,34 +6156,34 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, GCP, Spark, Scala, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aed0adf2e92986f6</t>
+          <t>https://www.indeed.com/viewjob?jk=8cf5cd1df0f54fe6</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6191,34 +6191,34 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab7793f0a792b417</t>
+          <t>https://www.indeed.com/viewjob?jk=2ae2d7c352959fb2</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>University of Maryland Medical System</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>North Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Hadoop, HDFS, Hive, MapReduce, Spark, Scala, Oracle, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -6236,24 +6236,24 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=650677ad14cf645f</t>
+          <t>https://www.indeed.com/viewjob?jk=4188adfee24d1373</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Platform</t>
+          <t>Technical Operations Engineer</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Ramp</t>
+          <t>Codoxo</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6261,34 +6261,34 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Terraform, Airflow</t>
+          <t>AWS, Lambda, S3, RDS, Scala, NoSQL, ETL, Airflow, Bitbucket, CloudWatch</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45e12b77b9565199</t>
+          <t>https://www.indeed.com/viewjob?jk=e78a417a0f4410ac</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Quality Platform Engineer</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Empirx Health</t>
+          <t>Circle.so</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6296,34 +6296,34 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Blob Storage, GCP, Scala, Kafka, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c08697ee3f4bc0ba</t>
+          <t>https://www.indeed.com/viewjob?jk=3752971091aeeac9</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Enterprise AI Architect</t>
+          <t>Senior Software Engineer, Platform &amp; Product</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Capp</t>
+          <t>Ware Malcomb</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -6341,24 +6341,24 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a69902c54cdf2463</t>
+          <t>https://www.indeed.com/viewjob?jk=aed0adf2e92986f6</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Azure, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -6376,24 +6376,24 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff779f0dce63ada3</t>
+          <t>https://www.indeed.com/viewjob?jk=ab7793f0a792b417</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Azure, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -6411,24 +6411,24 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb55e9f7a6dc231</t>
+          <t>https://www.indeed.com/viewjob?jk=650677ad14cf645f</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Health-E Commerce</t>
+          <t>Ramp</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6436,34 +6436,34 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, Scala, Data Modeling, ETL, Azure DevOps, Python</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56afd442294fd678</t>
+          <t>https://www.indeed.com/viewjob?jk=45e12b77b9565199</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Go Outdoors Payments</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Brandt Information Services, Inc.</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6471,34 +6471,34 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f9736f5f852f3d</t>
+          <t>https://www.indeed.com/viewjob?jk=185c1836bede91b1</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Go Outdoors Payments</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Brandt Information Services, Inc.</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6506,34 +6506,34 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e66c9de7a81a7d66</t>
+          <t>https://www.indeed.com/viewjob?jk=2cedfc80fbfee214</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Fairlife, LLC</t>
+          <t>Empirx Health</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6541,34 +6541,34 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Star Schema, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, Databricks, Blob Storage, GCP, Scala, Kafka, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f203c334e20f61e9</t>
+          <t>https://www.indeed.com/viewjob?jk=c08697ee3f4bc0ba</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Enterprise AI Architect</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Capp</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -6586,24 +6586,24 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd98e6c90182dad1</t>
+          <t>https://www.indeed.com/viewjob?jk=a69902c54cdf2463</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+          <t>Azure, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -6621,24 +6621,24 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1188cf2ae8e587af</t>
+          <t>https://www.indeed.com/viewjob?jk=ff779f0dce63ada3</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+          <t>Azure, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -6656,24 +6656,24 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec0dc8f9f8c8d698</t>
+          <t>https://www.indeed.com/viewjob?jk=9eb55e9f7a6dc231</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Java Compliance &amp; Governance Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Health-E Commerce</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6681,34 +6681,34 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
+          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, Scala, Data Modeling, ETL, Azure DevOps, Python</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=243990c269c56673</t>
+          <t>https://www.indeed.com/viewjob?jk=56afd442294fd678</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Java Compliance &amp; Governance Developer</t>
+          <t>Senior Software Engineer Go Outdoors Payments</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Brandt Information Services, Inc.</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6716,34 +6716,34 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9d53f3c6ff20349</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f9736f5f852f3d</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Java Compliance &amp; Governance Developer</t>
+          <t>Senior Software Engineer Go Outdoors Payments</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Brandt Information Services, Inc.</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6751,34 +6751,34 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14d0312c67f01746</t>
+          <t>https://www.indeed.com/viewjob?jk=e66c9de7a81a7d66</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Fairlife, LLC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6786,34 +6786,34 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Star Schema, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d2728ef533caf7a</t>
+          <t>https://www.indeed.com/viewjob?jk=f203c334e20f61e9</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Java Compliance &amp; Governance Developer</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Yarmouth, ME, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -6831,24 +6831,24 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68f623995aa05734</t>
+          <t>https://www.indeed.com/viewjob?jk=243990c269c56673</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Java Compliance &amp; Governance Developer</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -6866,24 +6866,24 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ef46c3d4fd66d6a</t>
+          <t>https://www.indeed.com/viewjob?jk=e9d53f3c6ff20349</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Java Compliance &amp; Governance Developer</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6891,15 +6891,260 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=14d0312c67f01746</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Metropolis</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cd98e6c90182dad1</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Metropolis</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1188cf2ae8e587af</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Metropolis</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ec0dc8f9f8c8d698</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Tyler Technologies</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Herndon, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
           <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9d2728ef533caf7a</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Tyler Technologies</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Yarmouth, ME, US USA</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=68f623995aa05734</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Tyler Technologies</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Troy, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ef46c3d4fd66d6a</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Tyler Technologies</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Overland Park, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=f7c890c6597a8569</t>
         </is>

--- a/results/job_matches_2026-04-23.xlsx
+++ b/results/job_matches_2026-04-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G192"/>
+  <dimension ref="A1:G176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,25 +643,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AWS Architect with AI + Automation</t>
+          <t>Associate Data and AI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ERP Initiatives Group Inc.</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Clarksburg, MD, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server</t>
+          <t>AWS, EMR, Kinesis, Redshift, S3, RDS, GCP, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46058fb33ffd00c5</t>
+          <t>https://www.indeed.com/viewjob?jk=718af7ca01e94aee</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=718af7ca01e94aee</t>
+          <t>https://www.indeed.com/viewjob?jk=10c4f60d661f5f00</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10c4f60d661f5f00</t>
+          <t>https://www.indeed.com/viewjob?jk=6f971eeb79a21180</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f971eeb79a21180</t>
+          <t>https://www.indeed.com/viewjob?jk=cfbf52f31ea2e787</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Associate Data and AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Climate First Bank</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, S3, RDS, GCP, Hadoop, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfbf52f31ea2e787</t>
+          <t>https://www.indeed.com/viewjob?jk=32602a30e2eae4db</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Engineer - Remote US</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Climate First Bank</t>
+          <t>Smile Digital Health</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, GCP, Cloud Storage, Scala, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,19 +846,19 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32602a30e2eae4db</t>
+          <t>https://www.indeed.com/viewjob?jk=3c0faea77dd1e82a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Remote US</t>
+          <t>Senior DevOps Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Smile Digital Health</t>
+          <t>eClinical Solutions, LLC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -871,29 +871,29 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, GCP, Cloud Storage, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c0faea77dd1e82a</t>
+          <t>https://www.indeed.com/viewjob?jk=bc6ebe88367f5090</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior DevOps Software Engineer</t>
+          <t>Senior Platform Engineer (DataOps)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>eClinical Solutions, LLC</t>
+          <t>Black Canyon Consulting</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, MLOps, MLflow</t>
+          <t>AWS, Kinesis, RDS, Azure, Google Cloud Platform, GCP, Flume, Spark, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc6ebe88367f5090</t>
+          <t>https://www.indeed.com/viewjob?jk=298c77dba97763b9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (DataOps)</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Black Canyon Consulting</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Google Cloud Platform, GCP, Flume, Spark, Spark Streaming, Kafka</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=298c77dba97763b9</t>
+          <t>https://www.indeed.com/viewjob?jk=0672f1d449c9d9e2</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0672f1d449c9d9e2</t>
+          <t>https://www.indeed.com/viewjob?jk=96a88c14093ccdaf</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96a88c14093ccdaf</t>
+          <t>https://www.indeed.com/viewjob?jk=14f80cb5b125e7cc</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f80cb5b125e7cc</t>
+          <t>https://www.indeed.com/viewjob?jk=ca6623928abe2730</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca6623928abe2730</t>
+          <t>https://www.indeed.com/viewjob?jk=46e364170a7ee29f</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46e364170a7ee29f</t>
+          <t>https://www.indeed.com/viewjob?jk=0e67913bb063b4e1</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e67913bb063b4e1</t>
+          <t>https://www.indeed.com/viewjob?jk=03e6278fa86f66b6</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e6278fa86f66b6</t>
+          <t>https://www.indeed.com/viewjob?jk=a417258c27e6884b</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a417258c27e6884b</t>
+          <t>https://www.indeed.com/viewjob?jk=68ff6a6e54c5bb38</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68ff6a6e54c5bb38</t>
+          <t>https://www.indeed.com/viewjob?jk=b864420111578783</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b864420111578783</t>
+          <t>https://www.indeed.com/viewjob?jk=90020927d62d9e32</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90020927d62d9e32</t>
+          <t>https://www.indeed.com/viewjob?jk=e6445ef98b11402a</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6445ef98b11402a</t>
+          <t>https://www.indeed.com/viewjob?jk=63c85699934dff6e</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63c85699934dff6e</t>
+          <t>https://www.indeed.com/viewjob?jk=26b24994302869a9</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26b24994302869a9</t>
+          <t>https://www.indeed.com/viewjob?jk=06b0116b71837d13</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06b0116b71837d13</t>
+          <t>https://www.indeed.com/viewjob?jk=8120526ad261b6a4</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8120526ad261b6a4</t>
+          <t>https://www.indeed.com/viewjob?jk=71be0c8c221ee567</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71be0c8c221ee567</t>
+          <t>https://www.indeed.com/viewjob?jk=ee059ac44d2277d6</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee059ac44d2277d6</t>
+          <t>https://www.indeed.com/viewjob?jk=af1a0c944d7d687c</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af1a0c944d7d687c</t>
+          <t>https://www.indeed.com/viewjob?jk=a757acecac7ae896</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a757acecac7ae896</t>
+          <t>https://www.indeed.com/viewjob?jk=46cdcaa9c274907d</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46cdcaa9c274907d</t>
+          <t>https://www.indeed.com/viewjob?jk=0c545200255ccd75</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c545200255ccd75</t>
+          <t>https://www.indeed.com/viewjob?jk=99c6d56e1e9ecbd9</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99c6d56e1e9ecbd9</t>
+          <t>https://www.indeed.com/viewjob?jk=ec2268853b5e3d32</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec2268853b5e3d32</t>
+          <t>https://www.indeed.com/viewjob?jk=cc317ad96269ff6c</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc317ad96269ff6c</t>
+          <t>https://www.indeed.com/viewjob?jk=2c59791ffa8037e0</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c59791ffa8037e0</t>
+          <t>https://www.indeed.com/viewjob?jk=93c00120a22fd95f</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93c00120a22fd95f</t>
+          <t>https://www.indeed.com/viewjob?jk=e5fd76a0505c1f45</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5fd76a0505c1f45</t>
+          <t>https://www.indeed.com/viewjob?jk=52bda57a7eae91d3</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52bda57a7eae91d3</t>
+          <t>https://www.indeed.com/viewjob?jk=8d79924b7c683266</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d79924b7c683266</t>
+          <t>https://www.indeed.com/viewjob?jk=18b51a17582c12e7</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18b51a17582c12e7</t>
+          <t>https://www.indeed.com/viewjob?jk=c239cf58c8fa1c71</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c239cf58c8fa1c71</t>
+          <t>https://www.indeed.com/viewjob?jk=d5a42ec359480e0d</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5a42ec359480e0d</t>
+          <t>https://www.indeed.com/viewjob?jk=5ed6224d65d164cb</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ed6224d65d164cb</t>
+          <t>https://www.indeed.com/viewjob?jk=ffcd6c03d59f6052</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffcd6c03d59f6052</t>
+          <t>https://www.indeed.com/viewjob?jk=ddc6dd123946c0df</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddc6dd123946c0df</t>
+          <t>https://www.indeed.com/viewjob?jk=2b026195b5394344</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b026195b5394344</t>
+          <t>https://www.indeed.com/viewjob?jk=9ffe2cd40b6dd0e7</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ffe2cd40b6dd0e7</t>
+          <t>https://www.indeed.com/viewjob?jk=2581b6e435257226</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2581b6e435257226</t>
+          <t>https://www.indeed.com/viewjob?jk=de24f7419929c1bf</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de24f7419929c1bf</t>
+          <t>https://www.indeed.com/viewjob?jk=5380c72e36e9ef3d</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5380c72e36e9ef3d</t>
+          <t>https://www.indeed.com/viewjob?jk=43d4c68e7e9e2fef</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43d4c68e7e9e2fef</t>
+          <t>https://www.indeed.com/viewjob?jk=7a8557481e61c905</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a8557481e61c905</t>
+          <t>https://www.indeed.com/viewjob?jk=af8a69205565050f</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af8a69205565050f</t>
+          <t>https://www.indeed.com/viewjob?jk=dfedec5986433f19</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfedec5986433f19</t>
+          <t>https://www.indeed.com/viewjob?jk=dadc73e392f990d3</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dadc73e392f990d3</t>
+          <t>https://www.indeed.com/viewjob?jk=df6f8697322180c6</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df6f8697322180c6</t>
+          <t>https://www.indeed.com/viewjob?jk=b407a88f3a1f87f8</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b407a88f3a1f87f8</t>
+          <t>https://www.indeed.com/viewjob?jk=ce6e6d7e4f41a3e8</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce6e6d7e4f41a3e8</t>
+          <t>https://www.indeed.com/viewjob?jk=1662c7096eaa5c34</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1662c7096eaa5c34</t>
+          <t>https://www.indeed.com/viewjob?jk=9b54c062fe208581</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b54c062fe208581</t>
+          <t>https://www.indeed.com/viewjob?jk=3ca77008309e43be</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
+          <t>Java CI/CD Automation Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ca77008309e43be</t>
+          <t>https://www.indeed.com/viewjob?jk=83b240190f37e48e</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Java CI/CD Automation Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Capp</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Databricks, Kafka, Splunk, MLflow</t>
+          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5005229862766ee1</t>
+          <t>https://www.indeed.com/viewjob?jk=9a0ee2ebd6b94c60</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Java CI/CD Automation Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Redshift, S3, Azure, Databricks, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,59 +2841,59 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83b240190f37e48e</t>
+          <t>https://www.indeed.com/viewjob?jk=ede735cbdf2b63e0</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Java CI/CD Automation Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Axle</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Frederick, MD, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a0ee2ebd6b94c60</t>
+          <t>https://www.indeed.com/viewjob?jk=353f08220bc3960e</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer | The Points Guy</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Red Ventures</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Azure, Databricks, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ede735cbdf2b63e0</t>
+          <t>https://www.indeed.com/viewjob?jk=ec2d5686f500c7c1</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Engineer | The Points Guy</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Axle</t>
+          <t>Red Ventures</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Frederick, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=353f08220bc3960e</t>
+          <t>https://www.indeed.com/viewjob?jk=ac5793781d1c8a3c</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer | The Points Guy</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Red Ventures</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec2d5686f500c7c1</t>
+          <t>https://www.indeed.com/viewjob?jk=e3a17b22e5142267</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer | The Points Guy</t>
+          <t>Senior Analytics Engineer (Data Modeling &amp; BI)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Red Ventures</t>
+          <t>Keeper Security</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,17 +3006,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac5793781d1c8a3c</t>
+          <t>https://www.indeed.com/viewjob?jk=b319560288703a69</t>
         </is>
       </c>
     </row>
@@ -3028,12 +3028,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, clustering keys, PostgreSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3a17b22e5142267</t>
+          <t>https://www.indeed.com/viewjob?jk=53f7dd47c3f8803c</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (Data Modeling &amp; BI)</t>
+          <t>CA IAM Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Keeper Security</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,42 +3076,42 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Scala, Snowflake, Data Modeling</t>
+          <t>Redshift, IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Snowflake, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b319560288703a69</t>
+          <t>https://www.indeed.com/viewjob?jk=1a8d75516142a508</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Verse</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, clustering keys, PostgreSQL, Data Modeling, Dimensional Modeling</t>
+          <t>Kinesis, Redshift, S3, RDS, Databricks, GCP, BigQuery, Hadoop, Hive, HBase</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,59 +3121,59 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53f7dd47c3f8803c</t>
+          <t>https://www.indeed.com/viewjob?jk=2169de43fedb76d3</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>CA IAM Engineer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SambaNova Systems</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Redshift, IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Snowflake, Tableau, Tableau Server</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a8d75516142a508</t>
+          <t>https://www.indeed.com/viewjob?jk=564c2131c7a47b4e</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Engineering</t>
+          <t>Sr. Platform Engineering</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Verse</t>
+          <t>archer</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, S3, RDS, Databricks, GCP, BigQuery, Hadoop, Hive, HBase</t>
+          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2169de43fedb76d3</t>
+          <t>https://www.indeed.com/viewjob?jk=e910893e7900f872</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Computer Programmer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SambaNova Systems</t>
+          <t>Axle</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3221,37 +3221,37 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=564c2131c7a47b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=b3f8d985ccebf8fe</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr. Platform Engineering</t>
+          <t>Data Engineer (AIA)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>archer</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,42 +3261,42 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e910893e7900f872</t>
+          <t>https://www.indeed.com/viewjob?jk=422b5002f3c92e96</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Computer Programmer</t>
+          <t>Data Engineer (AIA)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Axle</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3f8d985ccebf8fe</t>
+          <t>https://www.indeed.com/viewjob?jk=4ca947b911b13d47</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=422b5002f3c92e96</t>
+          <t>https://www.indeed.com/viewjob?jk=2762492ad7551efe</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer (AIA)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ca947b911b13d47</t>
+          <t>https://www.indeed.com/viewjob?jk=cb9acfcb385fd29f</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Engineer (AIA)</t>
+          <t>Data Engineer, Analytics &amp; Machine Learning Enablement</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Keeper Security</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2762492ad7551efe</t>
+          <t>https://www.indeed.com/viewjob?jk=b569d0296983d6a1</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb9acfcb385fd29f</t>
+          <t>https://www.indeed.com/viewjob?jk=6a924e0d6d13cba9</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Engineer, Analytics &amp; Machine Learning Enablement</t>
+          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Keeper Security</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,42 +3461,42 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b569d0296983d6a1</t>
+          <t>https://www.indeed.com/viewjob?jk=5239f6ce7d60780b</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SIGNITIVES</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,59 +3506,59 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a924e0d6d13cba9</t>
+          <t>https://www.indeed.com/viewjob?jk=ccbfb275c784c26b</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5239f6ce7d60780b</t>
+          <t>https://www.indeed.com/viewjob?jk=b67c42af6bdf7f4d</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SIGNITIVES</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccbfb275c784c26b</t>
+          <t>https://www.indeed.com/viewjob?jk=5ed12a9528f47173</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Senior Data Engineer | The Points Guy</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Red Ventures</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server</t>
+          <t>AWS, Lambda, S3, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b67c42af6bdf7f4d</t>
+          <t>https://www.indeed.com/viewjob?jk=aa160af377aea6a2</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Specialist Software Engineering</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Kinesis, S3, API Gateway, ECS, Event Hubs, Zookeeper, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ed12a9528f47173</t>
+          <t>https://www.indeed.com/viewjob?jk=66f8131b391d620e</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Data Engineer | The Points Guy</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Red Ventures</t>
+          <t>Focus Financial Partners</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Dask, Snowflake</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa160af377aea6a2</t>
+          <t>https://www.indeed.com/viewjob?jk=dc6ec804cfff5642</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Specialist Software Engineering</t>
+          <t>Senior Full-Stack Python Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>N-iX</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, API Gateway, ECS, Event Hubs, Zookeeper, Kafka, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Cloud Storage, Vertex AI, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f8131b391d620e</t>
+          <t>https://www.indeed.com/viewjob?jk=365bb0b9ec3ce321</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Software Development Engineer - Credential API</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Focus Financial Partners</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Dask, Snowflake</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,94 +3751,94 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc6ec804cfff5642</t>
+          <t>https://www.indeed.com/viewjob?jk=a4c302fda1f6ae84</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Python Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>N-iX</t>
+          <t>Bloom Growth Partners</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Cloud Storage, Vertex AI, Scala, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=365bb0b9ec3ce321</t>
+          <t>https://www.indeed.com/viewjob?jk=ec3ffe3d2951f742</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Software Development Engineer - Credential API</t>
+          <t>Senior DevOps Engineer II</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4c302fda1f6ae84</t>
+          <t>https://www.indeed.com/viewjob?jk=3af6a74b61fd0779</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer II</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>Gates Foundation</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, ELT</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af6a74b61fd0779</t>
+          <t>https://www.indeed.com/viewjob?jk=d0e09f867e58f64d</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Azure Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Gates Foundation</t>
+          <t>Witherite Law Group</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, ELT</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0e09f867e58f64d</t>
+          <t>https://www.indeed.com/viewjob?jk=2d4c16398c048d9f</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management-Cloud Engineer-Associate-Dallas</t>
+          <t>Senior Software Engineer - Contributory Network</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Scala, NoSQL, CI/CD, Jenkins, AWS CodePipeline, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, ECS, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd9663ecc56297d4</t>
+          <t>https://www.indeed.com/viewjob?jk=9a1c158c64508404</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Azure Engineer</t>
+          <t>Site Reliability Engineer (SRE) - AI Platform &amp; Cloud</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Witherite Law Group</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, API Gateway, RDS, Azure, Spark, Kafka, Snowflake, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d4c16398c048d9f</t>
+          <t>https://www.indeed.com/viewjob?jk=67434a699408c40f</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Contributory Network</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>Health-E Commerce</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, ECS, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a1c158c64508404</t>
+          <t>https://www.indeed.com/viewjob?jk=2b75ba4eaa7e2f72</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE) - AI Platform &amp; Cloud</t>
+          <t>Cloud Infrastructure, Engineer II</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Trinity Logistics</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Seaford, DE, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Spark, Kafka, Snowflake, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67434a699408c40f</t>
+          <t>https://www.indeed.com/viewjob?jk=e66613c1418d016b</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Engineer - Insurance Domain - HYBRID</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Health-E Commerce</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Warren, NJ, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b75ba4eaa7e2f72</t>
+          <t>https://www.indeed.com/viewjob?jk=aeda85e53ae1234a</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure, Engineer II</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Trinity Logistics</t>
+          <t>Kitsap Credit Union</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Seaford, DE, US USA</t>
+          <t>Bremerton, WA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Azure, Event Hubs, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, SonarQube</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e66613c1418d016b</t>
+          <t>https://www.indeed.com/viewjob?jk=150b9708ae649096</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Software Engineer, Back-End (Java &amp; Spring Boot)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Kitsap Credit Union</t>
+          <t>PlanOmatic HQ</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Bremerton, WA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, SonarQube</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=150b9708ae649096</t>
+          <t>https://www.indeed.com/viewjob?jk=4197b722f1b29f84</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Business Data Scientist, Marketing Analytics</t>
+          <t>Senior Integration Developer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>AlayaCare</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,139 +4161,139 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Spark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af7dae27066ed5bc</t>
+          <t>https://www.indeed.com/viewjob?jk=2d6930b008143758</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>AI Engineer - Insurance Domain - HYBRID</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Warren, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeda85e53ae1234a</t>
+          <t>https://www.indeed.com/viewjob?jk=75e319e5ec133537</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back-End (Java &amp; Spring Boot)</t>
+          <t>Sr Systems Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>PlanOmatic HQ</t>
+          <t>CEI Services</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Fargo, ND, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4197b722f1b29f84</t>
+          <t>https://www.indeed.com/viewjob?jk=f846bcd41f966d19</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Integration Developer</t>
+          <t>Sr Systems Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>AlayaCare</t>
+          <t>MasTec Inc</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Fargo, ND, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d6930b008143758</t>
+          <t>https://www.indeed.com/viewjob?jk=ba06f08c24782d2d</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>DevOps with IoT focus</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Intellimation LLC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, IAM, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75e319e5ec133537</t>
+          <t>https://www.indeed.com/viewjob?jk=3f64235fd5c4fac6</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Sr Systems Engineer</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>CEI Services</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Fargo, ND, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f846bcd41f966d19</t>
+          <t>https://www.indeed.com/viewjob?jk=458f2e64ebd817f0</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Sr Systems Engineer</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>MasTec Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Fargo, ND, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba06f08c24782d2d</t>
+          <t>https://www.indeed.com/viewjob?jk=3dc21140836b0e1a</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>DevOps with IoT focus</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Intellimation LLC</t>
+          <t>RapidSOS</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, IAM, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, SQS, SNS, ECS, IAM, Scala, Kafka, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f64235fd5c4fac6</t>
+          <t>https://www.indeed.com/viewjob?jk=6c059e9218f7e23d</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RapidSOS</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, SQS, SNS, ECS, IAM, Scala, Kafka, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=458f2e64ebd817f0</t>
+          <t>https://www.indeed.com/viewjob?jk=d3986c9d7e69f169</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Gen AI Platform &amp; Deployment Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dc21140836b0e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=7ad5e385a9b79a74</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, IAM, Snowflake, Data Modeling, ETL, ELT, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=903bc43e147b726e</t>
+          <t>https://www.indeed.com/viewjob?jk=842f8f1cf0d90520</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Voya Financial</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Braintree, MA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>Azure, Databricks, Spark, Kafka, Oracle, MySQL, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3666758a830bafe1</t>
+          <t>https://www.indeed.com/viewjob?jk=06f0f1071f3e2b14</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, ECS, IAM, Azure, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d2dccb9477bbad2</t>
+          <t>https://www.indeed.com/viewjob?jk=facf27c6b3631798</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Backend Engineer II</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Capp</t>
+          <t>HackerRank Careers</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e3afe7a50298373</t>
+          <t>https://www.indeed.com/viewjob?jk=d4979e4cfe40ed8d</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>RapidSOS</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,112 +4651,112 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, IAM, Scala, Kafka, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c059e9218f7e23d</t>
+          <t>https://www.indeed.com/viewjob?jk=3d356cba46c60202</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Multi-Cloud Networking Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>RapidSOS</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, IAM, Scala, Kafka, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, IAM, RDS, Scala, Oracle, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3986c9d7e69f169</t>
+          <t>https://www.indeed.com/viewjob?jk=7ff8e0f386ef907b</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Gen AI Platform &amp; Deployment Engineer</t>
+          <t>Senior Systems Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Fueled</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ad5e385a9b79a74</t>
+          <t>https://www.indeed.com/viewjob?jk=9642665184944e11</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Voya Financial</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Braintree, MA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, Kafka, Oracle, MySQL, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,32 +4766,32 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f0f1071f3e2b14</t>
+          <t>https://www.indeed.com/viewjob?jk=1de30f12b78fca01</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Snowflake, Data Modeling, ETL, ELT, Jenkins, Maven, Docker</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,32 +4801,32 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=842f8f1cf0d90520</t>
+          <t>https://www.indeed.com/viewjob?jk=b88b23e7d0b05c8f</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>DevOps / Platform Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Vivacity Tech PBC</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Azure, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,67 +4836,67 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=facf27c6b3631798</t>
+          <t>https://www.indeed.com/viewjob?jk=ed1d3fe1d3532916</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Backend Engineer II</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>HackerRank Careers</t>
+          <t>Illumio</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4979e4cfe40ed8d</t>
+          <t>https://www.indeed.com/viewjob?jk=cad79b56c244d0fa</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>DMV IT Service LLC</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>Richmond, TX, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,32 +4906,32 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d356cba46c60202</t>
+          <t>https://www.indeed.com/viewjob?jk=99e35b16ebbf3788</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>AI Engineer (AIA)</t>
+          <t>Senior Data Engineer (AWS)</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Capnexus</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Scala, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,67 +4941,67 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=620262fd8bc038be</t>
+          <t>https://www.indeed.com/viewjob?jk=5a7b11ddd229f030</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>AI Engineer (AIA)</t>
+          <t>BI Engineer I (Hybrid)</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>NEUMO</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fort Wayne, IN, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c87da22babbe085</t>
+          <t>https://www.indeed.com/viewjob?jk=9d2a5858f9149296</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>AI Engineer (AIA)</t>
+          <t>Software Engineer, Ads Infra - Serving and Foundation</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Hive, Spark, Scala, Kafka, Data Modeling, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,32 +5011,32 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=537fe809ab41770d</t>
+          <t>https://www.indeed.com/viewjob?jk=e26cb9e516d559dc</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>AI Engineer (AIA)</t>
+          <t>AI-ML Engineer 1</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Universal Avionics Systems Corporation</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tucson, AZ, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, Azure, GCP, Hadoop, Spark, Scala, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,94 +5046,94 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3776f71cd705f403</t>
+          <t>https://www.indeed.com/viewjob?jk=e3e0f3955fde63ec</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>AI Engineer (AIA)</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>isolved</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Nixa, MO, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Azure Cosmos DB, NoSQL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57e40902475718d3</t>
+          <t>https://www.indeed.com/viewjob?jk=3d13a0d2142e0261</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Trust/Security Engineer</t>
+          <t>Pre-Sales Engineer (Data &amp; Analytics)</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Autodesk</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4254814d062ad92d</t>
+          <t>https://www.indeed.com/viewjob?jk=3c940790b1550a5b</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Multi-Cloud Networking Engineer</t>
+          <t>Warranty Data Analyst / Data Scientist</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Oracle, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ff8e0f386ef907b</t>
+          <t>https://www.indeed.com/viewjob?jk=2e9bb1ef1dd7ba48</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer</t>
+          <t>Warranty Data Analyst / Data Scientist</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Fueled</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9642665184944e11</t>
+          <t>https://www.indeed.com/viewjob?jk=2ffd491a76c9fa66</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Headspace</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,34 +5211,34 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1de30f12b78fca01</t>
+          <t>https://www.indeed.com/viewjob?jk=cbb7191dcfe18f53</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>DevOps Engineer, Senior</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Mister Car Wash</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Tucson, AZ, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,34 +5246,34 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88b23e7d0b05c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=414fb4f6d3a8dcd9</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>DevOps / Platform Engineer</t>
+          <t>Software Engineer III (CJIS)</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Vivacity Tech PBC</t>
+          <t>County of San Luis Obispo</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, SQL Server, MySQL, DynamoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed1d3fe1d3532916</t>
+          <t>https://www.indeed.com/viewjob?jk=2cda7602e4b5904c</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Software Engineer - DevSecOps (Associate, Experienced or Senior)</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Illumio</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cad79b56c244d0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=afe37944ff3c78ea</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS)</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Capnexus</t>
+          <t>Gametime United</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,77 +5351,77 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Scala, DynamoDB, Data Modeling</t>
+          <t>AWS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a7b11ddd229f030</t>
+          <t>https://www.indeed.com/viewjob?jk=24a25e68a1bd6d4f</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>BI Engineer I (Hybrid)</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>NEUMO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Fort Wayne, IN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, IAM, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d2a5858f9149296</t>
+          <t>https://www.indeed.com/viewjob?jk=a2f5cef76808163a</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Software Engineer, Ads Infra - Serving and Foundation</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hive, Spark, Scala, Kafka, Data Modeling, ETL, Airflow, Git</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,32 +5431,32 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e26cb9e516d559dc</t>
+          <t>https://www.indeed.com/viewjob?jk=672dba9cce12de5f</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>AI-ML Engineer 1</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Universal Avionics Systems Corporation</t>
+          <t>Trepp</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Tucson, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Hadoop, Spark, Scala, Docker, Kubernetes, Git</t>
+          <t>AWS, Glue, EMR, Lambda, S3, Spark, Scala, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,67 +5466,67 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3e0f3955fde63ec</t>
+          <t>https://www.indeed.com/viewjob?jk=d561d8c2375dd6b1</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Senior</t>
+          <t>Senior Infrastructure Engineer-Azure Data &amp; Analytics Engineer - State National</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Mister Car Wash</t>
+          <t>Markel Corporation</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Tucson, AZ, US USA</t>
+          <t>Bedford, TX, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=414fb4f6d3a8dcd9</t>
+          <t>https://www.indeed.com/viewjob?jk=94507e2995b9ee29</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Software Engineer III (CJIS)</t>
+          <t>Data Engineer II - Information Technology</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>County of San Luis Obispo</t>
+          <t>Board of Governors of the Federal Reserve System</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, SQL Server, MySQL, DynamoDB, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,159 +5536,159 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cda7602e4b5904c</t>
+          <t>https://www.indeed.com/viewjob?jk=b222160bc0c2b3e3</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Warranty Data Analyst / Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>nSCALE</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Barstow, TX, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e9bb1ef1dd7ba48</t>
+          <t>https://www.indeed.com/viewjob?jk=bc6c300d9777dc4b</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Warranty Data Analyst / Data Scientist</t>
+          <t>Data Engineer - Seattle, WA</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>nSCALE</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ffd491a76c9fa66</t>
+          <t>https://www.indeed.com/viewjob?jk=894fb5b066595659</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Solution Engineer</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Headspace</t>
+          <t>SimilarWeb</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbb7191dcfe18f53</t>
+          <t>https://www.indeed.com/viewjob?jk=8e039b4fcb467133</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Software Engineer - DevSecOps (Associate, Experienced or Senior)</t>
+          <t>Engineer, Developer Platform (Cloud Apps)</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Motional</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, NoSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afe37944ff3c78ea</t>
+          <t>https://www.indeed.com/viewjob?jk=a10c8d4659b2bc91</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Gametime United</t>
+          <t>Envoy global</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5697,38 +5697,38 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>Azure, Blob Storage, Scala, SQL Server, Splunk, CI/CD, Azure DevOps, Terraform, AKS, Git</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24a25e68a1bd6d4f</t>
+          <t>https://www.indeed.com/viewjob?jk=3d81e4212199a1a8</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Envoy global</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,34 +5736,34 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, IAM, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>Azure, Blob Storage, Scala, SQL Server, Splunk, CI/CD, Azure DevOps, Terraform, AKS, Git</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2f5cef76808163a</t>
+          <t>https://www.indeed.com/viewjob?jk=d276b3164ac33893</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>SQL Engineer</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>Mechanical Licensing Collective</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,34 +5771,34 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Athena, RDS, Scala, Oracle, PostgreSQL, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=672dba9cce12de5f</t>
+          <t>https://www.indeed.com/viewjob?jk=e3db429a534810fa</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Trepp</t>
+          <t>Alpaca</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,34 +5806,34 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, Spark, Scala, Data Modeling, CI/CD, Git</t>
+          <t>AWS, RDS, GCP, Spark, Scala, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d561d8c2375dd6b1</t>
+          <t>https://www.indeed.com/viewjob?jk=8cf5cd1df0f54fe6</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer-Azure Data &amp; Analytics Engineer - State National</t>
+          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Markel Corporation</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Bedford, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,34 +5841,34 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94507e2995b9ee29</t>
+          <t>https://www.indeed.com/viewjob?jk=2ae2d7c352959fb2</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Data Engineer II - Information Technology</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Board of Governors of the Federal Reserve System</t>
+          <t>University of Maryland Medical System</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>North Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, PostgreSQL, NoSQL</t>
+          <t>RDS, Hadoop, HDFS, Hive, MapReduce, Spark, Scala, Oracle, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5886,24 +5886,24 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b222160bc0c2b3e3</t>
+          <t>https://www.indeed.com/viewjob?jk=4188adfee24d1373</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Technical Operations Engineer</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>nSCALE</t>
+          <t>Codoxo</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Barstow, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,34 +5911,34 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
+          <t>AWS, Lambda, S3, RDS, Scala, NoSQL, ETL, Airflow, Bitbucket, CloudWatch</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc6c300d9777dc4b</t>
+          <t>https://www.indeed.com/viewjob?jk=e78a417a0f4410ac</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Data Engineer - Seattle, WA</t>
+          <t>Senior Quality Platform Engineer</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>nSCALE</t>
+          <t>Circle.so</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,29 +5946,29 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=894fb5b066595659</t>
+          <t>https://www.indeed.com/viewjob?jk=3752971091aeeac9</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Data Solution Engineer</t>
+          <t>Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>SimilarWeb</t>
+          <t>Ramp</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5981,34 +5981,34 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e039b4fcb467133</t>
+          <t>https://www.indeed.com/viewjob?jk=45e12b77b9565199</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Engineer, Developer Platform (Cloud Apps)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Motional</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6016,34 +6016,34 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, NoSQL, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a10c8d4659b2bc91</t>
+          <t>https://www.indeed.com/viewjob?jk=185c1836bede91b1</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Envoy global</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6051,34 +6051,34 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, Scala, SQL Server, Splunk, CI/CD, Azure DevOps, Terraform, AKS, Git</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d81e4212199a1a8</t>
+          <t>https://www.indeed.com/viewjob?jk=2cedfc80fbfee214</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Envoy global</t>
+          <t>Empirx Health</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6086,34 +6086,34 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, Scala, SQL Server, Splunk, CI/CD, Azure DevOps, Terraform, AKS, Git</t>
+          <t>AWS, Azure, Databricks, Blob Storage, GCP, Scala, Kafka, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d276b3164ac33893</t>
+          <t>https://www.indeed.com/viewjob?jk=c08697ee3f4bc0ba</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>SQL Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Mechanical Licensing Collective</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6121,34 +6121,34 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AWS, Athena, RDS, Scala, Oracle, PostgreSQL, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3db429a534810fa</t>
+          <t>https://www.indeed.com/viewjob?jk=cd98e6c90182dad1</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Alpaca</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6156,34 +6156,34 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Spark, Scala, ETL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cf5cd1df0f54fe6</t>
+          <t>https://www.indeed.com/viewjob?jk=1188cf2ae8e587af</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6191,34 +6191,34 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ae2d7c352959fb2</t>
+          <t>https://www.indeed.com/viewjob?jk=ec0dc8f9f8c8d698</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>University of Maryland Medical System</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>North Bethesda, MD, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, MapReduce, Spark, Scala, Oracle, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -6236,24 +6236,24 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4188adfee24d1373</t>
+          <t>https://www.indeed.com/viewjob?jk=ab7793f0a792b417</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Technical Operations Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Codoxo</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6261,34 +6261,34 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, NoSQL, ETL, Airflow, Bitbucket, CloudWatch</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e78a417a0f4410ac</t>
+          <t>https://www.indeed.com/viewjob?jk=650677ad14cf645f</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Senior Quality Platform Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Circle.so</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6296,34 +6296,34 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
+          <t>Azure, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3752971091aeeac9</t>
+          <t>https://www.indeed.com/viewjob?jk=ff779f0dce63ada3</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform &amp; Product</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Ware Malcomb</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>Azure, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -6341,24 +6341,24 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aed0adf2e92986f6</t>
+          <t>https://www.indeed.com/viewjob?jk=9eb55e9f7a6dc231</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Health-E Commerce</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6366,34 +6366,34 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, Scala, Data Modeling, ETL, Azure DevOps, Python</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab7793f0a792b417</t>
+          <t>https://www.indeed.com/viewjob?jk=56afd442294fd678</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Senior Software Engineer Go Outdoors Payments</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Brandt Information Services, Inc.</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6401,34 +6401,34 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=650677ad14cf645f</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f9736f5f852f3d</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Platform</t>
+          <t>Senior Software Engineer Go Outdoors Payments</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Ramp</t>
+          <t>Brandt Information Services, Inc.</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6436,34 +6436,34 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Terraform, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45e12b77b9565199</t>
+          <t>https://www.indeed.com/viewjob?jk=e66c9de7a81a7d66</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Fairlife, LLC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6471,34 +6471,34 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Star Schema, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=185c1836bede91b1</t>
+          <t>https://www.indeed.com/viewjob?jk=f203c334e20f61e9</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Java Compliance &amp; Governance Developer</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -6516,24 +6516,24 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cedfc80fbfee214</t>
+          <t>https://www.indeed.com/viewjob?jk=243990c269c56673</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Java Compliance &amp; Governance Developer</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Empirx Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Blob Storage, GCP, Scala, Kafka, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -6551,24 +6551,24 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c08697ee3f4bc0ba</t>
+          <t>https://www.indeed.com/viewjob?jk=e9d53f3c6ff20349</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Enterprise AI Architect</t>
+          <t>Java Compliance &amp; Governance Developer</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Capp</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -6586,567 +6586,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a69902c54cdf2463</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>AI Integration Engineer (Java + AI)</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D177" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>Azure, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ff779f0dce63ada3</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>AI Integration Engineer (Java + AI)</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D178" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>Azure, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb55e9f7a6dc231</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>Health-E Commerce</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D179" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, Scala, Data Modeling, ETL, Azure DevOps, Python</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=56afd442294fd678</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer Go Outdoors Payments</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>Brandt Information Services, Inc.</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D180" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f9736f5f852f3d</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer Go Outdoors Payments</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>Brandt Information Services, Inc.</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>Tallahassee, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D181" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e66c9de7a81a7d66</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>Sr. Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>Fairlife, LLC</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D182" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Star Schema, ELT, Power BI, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f203c334e20f61e9</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>Java Compliance &amp; Governance Developer</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>NC, US USA</t>
-        </is>
-      </c>
-      <c r="D183" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=243990c269c56673</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>Java Compliance &amp; Governance Developer</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>NC, US USA</t>
-        </is>
-      </c>
-      <c r="D184" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e9d53f3c6ff20349</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>Java Compliance &amp; Governance Developer</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D185" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=14d0312c67f01746</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>Metropolis</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D186" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cd98e6c90182dad1</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>Metropolis</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D187" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1188cf2ae8e587af</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>Metropolis</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D188" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ec0dc8f9f8c8d698</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>Tyler Technologies</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>Herndon, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D189" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9d2728ef533caf7a</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>Tyler Technologies</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>Yarmouth, ME, US USA</t>
-        </is>
-      </c>
-      <c r="D190" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=68f623995aa05734</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>Tyler Technologies</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>Troy, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D191" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7ef46c3d4fd66d6a</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>Tyler Technologies</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>Overland Park, KS, US USA</t>
-        </is>
-      </c>
-      <c r="D192" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f7c890c6597a8569</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-23.xlsx
+++ b/results/job_matches_2026-04-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G176"/>
+  <dimension ref="A1:G175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Associate Data and AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Climate First Bank</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, S3, RDS, GCP, Hadoop, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=718af7ca01e94aee</t>
+          <t>https://www.indeed.com/viewjob?jk=32602a30e2eae4db</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10c4f60d661f5f00</t>
+          <t>https://www.indeed.com/viewjob?jk=718af7ca01e94aee</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f971eeb79a21180</t>
+          <t>https://www.indeed.com/viewjob?jk=10c4f60d661f5f00</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfbf52f31ea2e787</t>
+          <t>https://www.indeed.com/viewjob?jk=6f971eeb79a21180</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Data and AI Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Climate First Bank</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala</t>
+          <t>AWS, EMR, Kinesis, Redshift, S3, RDS, GCP, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32602a30e2eae4db</t>
+          <t>https://www.indeed.com/viewjob?jk=cfbf52f31ea2e787</t>
         </is>
       </c>
     </row>
@@ -3023,17 +3023,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>CA IAM Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, clustering keys, PostgreSQL, Data Modeling, Dimensional Modeling</t>
+          <t>Redshift, IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Snowflake, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53f7dd47c3f8803c</t>
+          <t>https://www.indeed.com/viewjob?jk=1a8d75516142a508</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CA IAM Engineer</t>
+          <t>Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Verse</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Redshift, IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Snowflake, Tableau, Tableau Server</t>
+          <t>Kinesis, Redshift, S3, RDS, Databricks, GCP, BigQuery, Hadoop, Hive, HBase</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a8d75516142a508</t>
+          <t>https://www.indeed.com/viewjob?jk=2169de43fedb76d3</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Engineering</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Verse</t>
+          <t>SambaNova Systems</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, S3, RDS, Databricks, GCP, BigQuery, Hadoop, Hive, HBase</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2169de43fedb76d3</t>
+          <t>https://www.indeed.com/viewjob?jk=564c2131c7a47b4e</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Software Engineer III - AI/ML</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SambaNova Systems</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,17 +3146,17 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=564c2131c7a47b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=e288d00b33f48efe</t>
         </is>
       </c>
     </row>
@@ -3478,17 +3478,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Specialist Software Engineering</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SIGNITIVES</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Kinesis, S3, API Gateway, ECS, Event Hubs, Zookeeper, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccbfb275c784c26b</t>
+          <t>https://www.indeed.com/viewjob?jk=66f8131b391d620e</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Senior Data Engineer | The Points Guy</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Red Ventures</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server</t>
+          <t>AWS, Lambda, S3, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b67c42af6bdf7f4d</t>
+          <t>https://www.indeed.com/viewjob?jk=aa160af377aea6a2</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>SIGNITIVES</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ed12a9528f47173</t>
+          <t>https://www.indeed.com/viewjob?jk=ccbfb275c784c26b</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Data Engineer | The Points Guy</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Red Ventures</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa160af377aea6a2</t>
+          <t>https://www.indeed.com/viewjob?jk=b67c42af6bdf7f4d</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Specialist Software Engineering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,17 +3636,17 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, API Gateway, ECS, Event Hubs, Zookeeper, Kafka, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f8131b391d620e</t>
+          <t>https://www.indeed.com/viewjob?jk=5ed12a9528f47173</t>
         </is>
       </c>
     </row>
@@ -3793,17 +3793,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>Health-E Commerce</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af6a74b61fd0779</t>
+          <t>https://www.indeed.com/viewjob?jk=2b75ba4eaa7e2f72</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior DevOps Engineer II</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Gates Foundation</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, ELT</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0e09f867e58f64d</t>
+          <t>https://www.indeed.com/viewjob?jk=3af6a74b61fd0779</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Azure Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Witherite Law Group</t>
+          <t>Gates Foundation</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, ELT</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d4c16398c048d9f</t>
+          <t>https://www.indeed.com/viewjob?jk=d0e09f867e58f64d</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Contributory Network</t>
+          <t>Azure Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>Witherite Law Group</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, ECS, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a1c158c64508404</t>
+          <t>https://www.indeed.com/viewjob?jk=2d4c16398c048d9f</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE) - AI Platform &amp; Cloud</t>
+          <t>Senior Software Engineer - Contributory Network</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Spark, Kafka, Snowflake, Terraform, Docker, Kubernetes</t>
+          <t>AWS, ECS, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67434a699408c40f</t>
+          <t>https://www.indeed.com/viewjob?jk=9a1c158c64508404</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Site Reliability Engineer (SRE) - AI Platform &amp; Cloud</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Health-E Commerce</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,17 +3986,17 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, Spark, Kafka, Snowflake, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b75ba4eaa7e2f72</t>
+          <t>https://www.indeed.com/viewjob?jk=67434a699408c40f</t>
         </is>
       </c>
     </row>
@@ -4213,17 +4213,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Sr Systems Engineer</t>
+          <t>Cloud Platforms Engineer II</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>CEI Services</t>
+          <t>Amcor</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Fargo, ND, US USA</t>
+          <t>Oshkosh, WI, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,17 +4231,17 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Scala, Power BI, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f846bcd41f966d19</t>
+          <t>https://www.indeed.com/viewjob?jk=0a5bd8b939af9f70</t>
         </is>
       </c>
     </row>
@@ -4253,7 +4253,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>MasTec Inc</t>
+          <t>CEI Services</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba06f08c24782d2d</t>
+          <t>https://www.indeed.com/viewjob?jk=f846bcd41f966d19</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>DevOps with IoT focus</t>
+          <t>Sr Systems Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Intellimation LLC</t>
+          <t>MasTec Inc</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fargo, ND, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, IAM, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f64235fd5c4fac6</t>
+          <t>https://www.indeed.com/viewjob?jk=ba06f08c24782d2d</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>DevOps with IoT focus</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Intellimation LLC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, IAM, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=458f2e64ebd817f0</t>
+          <t>https://www.indeed.com/viewjob?jk=3f64235fd5c4fac6</t>
         </is>
       </c>
     </row>
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dc21140836b0e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=458f2e64ebd817f0</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>RapidSOS</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,17 +4406,17 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, IAM, Scala, Kafka, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c059e9218f7e23d</t>
+          <t>https://www.indeed.com/viewjob?jk=3dc21140836b0e1a</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3986c9d7e69f169</t>
+          <t>https://www.indeed.com/viewjob?jk=6c059e9218f7e23d</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Gen AI Platform &amp; Deployment Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>RapidSOS</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, SQS, SNS, ECS, IAM, Scala, Kafka, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ad5e385a9b79a74</t>
+          <t>https://www.indeed.com/viewjob?jk=d3986c9d7e69f169</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Gen AI Platform &amp; Deployment Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,17 +4511,17 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Snowflake, Data Modeling, ETL, ELT, Jenkins, Maven, Docker</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=842f8f1cf0d90520</t>
+          <t>https://www.indeed.com/viewjob?jk=7ad5e385a9b79a74</t>
         </is>
       </c>
     </row>
@@ -4668,17 +4668,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Multi-Cloud Networking Engineer</t>
+          <t>Software Engineer, Ads Infra - Serving and Foundation</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Oracle, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
+          <t>AWS, RDS, Hive, Spark, Scala, Kafka, Data Modeling, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ff8e0f386ef907b</t>
+          <t>https://www.indeed.com/viewjob?jk=e26cb9e516d559dc</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer</t>
+          <t>AI-ML Engineer 1</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Fueled</t>
+          <t>Universal Avionics Systems Corporation</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tucson, AZ, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, S3, Azure, GCP, Hadoop, Spark, Scala, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9642665184944e11</t>
+          <t>https://www.indeed.com/viewjob?jk=e3e0f3955fde63ec</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>DMV IT Service LLC</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Richmond, TX, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1de30f12b78fca01</t>
+          <t>https://www.indeed.com/viewjob?jk=99e35b16ebbf3788</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Senior Data Engineer (AWS)</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Capnexus</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Scala, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88b23e7d0b05c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=5a7b11ddd229f030</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>DevOps / Platform Engineer</t>
+          <t>Multi-Cloud Networking Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Vivacity Tech PBC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Scala, Oracle, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed1d3fe1d3532916</t>
+          <t>https://www.indeed.com/viewjob?jk=7ff8e0f386ef907b</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Senior Systems Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Illumio</t>
+          <t>Fueled</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cad79b56c244d0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=9642665184944e11</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>DMV IT Service LLC</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Richmond, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99e35b16ebbf3788</t>
+          <t>https://www.indeed.com/viewjob?jk=1de30f12b78fca01</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS)</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Capnexus</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Scala, DynamoDB, Data Modeling</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a7b11ddd229f030</t>
+          <t>https://www.indeed.com/viewjob?jk=b88b23e7d0b05c8f</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>BI Engineer I (Hybrid)</t>
+          <t>DevOps / Platform Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>NEUMO</t>
+          <t>Vivacity Tech PBC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Fort Wayne, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d2a5858f9149296</t>
+          <t>https://www.indeed.com/viewjob?jk=ed1d3fe1d3532916</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Software Engineer, Ads Infra - Serving and Foundation</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Illumio</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hive, Spark, Scala, Kafka, Data Modeling, ETL, Airflow, Git</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e26cb9e516d559dc</t>
+          <t>https://www.indeed.com/viewjob?jk=cad79b56c244d0fa</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>AI-ML Engineer 1</t>
+          <t>BI Engineer I (Hybrid)</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Universal Avionics Systems Corporation</t>
+          <t>NEUMO</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Tucson, AZ, US USA</t>
+          <t>Fort Wayne, IN, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,17 +5036,17 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Hadoop, Spark, Scala, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3e0f3955fde63ec</t>
+          <t>https://www.indeed.com/viewjob?jk=9d2a5858f9149296</t>
         </is>
       </c>
     </row>
@@ -5368,17 +5368,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Trepp</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, IAM, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, S3, Spark, Scala, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2f5cef76808163a</t>
+          <t>https://www.indeed.com/viewjob?jk=d561d8c2375dd6b1</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Engineer II - Information Technology</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>Board of Governors of the Federal Reserve System</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=672dba9cce12de5f</t>
+          <t>https://www.indeed.com/viewjob?jk=b222160bc0c2b3e3</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Technical Operations Engineer</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Trepp</t>
+          <t>Codoxo</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,34 +5456,34 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, Spark, Scala, Data Modeling, CI/CD, Git</t>
+          <t>AWS, Lambda, S3, RDS, Scala, NoSQL, ETL, Airflow, Bitbucket, CloudWatch</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d561d8c2375dd6b1</t>
+          <t>https://www.indeed.com/viewjob?jk=e78a417a0f4410ac</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer-Azure Data &amp; Analytics Engineer - State National</t>
+          <t>Data Solution Engineer</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Markel Corporation</t>
+          <t>SimilarWeb</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Bedford, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,34 +5491,34 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94507e2995b9ee29</t>
+          <t>https://www.indeed.com/viewjob?jk=8e039b4fcb467133</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Data Engineer II - Information Technology</t>
+          <t>Senior Quality Platform Engineer</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Board of Governors of the Federal Reserve System</t>
+          <t>Circle.so</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,34 +5526,34 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, PostgreSQL, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b222160bc0c2b3e3</t>
+          <t>https://www.indeed.com/viewjob?jk=3752971091aeeac9</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>nSCALE</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Barstow, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,34 +5561,34 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
+          <t>AWS, Glue, Lambda, Redshift, IAM, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc6c300d9777dc4b</t>
+          <t>https://www.indeed.com/viewjob?jk=a2f5cef76808163a</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Data Engineer - Seattle, WA</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>nSCALE</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,34 +5596,34 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=894fb5b066595659</t>
+          <t>https://www.indeed.com/viewjob?jk=672dba9cce12de5f</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Data Solution Engineer</t>
+          <t>Senior Infrastructure Engineer-Azure Data &amp; Analytics Engineer - State National</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>SimilarWeb</t>
+          <t>Markel Corporation</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bedford, TX, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,34 +5631,34 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e039b4fcb467133</t>
+          <t>https://www.indeed.com/viewjob?jk=94507e2995b9ee29</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Engineer, Developer Platform (Cloud Apps)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Motional</t>
+          <t>nSCALE</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Barstow, TX, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,34 +5666,34 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, NoSQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a10c8d4659b2bc91</t>
+          <t>https://www.indeed.com/viewjob?jk=bc6c300d9777dc4b</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Engineer - Seattle, WA</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Envoy global</t>
+          <t>nSCALE</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,34 +5701,34 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, Scala, SQL Server, Splunk, CI/CD, Azure DevOps, Terraform, AKS, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d81e4212199a1a8</t>
+          <t>https://www.indeed.com/viewjob?jk=894fb5b066595659</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Engineer, Developer Platform (Cloud Apps)</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Envoy global</t>
+          <t>Motional</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,34 +5736,34 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, Scala, SQL Server, Splunk, CI/CD, Azure DevOps, Terraform, AKS, Git</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, NoSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d276b3164ac33893</t>
+          <t>https://www.indeed.com/viewjob?jk=a10c8d4659b2bc91</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>SQL Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Mechanical Licensing Collective</t>
+          <t>Envoy global</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AWS, Athena, RDS, Scala, Oracle, PostgreSQL, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>Azure, Blob Storage, Scala, SQL Server, Splunk, CI/CD, Azure DevOps, Terraform, AKS, Git</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -5781,24 +5781,24 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3db429a534810fa</t>
+          <t>https://www.indeed.com/viewjob?jk=3d81e4212199a1a8</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Alpaca</t>
+          <t>Envoy global</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,34 +5806,34 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Spark, Scala, ETL, ELT, dbt, CI/CD, Airflow</t>
+          <t>Azure, Blob Storage, Scala, SQL Server, Splunk, CI/CD, Azure DevOps, Terraform, AKS, Git</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cf5cd1df0f54fe6</t>
+          <t>https://www.indeed.com/viewjob?jk=d276b3164ac33893</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
+          <t>SQL Engineer</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>Mechanical Licensing Collective</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,34 +5841,34 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Athena, RDS, Scala, Oracle, PostgreSQL, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ae2d7c352959fb2</t>
+          <t>https://www.indeed.com/viewjob?jk=e3db429a534810fa</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>University of Maryland Medical System</t>
+          <t>Alpaca</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>North Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,34 +5876,34 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, MapReduce, Spark, Scala, Oracle, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, GCP, Spark, Scala, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4188adfee24d1373</t>
+          <t>https://www.indeed.com/viewjob?jk=8cf5cd1df0f54fe6</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Technical Operations Engineer</t>
+          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Codoxo</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,34 +5911,34 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, NoSQL, ETL, Airflow, Bitbucket, CloudWatch</t>
+          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e78a417a0f4410ac</t>
+          <t>https://www.indeed.com/viewjob?jk=2ae2d7c352959fb2</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Senior Quality Platform Engineer</t>
+          <t>Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Circle.so</t>
+          <t>Ramp</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,34 +5946,34 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3752971091aeeac9</t>
+          <t>https://www.indeed.com/viewjob?jk=45e12b77b9565199</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Platform</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Ramp</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Terraform, Airflow</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45e12b77b9565199</t>
+          <t>https://www.indeed.com/viewjob?jk=185c1836bede91b1</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,24 +6026,24 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=185c1836bede91b1</t>
+          <t>https://www.indeed.com/viewjob?jk=2cedfc80fbfee214</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Empirx Health</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, Azure, Databricks, Blob Storage, GCP, Scala, Kafka, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -6061,24 +6061,24 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cedfc80fbfee214</t>
+          <t>https://www.indeed.com/viewjob?jk=c08697ee3f4bc0ba</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Empirx Health</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Blob Storage, GCP, Scala, Kafka, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -6096,24 +6096,24 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c08697ee3f4bc0ba</t>
+          <t>https://www.indeed.com/viewjob?jk=ab7793f0a792b417</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -6131,24 +6131,24 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd98e6c90182dad1</t>
+          <t>https://www.indeed.com/viewjob?jk=650677ad14cf645f</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+          <t>Azure, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -6166,24 +6166,24 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1188cf2ae8e587af</t>
+          <t>https://www.indeed.com/viewjob?jk=ff779f0dce63ada3</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+          <t>Azure, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -6201,24 +6201,24 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec0dc8f9f8c8d698</t>
+          <t>https://www.indeed.com/viewjob?jk=9eb55e9f7a6dc231</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Health-E Commerce</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6226,34 +6226,34 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, Scala, Data Modeling, ETL, Azure DevOps, Python</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab7793f0a792b417</t>
+          <t>https://www.indeed.com/viewjob?jk=56afd442294fd678</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Senior Software Engineer Go Outdoors Payments</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Brandt Information Services, Inc.</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6261,34 +6261,34 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=650677ad14cf645f</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f9736f5f852f3d</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Senior Software Engineer Go Outdoors Payments</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Brandt Information Services, Inc.</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6296,34 +6296,34 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Azure, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff779f0dce63ada3</t>
+          <t>https://www.indeed.com/viewjob?jk=e66c9de7a81a7d66</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fairlife, LLC</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6331,34 +6331,34 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Azure, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Star Schema, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb55e9f7a6dc231</t>
+          <t>https://www.indeed.com/viewjob?jk=f203c334e20f61e9</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Health-E Commerce</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6366,34 +6366,34 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, Scala, Data Modeling, ETL, Azure DevOps, Python</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56afd442294fd678</t>
+          <t>https://www.indeed.com/viewjob?jk=cd98e6c90182dad1</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Go Outdoors Payments</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Brandt Information Services, Inc.</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6401,34 +6401,34 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f9736f5f852f3d</t>
+          <t>https://www.indeed.com/viewjob?jk=1188cf2ae8e587af</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Go Outdoors Payments</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Brandt Information Services, Inc.</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6436,34 +6436,34 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e66c9de7a81a7d66</t>
+          <t>https://www.indeed.com/viewjob?jk=ec0dc8f9f8c8d698</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>Java Compliance &amp; Governance Developer</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Fairlife, LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6471,17 +6471,17 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Star Schema, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f203c334e20f61e9</t>
+          <t>https://www.indeed.com/viewjob?jk=243990c269c56673</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=243990c269c56673</t>
+          <t>https://www.indeed.com/viewjob?jk=e9d53f3c6ff20349</t>
         </is>
       </c>
     </row>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6550,41 +6550,6 @@
         </is>
       </c>
       <c r="G175" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e9d53f3c6ff20349</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>Java Compliance &amp; Governance Developer</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D176" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=14d0312c67f01746</t>
         </is>

--- a/results/job_matches_2026-04-23.xlsx
+++ b/results/job_matches_2026-04-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G175"/>
+  <dimension ref="A1:G177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Data and AI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Climate First Bank</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala</t>
+          <t>AWS, EMR, Kinesis, Redshift, S3, RDS, GCP, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32602a30e2eae4db</t>
+          <t>https://www.indeed.com/viewjob?jk=718af7ca01e94aee</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=718af7ca01e94aee</t>
+          <t>https://www.indeed.com/viewjob?jk=10c4f60d661f5f00</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10c4f60d661f5f00</t>
+          <t>https://www.indeed.com/viewjob?jk=6f971eeb79a21180</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f971eeb79a21180</t>
+          <t>https://www.indeed.com/viewjob?jk=cfbf52f31ea2e787</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Associate Data and AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Climate First Bank</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, S3, RDS, GCP, Hadoop, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfbf52f31ea2e787</t>
+          <t>https://www.indeed.com/viewjob?jk=32602a30e2eae4db</t>
         </is>
       </c>
     </row>
@@ -2743,25 +2743,25 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Java CI/CD Automation Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Redshift, S3, Azure, Databricks, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,59 +2771,59 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83b240190f37e48e</t>
+          <t>https://www.indeed.com/viewjob?jk=ede735cbdf2b63e0</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Java CI/CD Automation Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Axle</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Frederick, MD, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a0ee2ebd6b94c60</t>
+          <t>https://www.indeed.com/viewjob?jk=353f08220bc3960e</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer | The Points Guy</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Red Ventures</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Azure, Databricks, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ede735cbdf2b63e0</t>
+          <t>https://www.indeed.com/viewjob?jk=ec2d5686f500c7c1</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Engineer | The Points Guy</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Axle</t>
+          <t>Red Ventures</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Frederick, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=353f08220bc3960e</t>
+          <t>https://www.indeed.com/viewjob?jk=ac5793781d1c8a3c</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer | The Points Guy</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Red Ventures</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec2d5686f500c7c1</t>
+          <t>https://www.indeed.com/viewjob?jk=e3a17b22e5142267</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer | The Points Guy</t>
+          <t>Senior Analytics Engineer (Data Modeling &amp; BI)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Red Ventures</t>
+          <t>Keeper Security</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac5793781d1c8a3c</t>
+          <t>https://www.indeed.com/viewjob?jk=b319560288703a69</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>CA IAM Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,104 +2971,104 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Data Modeling, ETL</t>
+          <t>Redshift, IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Snowflake, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3a17b22e5142267</t>
+          <t>https://www.indeed.com/viewjob?jk=1a8d75516142a508</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (Data Modeling &amp; BI)</t>
+          <t>Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Keeper Security</t>
+          <t>Verse</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Scala, Snowflake, Data Modeling</t>
+          <t>Kinesis, Redshift, S3, RDS, Databricks, GCP, BigQuery, Hadoop, Hive, HBase</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b319560288703a69</t>
+          <t>https://www.indeed.com/viewjob?jk=2169de43fedb76d3</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CA IAM Engineer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SambaNova Systems</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Redshift, IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Snowflake, Tableau, Tableau Server</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a8d75516142a508</t>
+          <t>https://www.indeed.com/viewjob?jk=564c2131c7a47b4e</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Engineering</t>
+          <t>Software Engineer III - AI/ML</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Verse</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, S3, RDS, Databricks, GCP, BigQuery, Hadoop, Hive, HBase</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2169de43fedb76d3</t>
+          <t>https://www.indeed.com/viewjob?jk=e288d00b33f48efe</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Sr. Platform Engineering</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SambaNova Systems</t>
+          <t>archer</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=564c2131c7a47b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=e910893e7900f872</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML</t>
+          <t>Computer Programmer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Axle</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,42 +3146,42 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e288d00b33f48efe</t>
+          <t>https://www.indeed.com/viewjob?jk=b3f8d985ccebf8fe</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sr. Platform Engineering</t>
+          <t>Data Engineer (AIA)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>archer</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,42 +3191,42 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e910893e7900f872</t>
+          <t>https://www.indeed.com/viewjob?jk=422b5002f3c92e96</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Computer Programmer</t>
+          <t>Data Engineer (AIA)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Axle</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3f8d985ccebf8fe</t>
+          <t>https://www.indeed.com/viewjob?jk=4ca947b911b13d47</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=422b5002f3c92e96</t>
+          <t>https://www.indeed.com/viewjob?jk=2762492ad7551efe</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer (AIA)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ca947b911b13d47</t>
+          <t>https://www.indeed.com/viewjob?jk=cb9acfcb385fd29f</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer (AIA)</t>
+          <t>Data Engineer, Analytics &amp; Machine Learning Enablement</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Keeper Security</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2762492ad7551efe</t>
+          <t>https://www.indeed.com/viewjob?jk=b569d0296983d6a1</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb9acfcb385fd29f</t>
+          <t>https://www.indeed.com/viewjob?jk=fbdcf2158c6b2d0d</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Engineer, Analytics &amp; Machine Learning Enablement</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Keeper Security</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b569d0296983d6a1</t>
+          <t>https://www.indeed.com/viewjob?jk=6a924e0d6d13cba9</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,69 +3426,69 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a924e0d6d13cba9</t>
+          <t>https://www.indeed.com/viewjob?jk=5239f6ce7d60780b</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>SIGNITIVES</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
+          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5239f6ce7d60780b</t>
+          <t>https://www.indeed.com/viewjob?jk=ccbfb275c784c26b</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Specialist Software Engineering</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, API Gateway, ECS, Event Hubs, Zookeeper, Kafka, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f8131b391d620e</t>
+          <t>https://www.indeed.com/viewjob?jk=b67c42af6bdf7f4d</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Data Engineer | The Points Guy</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Red Ventures</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa160af377aea6a2</t>
+          <t>https://www.indeed.com/viewjob?jk=5ed12a9528f47173</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior Data Engineer | The Points Guy</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SIGNITIVES</t>
+          <t>Red Ventures</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccbfb275c784c26b</t>
+          <t>https://www.indeed.com/viewjob?jk=aa160af377aea6a2</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Specialist Software Engineering</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server</t>
+          <t>AWS, Kinesis, S3, API Gateway, ECS, Event Hubs, Zookeeper, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b67c42af6bdf7f4d</t>
+          <t>https://www.indeed.com/viewjob?jk=66f8131b391d620e</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, Kafka, Oracle, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ed12a9528f47173</t>
+          <t>https://www.indeed.com/viewjob?jk=6bd882abe2f239e8</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Full-Stack Python Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Focus Financial Partners</t>
+          <t>N-iX</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Dask, Snowflake</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Cloud Storage, Vertex AI, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc6ec804cfff5642</t>
+          <t>https://www.indeed.com/viewjob?jk=365bb0b9ec3ce321</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Python Engineer</t>
+          <t>Software Development Engineer - Credential API</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>N-iX</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Cloud Storage, Vertex AI, Scala, PostgreSQL, MySQL</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=365bb0b9ec3ce321</t>
+          <t>https://www.indeed.com/viewjob?jk=a4c302fda1f6ae84</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Software Development Engineer - Credential API</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>Focus Financial Partners</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Dask, Snowflake</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4c302fda1f6ae84</t>
+          <t>https://www.indeed.com/viewjob?jk=dc6ec804cfff5642</t>
         </is>
       </c>
     </row>
@@ -3793,17 +3793,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer II</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Health-E Commerce</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b75ba4eaa7e2f72</t>
+          <t>https://www.indeed.com/viewjob?jk=3af6a74b61fd0779</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer II</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>Gates Foundation</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, ELT</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af6a74b61fd0779</t>
+          <t>https://www.indeed.com/viewjob?jk=d0e09f867e58f64d</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Azure Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Gates Foundation</t>
+          <t>Witherite Law Group</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, ELT</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0e09f867e58f64d</t>
+          <t>https://www.indeed.com/viewjob?jk=2d4c16398c048d9f</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Azure Engineer</t>
+          <t>Senior Software Engineer - Contributory Network</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Witherite Law Group</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, ECS, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d4c16398c048d9f</t>
+          <t>https://www.indeed.com/viewjob?jk=9a1c158c64508404</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Contributory Network</t>
+          <t>Site Reliability Engineer (SRE) - AI Platform &amp; Cloud</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, ECS, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, Spark, Kafka, Snowflake, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a1c158c64508404</t>
+          <t>https://www.indeed.com/viewjob?jk=67434a699408c40f</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE) - AI Platform &amp; Cloud</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Health-E Commerce</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,17 +3986,17 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Spark, Kafka, Snowflake, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67434a699408c40f</t>
+          <t>https://www.indeed.com/viewjob?jk=2b75ba4eaa7e2f72</t>
         </is>
       </c>
     </row>
@@ -4038,17 +4038,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>AI Engineer - Insurance Domain - HYBRID</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Warren, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Google Cloud Platform, Scala, MySQL, NoSQL, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeda85e53ae1234a</t>
+          <t>https://www.indeed.com/viewjob?jk=5f84e68d5415404a</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Kitsap Credit Union</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bremerton, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, SonarQube</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, Scala, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=150b9708ae649096</t>
+          <t>https://www.indeed.com/viewjob?jk=eec716db1d652f56</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back-End (Java &amp; Spring Boot)</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>PlanOmatic HQ</t>
+          <t>Kitsap Credit Union</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Bremerton, WA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>RDS, Azure, Event Hubs, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, SonarQube</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4197b722f1b29f84</t>
+          <t>https://www.indeed.com/viewjob?jk=150b9708ae649096</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Integration Developer</t>
+          <t>Senior Software Engineer, Back-End (Java &amp; Spring Boot)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>AlayaCare</t>
+          <t>PlanOmatic HQ</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,104 +4161,104 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d6930b008143758</t>
+          <t>https://www.indeed.com/viewjob?jk=4197b722f1b29f84</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>AI Engineer - Insurance Domain - HYBRID</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Warren, NJ, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Spark, Scala, Data Modeling, ETL</t>
+          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75e319e5ec133537</t>
+          <t>https://www.indeed.com/viewjob?jk=aeda85e53ae1234a</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Cloud Platforms Engineer II</t>
+          <t>Senior Integration Developer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Amcor</t>
+          <t>AlayaCare</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Oshkosh, WI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Scala, Power BI, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a5bd8b939af9f70</t>
+          <t>https://www.indeed.com/viewjob?jk=2d6930b008143758</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Sr Systems Engineer</t>
+          <t>Cloud Platforms Engineer II</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>CEI Services</t>
+          <t>Amcor</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Fargo, ND, US USA</t>
+          <t>Oshkosh, WI, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Scala, Power BI, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f846bcd41f966d19</t>
+          <t>https://www.indeed.com/viewjob?jk=0a5bd8b939af9f70</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Sr Systems Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>MasTec Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Fargo, ND, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba06f08c24782d2d</t>
+          <t>https://www.indeed.com/viewjob?jk=75e319e5ec133537</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>DevOps with IoT focus</t>
+          <t>Sr Systems Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Intellimation LLC</t>
+          <t>CEI Services</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fargo, ND, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, IAM, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f64235fd5c4fac6</t>
+          <t>https://www.indeed.com/viewjob?jk=f846bcd41f966d19</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Sr Systems Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>MasTec Inc</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Fargo, ND, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=458f2e64ebd817f0</t>
+          <t>https://www.indeed.com/viewjob?jk=ba06f08c24782d2d</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>DevOps with IoT focus</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Intellimation LLC</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, IAM, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dc21140836b0e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=3f64235fd5c4fac6</t>
         </is>
       </c>
     </row>
@@ -4528,17 +4528,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Voya Financial</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Braintree, MA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, Kafka, Oracle, MySQL, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, S3, ECS, IAM, Azure, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f0f1071f3e2b14</t>
+          <t>https://www.indeed.com/viewjob?jk=facf27c6b3631798</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Backend Engineer II</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>HackerRank Careers</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Azure, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=facf27c6b3631798</t>
+          <t>https://www.indeed.com/viewjob?jk=d4979e4cfe40ed8d</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Backend Engineer II</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>HackerRank Careers</t>
+          <t>Voya Financial</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Braintree, MA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,17 +4616,17 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>Azure, Databricks, Spark, Kafka, Oracle, MySQL, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4979e4cfe40ed8d</t>
+          <t>https://www.indeed.com/viewjob?jk=06f0f1071f3e2b14</t>
         </is>
       </c>
     </row>
@@ -4668,17 +4668,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Software Engineer, Ads Infra - Serving and Foundation</t>
+          <t>Multi-Cloud Networking Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hive, Spark, Scala, Kafka, Data Modeling, ETL, Airflow, Git</t>
+          <t>AWS, IAM, RDS, Scala, Oracle, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e26cb9e516d559dc</t>
+          <t>https://www.indeed.com/viewjob?jk=7ff8e0f386ef907b</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>AI-ML Engineer 1</t>
+          <t>Senior Systems Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Universal Avionics Systems Corporation</t>
+          <t>Fueled</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Tucson, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Hadoop, Spark, Scala, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3e0f3955fde63ec</t>
+          <t>https://www.indeed.com/viewjob?jk=9642665184944e11</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>DMV IT Service LLC</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Richmond, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99e35b16ebbf3788</t>
+          <t>https://www.indeed.com/viewjob?jk=1de30f12b78fca01</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS)</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Capnexus</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Scala, DynamoDB, Data Modeling</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a7b11ddd229f030</t>
+          <t>https://www.indeed.com/viewjob?jk=b88b23e7d0b05c8f</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Multi-Cloud Networking Engineer</t>
+          <t>DevOps / Platform Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Vivacity Tech PBC</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Oracle, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ff8e0f386ef907b</t>
+          <t>https://www.indeed.com/viewjob?jk=ed1d3fe1d3532916</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Fueled</t>
+          <t>Illumio</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9642665184944e11</t>
+          <t>https://www.indeed.com/viewjob?jk=cad79b56c244d0fa</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>DMV IT Service LLC</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Richmond, TX, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1de30f12b78fca01</t>
+          <t>https://www.indeed.com/viewjob?jk=99e35b16ebbf3788</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Senior Data Engineer (AWS)</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Capnexus</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Scala, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88b23e7d0b05c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=5a7b11ddd229f030</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>DevOps / Platform Engineer</t>
+          <t>BI Engineer I (Hybrid)</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Vivacity Tech PBC</t>
+          <t>NEUMO</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Wayne, IN, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed1d3fe1d3532916</t>
+          <t>https://www.indeed.com/viewjob?jk=9d2a5858f9149296</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Software Engineer, Ads Infra - Serving and Foundation</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Illumio</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Hive, Spark, Scala, Kafka, Data Modeling, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cad79b56c244d0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=e26cb9e516d559dc</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>BI Engineer I (Hybrid)</t>
+          <t>AI-ML Engineer 1</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>NEUMO</t>
+          <t>Universal Avionics Systems Corporation</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Fort Wayne, IN, US USA</t>
+          <t>Tucson, AZ, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,34 +5036,34 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Hadoop, Spark, Scala, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d2a5858f9149296</t>
+          <t>https://www.indeed.com/viewjob?jk=e3e0f3955fde63ec</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>DevOps Engineer, Senior</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>isolved</t>
+          <t>Mister Car Wash</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Nixa, MO, US USA</t>
+          <t>Tucson, AZ, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Azure Cosmos DB, NoSQL, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d13a0d2142e0261</t>
+          <t>https://www.indeed.com/viewjob?jk=414fb4f6d3a8dcd9</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Pre-Sales Engineer (Data &amp; Analytics)</t>
+          <t>Software Engineer III (CJIS)</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>County of San Luis Obispo</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,34 +5106,34 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, GCP, SQL Server, MySQL, DynamoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c940790b1550a5b</t>
+          <t>https://www.indeed.com/viewjob?jk=2cda7602e4b5904c</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Warranty Data Analyst / Data Scientist</t>
+          <t>Software Engineer - DevSecOps (Associate, Experienced or Senior)</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e9bb1ef1dd7ba48</t>
+          <t>https://www.indeed.com/viewjob?jk=afe37944ff3c78ea</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Warranty Data Analyst / Data Scientist</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Gametime United</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,34 +5176,34 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ffd491a76c9fa66</t>
+          <t>https://www.indeed.com/viewjob?jk=24a25e68a1bd6d4f</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Headspace</t>
+          <t>isolved</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nixa, MO, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,34 +5211,34 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Azure Cosmos DB, NoSQL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbb7191dcfe18f53</t>
+          <t>https://www.indeed.com/viewjob?jk=3d13a0d2142e0261</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Senior</t>
+          <t>Pre-Sales Engineer (Data &amp; Analytics)</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Mister Car Wash</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Tucson, AZ, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=414fb4f6d3a8dcd9</t>
+          <t>https://www.indeed.com/viewjob?jk=3c940790b1550a5b</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Software Engineer III (CJIS)</t>
+          <t>Warranty Data Analyst / Data Scientist</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>County of San Luis Obispo</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, SQL Server, MySQL, DynamoDB, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cda7602e4b5904c</t>
+          <t>https://www.indeed.com/viewjob?jk=2e9bb1ef1dd7ba48</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Software Engineer - DevSecOps (Associate, Experienced or Senior)</t>
+          <t>Warranty Data Analyst / Data Scientist</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,19 +5326,19 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afe37944ff3c78ea</t>
+          <t>https://www.indeed.com/viewjob?jk=2ffd491a76c9fa66</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Gametime United</t>
+          <t>Headspace</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5351,34 +5351,34 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24a25e68a1bd6d4f</t>
+          <t>https://www.indeed.com/viewjob?jk=cbb7191dcfe18f53</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Trepp</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,34 +5386,34 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, Spark, Scala, Data Modeling, CI/CD, Git</t>
+          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d561d8c2375dd6b1</t>
+          <t>https://www.indeed.com/viewjob?jk=41f5f841b3bf67ad</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Data Engineer II - Information Technology</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Board of Governors of the Federal Reserve System</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,34 +5421,34 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, PostgreSQL, NoSQL</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, MS Excel, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b222160bc0c2b3e3</t>
+          <t>https://www.indeed.com/viewjob?jk=af37d87136cf35b5</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Technical Operations Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Codoxo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,34 +5456,34 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, NoSQL, ETL, Airflow, Bitbucket, CloudWatch</t>
+          <t>AWS, Glue, Lambda, Redshift, IAM, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e78a417a0f4410ac</t>
+          <t>https://www.indeed.com/viewjob?jk=a2f5cef76808163a</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Data Solution Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>SimilarWeb</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,34 +5491,34 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e039b4fcb467133</t>
+          <t>https://www.indeed.com/viewjob?jk=672dba9cce12de5f</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Senior Quality Platform Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Circle.so</t>
+          <t>Trepp</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,34 +5526,34 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
+          <t>AWS, Glue, EMR, Lambda, S3, Spark, Scala, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3752971091aeeac9</t>
+          <t>https://www.indeed.com/viewjob?jk=d561d8c2375dd6b1</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Infrastructure Engineer-Azure Data &amp; Analytics Engineer - State National</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Markel Corporation</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Bedford, TX, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, IAM, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,24 +5571,24 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2f5cef76808163a</t>
+          <t>https://www.indeed.com/viewjob?jk=94507e2995b9ee29</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Engineer II - Information Technology</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>Board of Governors of the Federal Reserve System</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,24 +5606,24 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=672dba9cce12de5f</t>
+          <t>https://www.indeed.com/viewjob?jk=b222160bc0c2b3e3</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer-Azure Data &amp; Analytics Engineer - State National</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Markel Corporation</t>
+          <t>nSCALE</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Bedford, TX, US USA</t>
+          <t>Barstow, TX, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,24 +5631,24 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94507e2995b9ee29</t>
+          <t>https://www.indeed.com/viewjob?jk=bc6c300d9777dc4b</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - Seattle, WA</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Barstow, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,24 +5676,24 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc6c300d9777dc4b</t>
+          <t>https://www.indeed.com/viewjob?jk=894fb5b066595659</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Data Engineer - Seattle, WA</t>
+          <t>Data Solution Engineer</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>nSCALE</t>
+          <t>SimilarWeb</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,17 +5701,17 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=894fb5b066595659</t>
+          <t>https://www.indeed.com/viewjob?jk=8e039b4fcb467133</t>
         </is>
       </c>
     </row>
@@ -5928,17 +5928,17 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Platform</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Ramp</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,34 +5946,34 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Terraform, Airflow</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45e12b77b9565199</t>
+          <t>https://www.indeed.com/viewjob?jk=5b0780a9fb0dbc39</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Ads Targeting Data Engineer, Ads Core</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5981,34 +5981,34 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Hive, Spark, Scala, Kafka, Data Modeling, ETL, Airflow, Python</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=185c1836bede91b1</t>
+          <t>https://www.indeed.com/viewjob?jk=cd2adeacdfffb183</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Quality Platform Engineer</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Circle.so</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6016,34 +6016,34 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cedfc80fbfee214</t>
+          <t>https://www.indeed.com/viewjob?jk=3752971091aeeac9</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Empirx Health</t>
+          <t>Ramp</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Blob Storage, GCP, Scala, Kafka, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c08697ee3f4bc0ba</t>
+          <t>https://www.indeed.com/viewjob?jk=45e12b77b9565199</t>
         </is>
       </c>
     </row>
@@ -6208,17 +6208,17 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Health-E Commerce</t>
+          <t>Empirx Health</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6226,34 +6226,34 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, Scala, Data Modeling, ETL, Azure DevOps, Python</t>
+          <t>AWS, Azure, Databricks, Blob Storage, GCP, Scala, Kafka, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56afd442294fd678</t>
+          <t>https://www.indeed.com/viewjob?jk=c08697ee3f4bc0ba</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Go Outdoors Payments</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Brandt Information Services, Inc.</t>
+          <t>Health-E Commerce</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6261,17 +6261,17 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, Scala, Data Modeling, ETL, Azure DevOps, Python</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f9736f5f852f3d</t>
+          <t>https://www.indeed.com/viewjob?jk=56afd442294fd678</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6306,24 +6306,24 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e66c9de7a81a7d66</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f9736f5f852f3d</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>Senior Software Engineer Go Outdoors Payments</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Fairlife, LLC</t>
+          <t>Brandt Information Services, Inc.</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6331,34 +6331,34 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Star Schema, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f203c334e20f61e9</t>
+          <t>https://www.indeed.com/viewjob?jk=e66c9de7a81a7d66</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Fairlife, LLC</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6366,34 +6366,34 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Star Schema, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd98e6c90182dad1</t>
+          <t>https://www.indeed.com/viewjob?jk=f203c334e20f61e9</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -6411,24 +6411,24 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1188cf2ae8e587af</t>
+          <t>https://www.indeed.com/viewjob?jk=185c1836bede91b1</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec0dc8f9f8c8d698</t>
+          <t>https://www.indeed.com/viewjob?jk=2cedfc80fbfee214</t>
         </is>
       </c>
     </row>
@@ -6523,17 +6523,17 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Java Compliance &amp; Governance Developer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -6551,7 +6551,77 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14d0312c67f01746</t>
+          <t>https://www.indeed.com/viewjob?jk=cd98e6c90182dad1</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Metropolis</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1188cf2ae8e587af</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Metropolis</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ec0dc8f9f8c8d698</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-23.xlsx
+++ b/results/job_matches_2026-04-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G177"/>
+  <dimension ref="A1:G182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,47 +608,47 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer/ Architecture (ADF &amp; Databricks)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>United Vein &amp; Vascular Centers</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=443e4c4dac7242b8</t>
+          <t>https://www.indeed.com/viewjob?jk=9a75bae8fe6b588f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Associate Data and AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -657,56 +657,56 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, S3, RDS, GCP, Hadoop, Spark, Scala</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=718af7ca01e94aee</t>
+          <t>https://www.indeed.com/viewjob?jk=be5d882b0154cb62</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Associate Data and AI Engineer</t>
+          <t>Senior Data Engineer/ Architecture (ADF &amp; Databricks)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>United Vein &amp; Vascular Centers</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, S3, RDS, GCP, Hadoop, Spark, Scala</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10c4f60d661f5f00</t>
+          <t>https://www.indeed.com/viewjob?jk=443e4c4dac7242b8</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f971eeb79a21180</t>
+          <t>https://www.indeed.com/viewjob?jk=718af7ca01e94aee</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfbf52f31ea2e787</t>
+          <t>https://www.indeed.com/viewjob?jk=10c4f60d661f5f00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Data and AI Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Climate First Bank</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala</t>
+          <t>AWS, EMR, Kinesis, Redshift, S3, RDS, GCP, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32602a30e2eae4db</t>
+          <t>https://www.indeed.com/viewjob?jk=6f971eeb79a21180</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Remote US</t>
+          <t>Associate Data and AI Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Smile Digital Health</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, GCP, Cloud Storage, Scala, Kafka</t>
+          <t>AWS, EMR, Kinesis, Redshift, S3, RDS, GCP, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,54 +846,54 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c0faea77dd1e82a</t>
+          <t>https://www.indeed.com/viewjob?jk=cfbf52f31ea2e787</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior DevOps Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>eClinical Solutions, LLC</t>
+          <t>Climate First Bank</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc6ebe88367f5090</t>
+          <t>https://www.indeed.com/viewjob?jk=32602a30e2eae4db</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (DataOps)</t>
+          <t>Senior Cloud Engineer - Remote US</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Black Canyon Consulting</t>
+          <t>Smile Digital Health</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Google Cloud Platform, GCP, Flume, Spark, Spark Streaming, Kafka</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, GCP, Cloud Storage, Scala, Kafka</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=298c77dba97763b9</t>
+          <t>https://www.indeed.com/viewjob?jk=3c0faea77dd1e82a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
+          <t>Senior DevOps Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>eClinical Solutions, LLC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0672f1d449c9d9e2</t>
+          <t>https://www.indeed.com/viewjob?jk=bc6ebe88367f5090</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
+          <t>Senior Platform Engineer (DataOps)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Black Canyon Consulting</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,17 +976,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Kinesis, RDS, Azure, Google Cloud Platform, GCP, Flume, Spark, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96a88c14093ccdaf</t>
+          <t>https://www.indeed.com/viewjob?jk=298c77dba97763b9</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f80cb5b125e7cc</t>
+          <t>https://www.indeed.com/viewjob?jk=0672f1d449c9d9e2</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca6623928abe2730</t>
+          <t>https://www.indeed.com/viewjob?jk=96a88c14093ccdaf</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46e364170a7ee29f</t>
+          <t>https://www.indeed.com/viewjob?jk=14f80cb5b125e7cc</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e67913bb063b4e1</t>
+          <t>https://www.indeed.com/viewjob?jk=ca6623928abe2730</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e6278fa86f66b6</t>
+          <t>https://www.indeed.com/viewjob?jk=46e364170a7ee29f</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a417258c27e6884b</t>
+          <t>https://www.indeed.com/viewjob?jk=0e67913bb063b4e1</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68ff6a6e54c5bb38</t>
+          <t>https://www.indeed.com/viewjob?jk=03e6278fa86f66b6</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b864420111578783</t>
+          <t>https://www.indeed.com/viewjob?jk=a417258c27e6884b</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90020927d62d9e32</t>
+          <t>https://www.indeed.com/viewjob?jk=68ff6a6e54c5bb38</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6445ef98b11402a</t>
+          <t>https://www.indeed.com/viewjob?jk=b864420111578783</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63c85699934dff6e</t>
+          <t>https://www.indeed.com/viewjob?jk=90020927d62d9e32</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26b24994302869a9</t>
+          <t>https://www.indeed.com/viewjob?jk=e6445ef98b11402a</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06b0116b71837d13</t>
+          <t>https://www.indeed.com/viewjob?jk=63c85699934dff6e</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8120526ad261b6a4</t>
+          <t>https://www.indeed.com/viewjob?jk=26b24994302869a9</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71be0c8c221ee567</t>
+          <t>https://www.indeed.com/viewjob?jk=06b0116b71837d13</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee059ac44d2277d6</t>
+          <t>https://www.indeed.com/viewjob?jk=8120526ad261b6a4</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af1a0c944d7d687c</t>
+          <t>https://www.indeed.com/viewjob?jk=71be0c8c221ee567</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a757acecac7ae896</t>
+          <t>https://www.indeed.com/viewjob?jk=ee059ac44d2277d6</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46cdcaa9c274907d</t>
+          <t>https://www.indeed.com/viewjob?jk=af1a0c944d7d687c</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c545200255ccd75</t>
+          <t>https://www.indeed.com/viewjob?jk=a757acecac7ae896</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99c6d56e1e9ecbd9</t>
+          <t>https://www.indeed.com/viewjob?jk=46cdcaa9c274907d</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec2268853b5e3d32</t>
+          <t>https://www.indeed.com/viewjob?jk=0c545200255ccd75</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc317ad96269ff6c</t>
+          <t>https://www.indeed.com/viewjob?jk=99c6d56e1e9ecbd9</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c59791ffa8037e0</t>
+          <t>https://www.indeed.com/viewjob?jk=ec2268853b5e3d32</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93c00120a22fd95f</t>
+          <t>https://www.indeed.com/viewjob?jk=cc317ad96269ff6c</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5fd76a0505c1f45</t>
+          <t>https://www.indeed.com/viewjob?jk=2c59791ffa8037e0</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52bda57a7eae91d3</t>
+          <t>https://www.indeed.com/viewjob?jk=93c00120a22fd95f</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d79924b7c683266</t>
+          <t>https://www.indeed.com/viewjob?jk=e5fd76a0505c1f45</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18b51a17582c12e7</t>
+          <t>https://www.indeed.com/viewjob?jk=52bda57a7eae91d3</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c239cf58c8fa1c71</t>
+          <t>https://www.indeed.com/viewjob?jk=8d79924b7c683266</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5a42ec359480e0d</t>
+          <t>https://www.indeed.com/viewjob?jk=18b51a17582c12e7</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ed6224d65d164cb</t>
+          <t>https://www.indeed.com/viewjob?jk=c239cf58c8fa1c71</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffcd6c03d59f6052</t>
+          <t>https://www.indeed.com/viewjob?jk=d5a42ec359480e0d</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddc6dd123946c0df</t>
+          <t>https://www.indeed.com/viewjob?jk=5ed6224d65d164cb</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b026195b5394344</t>
+          <t>https://www.indeed.com/viewjob?jk=ffcd6c03d59f6052</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ffe2cd40b6dd0e7</t>
+          <t>https://www.indeed.com/viewjob?jk=ddc6dd123946c0df</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2581b6e435257226</t>
+          <t>https://www.indeed.com/viewjob?jk=2b026195b5394344</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de24f7419929c1bf</t>
+          <t>https://www.indeed.com/viewjob?jk=9ffe2cd40b6dd0e7</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5380c72e36e9ef3d</t>
+          <t>https://www.indeed.com/viewjob?jk=2581b6e435257226</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43d4c68e7e9e2fef</t>
+          <t>https://www.indeed.com/viewjob?jk=de24f7419929c1bf</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a8557481e61c905</t>
+          <t>https://www.indeed.com/viewjob?jk=5380c72e36e9ef3d</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af8a69205565050f</t>
+          <t>https://www.indeed.com/viewjob?jk=43d4c68e7e9e2fef</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfedec5986433f19</t>
+          <t>https://www.indeed.com/viewjob?jk=7a8557481e61c905</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dadc73e392f990d3</t>
+          <t>https://www.indeed.com/viewjob?jk=af8a69205565050f</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df6f8697322180c6</t>
+          <t>https://www.indeed.com/viewjob?jk=dfedec5986433f19</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b407a88f3a1f87f8</t>
+          <t>https://www.indeed.com/viewjob?jk=dadc73e392f990d3</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce6e6d7e4f41a3e8</t>
+          <t>https://www.indeed.com/viewjob?jk=df6f8697322180c6</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1662c7096eaa5c34</t>
+          <t>https://www.indeed.com/viewjob?jk=b407a88f3a1f87f8</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b54c062fe208581</t>
+          <t>https://www.indeed.com/viewjob?jk=ce6e6d7e4f41a3e8</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ca77008309e43be</t>
+          <t>https://www.indeed.com/viewjob?jk=1662c7096eaa5c34</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Azure, Databricks, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,59 +2771,59 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ede735cbdf2b63e0</t>
+          <t>https://www.indeed.com/viewjob?jk=9b54c062fe208581</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Axle</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Frederick, MD, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=353f08220bc3960e</t>
+          <t>https://www.indeed.com/viewjob?jk=3ca77008309e43be</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer | The Points Guy</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Red Ventures</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, Glue, Redshift, S3, Azure, Databricks, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec2d5686f500c7c1</t>
+          <t>https://www.indeed.com/viewjob?jk=ede735cbdf2b63e0</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer | The Points Guy</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Red Ventures</t>
+          <t>Axle</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Frederick, MD, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac5793781d1c8a3c</t>
+          <t>https://www.indeed.com/viewjob?jk=353f08220bc3960e</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer | The Points Guy</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Red Ventures</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Data Modeling, ETL</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3a17b22e5142267</t>
+          <t>https://www.indeed.com/viewjob?jk=ec2d5686f500c7c1</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (Data Modeling &amp; BI)</t>
+          <t>Data Engineer | The Points Guy</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Keeper Security</t>
+          <t>Red Ventures</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b319560288703a69</t>
+          <t>https://www.indeed.com/viewjob?jk=ac5793781d1c8a3c</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CA IAM Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,104 +2971,104 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Redshift, IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Snowflake, Tableau, Tableau Server</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a8d75516142a508</t>
+          <t>https://www.indeed.com/viewjob?jk=e3a17b22e5142267</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Engineering</t>
+          <t>Senior Analytics Engineer (Data Modeling &amp; BI)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Verse</t>
+          <t>Keeper Security</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, S3, RDS, Databricks, GCP, BigQuery, Hadoop, Hive, HBase</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2169de43fedb76d3</t>
+          <t>https://www.indeed.com/viewjob?jk=b319560288703a69</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>CA IAM Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SambaNova Systems</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Redshift, IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Snowflake, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=564c2131c7a47b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=1a8d75516142a508</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML</t>
+          <t>Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Verse</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>Kinesis, Redshift, S3, RDS, Databricks, GCP, BigQuery, Hadoop, Hive, HBase</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e288d00b33f48efe</t>
+          <t>https://www.indeed.com/viewjob?jk=2169de43fedb76d3</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sr. Platform Engineering</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>archer</t>
+          <t>SambaNova Systems</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e910893e7900f872</t>
+          <t>https://www.indeed.com/viewjob?jk=564c2131c7a47b4e</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Computer Programmer</t>
+          <t>Software Engineer III - AI/ML</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Axle</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,42 +3146,42 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3f8d985ccebf8fe</t>
+          <t>https://www.indeed.com/viewjob?jk=e288d00b33f48efe</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer (AIA)</t>
+          <t>Sr. Platform Engineering</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>archer</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,42 +3191,42 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=422b5002f3c92e96</t>
+          <t>https://www.indeed.com/viewjob?jk=e910893e7900f872</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer (AIA)</t>
+          <t>Computer Programmer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Axle</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ca947b911b13d47</t>
+          <t>https://www.indeed.com/viewjob?jk=b3f8d985ccebf8fe</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2762492ad7551efe</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f49ea5746dd899</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer (AIA)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb9acfcb385fd29f</t>
+          <t>https://www.indeed.com/viewjob?jk=422b5002f3c92e96</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer, Analytics &amp; Machine Learning Enablement</t>
+          <t>Data Engineer (AIA)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Keeper Security</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b569d0296983d6a1</t>
+          <t>https://www.indeed.com/viewjob?jk=4ca947b911b13d47</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Data Engineer (AIA)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbdcf2158c6b2d0d</t>
+          <t>https://www.indeed.com/viewjob?jk=2762492ad7551efe</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a924e0d6d13cba9</t>
+          <t>https://www.indeed.com/viewjob?jk=cb9acfcb385fd29f</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
+          <t>Data Engineer, Analytics &amp; Machine Learning Enablement</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Keeper Security</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,174 +3426,174 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5239f6ce7d60780b</t>
+          <t>https://www.indeed.com/viewjob?jk=b569d0296983d6a1</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SIGNITIVES</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccbfb275c784c26b</t>
+          <t>https://www.indeed.com/viewjob?jk=fbdcf2158c6b2d0d</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Cloud and Things</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Scala, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b67c42af6bdf7f4d</t>
+          <t>https://www.indeed.com/viewjob?jk=8dcbb0b99721efea</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ed12a9528f47173</t>
+          <t>https://www.indeed.com/viewjob?jk=6a924e0d6d13cba9</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Data Engineer | The Points Guy</t>
+          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Red Ventures</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa160af377aea6a2</t>
+          <t>https://www.indeed.com/viewjob?jk=5239f6ce7d60780b</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Specialist Software Engineering</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>SIGNITIVES</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, API Gateway, ECS, Event Hubs, Zookeeper, Kafka, CI/CD, Jenkins</t>
+          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f8131b391d620e</t>
+          <t>https://www.indeed.com/viewjob?jk=ccbfb275c784c26b</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, Kafka, Oracle, DynamoDB, NoSQL</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bd882abe2f239e8</t>
+          <t>https://www.indeed.com/viewjob?jk=b67c42af6bdf7f4d</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Python Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>N-iX</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Cloud Storage, Vertex AI, Scala, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=365bb0b9ec3ce321</t>
+          <t>https://www.indeed.com/viewjob?jk=5ed12a9528f47173</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Development Engineer - Credential API</t>
+          <t>Senior Data Engineer | The Points Guy</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>Red Ventures</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Lambda, S3, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4c302fda1f6ae84</t>
+          <t>https://www.indeed.com/viewjob?jk=aa160af377aea6a2</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Specialist Software Engineering</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Focus Financial Partners</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,42 +3741,42 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Dask, Snowflake</t>
+          <t>AWS, Kinesis, S3, API Gateway, ECS, Event Hubs, Zookeeper, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc6ec804cfff5642</t>
+          <t>https://www.indeed.com/viewjob?jk=66f8131b391d620e</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Bloom Growth Partners</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, Kafka, Oracle, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,129 +3786,129 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec3ffe3d2951f742</t>
+          <t>https://www.indeed.com/viewjob?jk=6bd882abe2f239e8</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer II</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>Focus Financial Partners</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Dask, Snowflake</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af6a74b61fd0779</t>
+          <t>https://www.indeed.com/viewjob?jk=dc6ec804cfff5642</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Full-Stack Python Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Gates Foundation</t>
+          <t>N-iX</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Cloud Storage, Vertex AI, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0e09f867e58f64d</t>
+          <t>https://www.indeed.com/viewjob?jk=365bb0b9ec3ce321</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Azure Engineer</t>
+          <t>Software Development Engineer - Credential API</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Witherite Law Group</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d4c16398c048d9f</t>
+          <t>https://www.indeed.com/viewjob?jk=a4c302fda1f6ae84</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Contributory Network</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>Bloom Growth Partners</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, ECS, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a1c158c64508404</t>
+          <t>https://www.indeed.com/viewjob?jk=ec3ffe3d2951f742</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE) - AI Platform &amp; Cloud</t>
+          <t>Senior DevOps Engineer II</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Spark, Kafka, Snowflake, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67434a699408c40f</t>
+          <t>https://www.indeed.com/viewjob?jk=3af6a74b61fd0779</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Health-E Commerce</t>
+          <t>Gates Foundation</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, ELT</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b75ba4eaa7e2f72</t>
+          <t>https://www.indeed.com/viewjob?jk=d0e09f867e58f64d</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure, Engineer II</t>
+          <t>Azure Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Trinity Logistics</t>
+          <t>Witherite Law Group</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Seaford, DE, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e66613c1418d016b</t>
+          <t>https://www.indeed.com/viewjob?jk=2d4c16398c048d9f</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>Senior Software Engineer - Contributory Network</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, MySQL, NoSQL, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, ECS, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f84e68d5415404a</t>
+          <t>https://www.indeed.com/viewjob?jk=9a1c158c64508404</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Site Reliability Engineer (SRE) - AI Platform &amp; Cloud</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, Scala, Data Modeling, MLOps, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, Spark, Kafka, Snowflake, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eec716db1d652f56</t>
+          <t>https://www.indeed.com/viewjob?jk=67434a699408c40f</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Kitsap Credit Union</t>
+          <t>Health-E Commerce</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Bremerton, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, SonarQube</t>
+          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=150b9708ae649096</t>
+          <t>https://www.indeed.com/viewjob?jk=2b75ba4eaa7e2f72</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back-End (Java &amp; Spring Boot)</t>
+          <t>Cloud Infrastructure, Engineer II</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>PlanOmatic HQ</t>
+          <t>Trinity Logistics</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Seaford, DE, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4197b722f1b29f84</t>
+          <t>https://www.indeed.com/viewjob?jk=e66613c1418d016b</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>AI Engineer - Insurance Domain - HYBRID</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Warren, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Google Cloud Platform, Scala, MySQL, NoSQL, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeda85e53ae1234a</t>
+          <t>https://www.indeed.com/viewjob?jk=5f84e68d5415404a</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Integration Developer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>AlayaCare</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,77 +4231,77 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, Scala, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d6930b008143758</t>
+          <t>https://www.indeed.com/viewjob?jk=eec716db1d652f56</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Cloud Platforms Engineer II</t>
+          <t>AI Engineer - Insurance Domain - HYBRID</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Amcor</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Oshkosh, WI, US USA</t>
+          <t>Warren, NJ, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Scala, Power BI, CI/CD, Jenkins, Terraform</t>
+          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a5bd8b939af9f70</t>
+          <t>https://www.indeed.com/viewjob?jk=aeda85e53ae1234a</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Kitsap Credit Union</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Bremerton, WA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Spark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Event Hubs, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, SonarQube</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,94 +4311,94 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75e319e5ec133537</t>
+          <t>https://www.indeed.com/viewjob?jk=150b9708ae649096</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Sr Systems Engineer</t>
+          <t>Senior Software Engineer, Back-End (Java &amp; Spring Boot)</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>CEI Services</t>
+          <t>PlanOmatic HQ</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Fargo, ND, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f846bcd41f966d19</t>
+          <t>https://www.indeed.com/viewjob?jk=4197b722f1b29f84</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Sr Systems Engineer</t>
+          <t>Senior Integration Developer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>MasTec Inc</t>
+          <t>AlayaCare</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Fargo, ND, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba06f08c24782d2d</t>
+          <t>https://www.indeed.com/viewjob?jk=2d6930b008143758</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>DevOps with IoT focus</t>
+          <t>Cloud Platforms Engineer II</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Intellimation LLC</t>
+          <t>Amcor</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oshkosh, WI, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, IAM, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Scala, Power BI, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f64235fd5c4fac6</t>
+          <t>https://www.indeed.com/viewjob?jk=0a5bd8b939af9f70</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>RapidSOS</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, IAM, Scala, Kafka, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c059e9218f7e23d</t>
+          <t>https://www.indeed.com/viewjob?jk=75e319e5ec133537</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Sr Systems Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>RapidSOS</t>
+          <t>CEI Services</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fargo, ND, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, IAM, Scala, Kafka, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3986c9d7e69f169</t>
+          <t>https://www.indeed.com/viewjob?jk=f846bcd41f966d19</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Gen AI Platform &amp; Deployment Engineer</t>
+          <t>Sr Systems Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>MasTec Inc</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Fargo, ND, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ad5e385a9b79a74</t>
+          <t>https://www.indeed.com/viewjob?jk=ba06f08c24782d2d</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>DevOps with IoT focus</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Intellimation LLC</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Azure, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, IAM, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=facf27c6b3631798</t>
+          <t>https://www.indeed.com/viewjob?jk=3f64235fd5c4fac6</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Backend Engineer II</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>HackerRank Careers</t>
+          <t>RapidSOS</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, SQS, SNS, ECS, IAM, Scala, Kafka, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4979e4cfe40ed8d</t>
+          <t>https://www.indeed.com/viewjob?jk=6c059e9218f7e23d</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Voya Financial</t>
+          <t>RapidSOS</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Braintree, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, Kafka, Oracle, MySQL, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, SQS, SNS, ECS, IAM, Scala, Kafka, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f0f1071f3e2b14</t>
+          <t>https://www.indeed.com/viewjob?jk=d3986c9d7e69f169</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
+          <t>Gen AI Platform &amp; Deployment Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,42 +4651,42 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d356cba46c60202</t>
+          <t>https://www.indeed.com/viewjob?jk=7ad5e385a9b79a74</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Multi-Cloud Networking Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Voya Financial</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Braintree, MA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Oracle, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
+          <t>Azure, Databricks, Spark, Kafka, Oracle, MySQL, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,32 +4696,32 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ff8e0f386ef907b</t>
+          <t>https://www.indeed.com/viewjob?jk=06f0f1071f3e2b14</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Fueled</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, S3, ECS, IAM, Azure, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,67 +4731,67 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9642665184944e11</t>
+          <t>https://www.indeed.com/viewjob?jk=facf27c6b3631798</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Backend Engineer II</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>HackerRank Careers</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1de30f12b78fca01</t>
+          <t>https://www.indeed.com/viewjob?jk=d4979e4cfe40ed8d</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88b23e7d0b05c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=3d356cba46c60202</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>DevOps / Platform Engineer</t>
+          <t>Multi-Cloud Networking Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Vivacity Tech PBC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Scala, Oracle, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed1d3fe1d3532916</t>
+          <t>https://www.indeed.com/viewjob?jk=7ff8e0f386ef907b</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Senior Systems Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Illumio</t>
+          <t>Fueled</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cad79b56c244d0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=9642665184944e11</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>DMV IT Service LLC</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Richmond, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99e35b16ebbf3788</t>
+          <t>https://www.indeed.com/viewjob?jk=1de30f12b78fca01</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS)</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Capnexus</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Scala, DynamoDB, Data Modeling</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a7b11ddd229f030</t>
+          <t>https://www.indeed.com/viewjob?jk=b88b23e7d0b05c8f</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>BI Engineer I (Hybrid)</t>
+          <t>DevOps / Platform Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>NEUMO</t>
+          <t>Vivacity Tech PBC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Fort Wayne, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d2a5858f9149296</t>
+          <t>https://www.indeed.com/viewjob?jk=ed1d3fe1d3532916</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Software Engineer, Ads Infra - Serving and Foundation</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Illumio</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hive, Spark, Scala, Kafka, Data Modeling, ETL, Airflow, Git</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e26cb9e516d559dc</t>
+          <t>https://www.indeed.com/viewjob?jk=cad79b56c244d0fa</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>AI-ML Engineer 1</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Universal Avionics Systems Corporation</t>
+          <t>DMV IT Service LLC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Tucson, AZ, US USA</t>
+          <t>Richmond, TX, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Hadoop, Spark, Scala, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3e0f3955fde63ec</t>
+          <t>https://www.indeed.com/viewjob?jk=99e35b16ebbf3788</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Senior</t>
+          <t>Senior Data Engineer (AWS)</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Mister Car Wash</t>
+          <t>Capnexus</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Tucson, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,34 +5071,34 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Scala, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=414fb4f6d3a8dcd9</t>
+          <t>https://www.indeed.com/viewjob?jk=5a7b11ddd229f030</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Software Engineer III (CJIS)</t>
+          <t>BI Engineer I (Hybrid)</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>County of San Luis Obispo</t>
+          <t>NEUMO</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Fort Wayne, IN, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,34 +5106,34 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, SQL Server, MySQL, DynamoDB, NoSQL, Data Modeling</t>
+          <t>RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cda7602e4b5904c</t>
+          <t>https://www.indeed.com/viewjob?jk=9d2a5858f9149296</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Software Engineer - DevSecOps (Associate, Experienced or Senior)</t>
+          <t>Software Engineer, Ads Infra - Serving and Foundation</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Hive, Spark, Scala, Kafka, Data Modeling, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afe37944ff3c78ea</t>
+          <t>https://www.indeed.com/viewjob?jk=e26cb9e516d559dc</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>AI-ML Engineer 1</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Gametime United</t>
+          <t>Universal Avionics Systems Corporation</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tucson, AZ, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,17 +5176,17 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Hadoop, Spark, Scala, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24a25e68a1bd6d4f</t>
+          <t>https://www.indeed.com/viewjob?jk=e3e0f3955fde63ec</t>
         </is>
       </c>
     </row>
@@ -5368,25 +5368,25 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>DevOps Engineer, Senior</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Mister Car Wash</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tucson, AZ, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,67 +5396,67 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f5f841b3bf67ad</t>
+          <t>https://www.indeed.com/viewjob?jk=414fb4f6d3a8dcd9</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Software Engineer III (CJIS)</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>County of San Luis Obispo</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, MS Excel, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, GCP, SQL Server, MySQL, DynamoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af37d87136cf35b5</t>
+          <t>https://www.indeed.com/viewjob?jk=2cda7602e4b5904c</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Software Engineer - DevSecOps (Associate, Experienced or Senior)</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, IAM, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,59 +5466,59 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2f5cef76808163a</t>
+          <t>https://www.indeed.com/viewjob?jk=afe37944ff3c78ea</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>Gametime United</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=672dba9cce12de5f</t>
+          <t>https://www.indeed.com/viewjob?jk=24a25e68a1bd6d4f</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Trepp</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,34 +5526,34 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, Spark, Scala, Data Modeling, CI/CD, Git</t>
+          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d561d8c2375dd6b1</t>
+          <t>https://www.indeed.com/viewjob?jk=41f5f841b3bf67ad</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer-Azure Data &amp; Analytics Engineer - State National</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Markel Corporation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Bedford, TX, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,34 +5561,34 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, MS Excel, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94507e2995b9ee29</t>
+          <t>https://www.indeed.com/viewjob?jk=af37d87136cf35b5</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Data Engineer II - Information Technology</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Board of Governors of the Federal Reserve System</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, PostgreSQL, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Impala, Spark, Scala</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,24 +5606,24 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b222160bc0c2b3e3</t>
+          <t>https://www.indeed.com/viewjob?jk=f28a43a00c1a7844</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>nSCALE</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Barstow, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,34 +5631,34 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
+          <t>AWS, Glue, Lambda, Redshift, IAM, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc6c300d9777dc4b</t>
+          <t>https://www.indeed.com/viewjob?jk=a2f5cef76808163a</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Data Engineer - Seattle, WA</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>nSCALE</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,29 +5666,29 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=894fb5b066595659</t>
+          <t>https://www.indeed.com/viewjob?jk=672dba9cce12de5f</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Data Solution Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>SimilarWeb</t>
+          <t>Trepp</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5701,34 +5701,34 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, S3, Spark, Scala, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e039b4fcb467133</t>
+          <t>https://www.indeed.com/viewjob?jk=d561d8c2375dd6b1</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Engineer, Developer Platform (Cloud Apps)</t>
+          <t>Senior Infrastructure Engineer-Azure Data &amp; Analytics Engineer - State National</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Motional</t>
+          <t>Markel Corporation</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Bedford, TX, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,34 +5736,34 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, NoSQL, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a10c8d4659b2bc91</t>
+          <t>https://www.indeed.com/viewjob?jk=94507e2995b9ee29</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Engineer II - Information Technology</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Envoy global</t>
+          <t>Board of Governors of the Federal Reserve System</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,34 +5771,34 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, Scala, SQL Server, Splunk, CI/CD, Azure DevOps, Terraform, AKS, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d81e4212199a1a8</t>
+          <t>https://www.indeed.com/viewjob?jk=b222160bc0c2b3e3</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Envoy global</t>
+          <t>nSCALE</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Barstow, TX, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,34 +5806,34 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, Scala, SQL Server, Splunk, CI/CD, Azure DevOps, Terraform, AKS, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d276b3164ac33893</t>
+          <t>https://www.indeed.com/viewjob?jk=bc6c300d9777dc4b</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>SQL Engineer</t>
+          <t>Data Engineer - Seattle, WA</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Mechanical Licensing Collective</t>
+          <t>nSCALE</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,34 +5841,34 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, Athena, RDS, Scala, Oracle, PostgreSQL, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3db429a534810fa</t>
+          <t>https://www.indeed.com/viewjob?jk=894fb5b066595659</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Solution Engineer</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Alpaca</t>
+          <t>SimilarWeb</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,34 +5876,34 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Spark, Scala, ETL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cf5cd1df0f54fe6</t>
+          <t>https://www.indeed.com/viewjob?jk=8e039b4fcb467133</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
+          <t>Engineer, Developer Platform (Cloud Apps)</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>Motional</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,34 +5911,34 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, NoSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ae2d7c352959fb2</t>
+          <t>https://www.indeed.com/viewjob?jk=a10c8d4659b2bc91</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Envoy global</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,34 +5946,34 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>Azure, Blob Storage, Scala, SQL Server, Splunk, CI/CD, Azure DevOps, Terraform, AKS, Git</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b0780a9fb0dbc39</t>
+          <t>https://www.indeed.com/viewjob?jk=3d81e4212199a1a8</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Ads Targeting Data Engineer, Ads Core</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Envoy global</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5981,34 +5981,34 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hive, Spark, Scala, Kafka, Data Modeling, ETL, Airflow, Python</t>
+          <t>Azure, Blob Storage, Scala, SQL Server, Splunk, CI/CD, Azure DevOps, Terraform, AKS, Git</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd2adeacdfffb183</t>
+          <t>https://www.indeed.com/viewjob?jk=d276b3164ac33893</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Senior Quality Platform Engineer</t>
+          <t>SQL Engineer</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Circle.so</t>
+          <t>Mechanical Licensing Collective</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6016,34 +6016,34 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
+          <t>AWS, Athena, RDS, Scala, Oracle, PostgreSQL, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3752971091aeeac9</t>
+          <t>https://www.indeed.com/viewjob?jk=e3db429a534810fa</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Platform</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Ramp</t>
+          <t>Alpaca</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6051,34 +6051,34 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Terraform, Airflow</t>
+          <t>AWS, RDS, GCP, Spark, Scala, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45e12b77b9565199</t>
+          <t>https://www.indeed.com/viewjob?jk=8cf5cd1df0f54fe6</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6086,34 +6086,34 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab7793f0a792b417</t>
+          <t>https://www.indeed.com/viewjob?jk=2ae2d7c352959fb2</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6121,34 +6121,34 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=650677ad14cf645f</t>
+          <t>https://www.indeed.com/viewjob?jk=5b0780a9fb0dbc39</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Ads Targeting Data Engineer, Ads Core</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6156,34 +6156,34 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Azure, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, RDS, Hive, Spark, Scala, Kafka, Data Modeling, ETL, Airflow, Python</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff779f0dce63ada3</t>
+          <t>https://www.indeed.com/viewjob?jk=cd2adeacdfffb183</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Senior Quality Platform Engineer</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Circle.so</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6191,34 +6191,34 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Azure, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb55e9f7a6dc231</t>
+          <t>https://www.indeed.com/viewjob?jk=3752971091aeeac9</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Empirx Health</t>
+          <t>Ramp</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Blob Storage, GCP, Scala, Kafka, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -6236,24 +6236,24 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c08697ee3f4bc0ba</t>
+          <t>https://www.indeed.com/viewjob?jk=45e12b77b9565199</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Health-E Commerce</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6261,34 +6261,34 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, Scala, Data Modeling, ETL, Azure DevOps, Python</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56afd442294fd678</t>
+          <t>https://www.indeed.com/viewjob?jk=185c1836bede91b1</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Go Outdoors Payments</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Brandt Information Services, Inc.</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6296,34 +6296,34 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f9736f5f852f3d</t>
+          <t>https://www.indeed.com/viewjob?jk=2cedfc80fbfee214</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Go Outdoors Payments</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Brandt Information Services, Inc.</t>
+          <t>Empirx Health</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6331,34 +6331,34 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Azure, Databricks, Blob Storage, GCP, Scala, Kafka, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e66c9de7a81a7d66</t>
+          <t>https://www.indeed.com/viewjob?jk=c08697ee3f4bc0ba</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Fairlife, LLC</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6366,34 +6366,34 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Star Schema, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f203c334e20f61e9</t>
+          <t>https://www.indeed.com/viewjob?jk=ab7793f0a792b417</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -6411,24 +6411,24 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=185c1836bede91b1</t>
+          <t>https://www.indeed.com/viewjob?jk=650677ad14cf645f</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>Azure, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -6446,14 +6446,14 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cedfc80fbfee214</t>
+          <t>https://www.indeed.com/viewjob?jk=ff779f0dce63ada3</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Java Compliance &amp; Governance Developer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
+          <t>Azure, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -6481,24 +6481,24 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=243990c269c56673</t>
+          <t>https://www.indeed.com/viewjob?jk=9eb55e9f7a6dc231</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Java Compliance &amp; Governance Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Health-E Commerce</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6506,34 +6506,34 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
+          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, Scala, Data Modeling, ETL, Azure DevOps, Python</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9d53f3c6ff20349</t>
+          <t>https://www.indeed.com/viewjob?jk=56afd442294fd678</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Software Engineer Go Outdoors Payments</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Brandt Information Services, Inc.</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6541,34 +6541,34 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd98e6c90182dad1</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f9736f5f852f3d</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Software Engineer Go Outdoors Payments</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Brandt Information Services, Inc.</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6576,34 +6576,34 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1188cf2ae8e587af</t>
+          <t>https://www.indeed.com/viewjob?jk=e66c9de7a81a7d66</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Fairlife, LLC</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6611,17 +6611,192 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Spark, Scala, Star Schema, ELT, Power BI, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f203c334e20f61e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Metropolis</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
           <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
         </is>
       </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cd98e6c90182dad1</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Metropolis</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1188cf2ae8e587af</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Metropolis</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ec0dc8f9f8c8d698</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Java Compliance &amp; Governance Developer</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>NC, US USA</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=243990c269c56673</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Java Compliance &amp; Governance Developer</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>NC, US USA</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e9d53f3c6ff20349</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-23.xlsx
+++ b/results/job_matches_2026-04-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G182"/>
+  <dimension ref="A1:G180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Cloud &amp; Data Platforms)</t>
+          <t>AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Customized Energy Solutions</t>
+          <t>Glacier Analytics LLC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,34 +521,34 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Unity Catalog, Spark, Scala</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14e471621c544ca6</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f2c6e67bc23530</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AWS DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Glacier Analytics LLC</t>
+          <t>DOW</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,42 +566,42 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f2c6e67bc23530</t>
+          <t>https://www.indeed.com/viewjob?jk=0e6f52d2577111f6</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DOW</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e6f52d2577111f6</t>
+          <t>https://www.indeed.com/viewjob?jk=9a75bae8fe6b588f</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,77 +636,77 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a75bae8fe6b588f</t>
+          <t>https://www.indeed.com/viewjob?jk=be5d882b0154cb62</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer/ Architecture (ADF &amp; Databricks)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>United Vein &amp; Vascular Centers</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be5d882b0154cb62</t>
+          <t>https://www.indeed.com/viewjob?jk=443e4c4dac7242b8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer/ Architecture (ADF &amp; Databricks)</t>
+          <t>Associate Data and AI Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>United Vein &amp; Vascular Centers</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala</t>
+          <t>AWS, EMR, Kinesis, Redshift, S3, RDS, GCP, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=443e4c4dac7242b8</t>
+          <t>https://www.indeed.com/viewjob?jk=718af7ca01e94aee</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=718af7ca01e94aee</t>
+          <t>https://www.indeed.com/viewjob?jk=10c4f60d661f5f00</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10c4f60d661f5f00</t>
+          <t>https://www.indeed.com/viewjob?jk=6f971eeb79a21180</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f971eeb79a21180</t>
+          <t>https://www.indeed.com/viewjob?jk=cfbf52f31ea2e787</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Associate Data and AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Climate First Bank</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, S3, RDS, GCP, Hadoop, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfbf52f31ea2e787</t>
+          <t>https://www.indeed.com/viewjob?jk=32602a30e2eae4db</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Engineer - Remote US</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Climate First Bank</t>
+          <t>Smile Digital Health</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, GCP, Cloud Storage, Scala, Kafka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,19 +881,19 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32602a30e2eae4db</t>
+          <t>https://www.indeed.com/viewjob?jk=3c0faea77dd1e82a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Remote US</t>
+          <t>Senior DevOps Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Smile Digital Health</t>
+          <t>eClinical Solutions, LLC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -906,29 +906,29 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, GCP, Cloud Storage, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c0faea77dd1e82a</t>
+          <t>https://www.indeed.com/viewjob?jk=bc6ebe88367f5090</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior DevOps Software Engineer</t>
+          <t>Senior Platform Engineer (DataOps)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>eClinical Solutions, LLC</t>
+          <t>Black Canyon Consulting</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, MLOps, MLflow</t>
+          <t>AWS, Kinesis, RDS, Azure, Google Cloud Platform, GCP, Flume, Spark, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc6ebe88367f5090</t>
+          <t>https://www.indeed.com/viewjob?jk=298c77dba97763b9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (DataOps)</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Black Canyon Consulting</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,17 +976,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Google Cloud Platform, GCP, Flume, Spark, Spark Streaming, Kafka</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=298c77dba97763b9</t>
+          <t>https://www.indeed.com/viewjob?jk=0672f1d449c9d9e2</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0672f1d449c9d9e2</t>
+          <t>https://www.indeed.com/viewjob?jk=96a88c14093ccdaf</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96a88c14093ccdaf</t>
+          <t>https://www.indeed.com/viewjob?jk=14f80cb5b125e7cc</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f80cb5b125e7cc</t>
+          <t>https://www.indeed.com/viewjob?jk=ca6623928abe2730</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca6623928abe2730</t>
+          <t>https://www.indeed.com/viewjob?jk=46e364170a7ee29f</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46e364170a7ee29f</t>
+          <t>https://www.indeed.com/viewjob?jk=0e67913bb063b4e1</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e67913bb063b4e1</t>
+          <t>https://www.indeed.com/viewjob?jk=03e6278fa86f66b6</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e6278fa86f66b6</t>
+          <t>https://www.indeed.com/viewjob?jk=a417258c27e6884b</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a417258c27e6884b</t>
+          <t>https://www.indeed.com/viewjob?jk=68ff6a6e54c5bb38</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68ff6a6e54c5bb38</t>
+          <t>https://www.indeed.com/viewjob?jk=b864420111578783</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b864420111578783</t>
+          <t>https://www.indeed.com/viewjob?jk=90020927d62d9e32</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90020927d62d9e32</t>
+          <t>https://www.indeed.com/viewjob?jk=e6445ef98b11402a</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6445ef98b11402a</t>
+          <t>https://www.indeed.com/viewjob?jk=63c85699934dff6e</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63c85699934dff6e</t>
+          <t>https://www.indeed.com/viewjob?jk=26b24994302869a9</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26b24994302869a9</t>
+          <t>https://www.indeed.com/viewjob?jk=06b0116b71837d13</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06b0116b71837d13</t>
+          <t>https://www.indeed.com/viewjob?jk=8120526ad261b6a4</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8120526ad261b6a4</t>
+          <t>https://www.indeed.com/viewjob?jk=71be0c8c221ee567</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71be0c8c221ee567</t>
+          <t>https://www.indeed.com/viewjob?jk=ee059ac44d2277d6</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee059ac44d2277d6</t>
+          <t>https://www.indeed.com/viewjob?jk=af1a0c944d7d687c</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af1a0c944d7d687c</t>
+          <t>https://www.indeed.com/viewjob?jk=a757acecac7ae896</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a757acecac7ae896</t>
+          <t>https://www.indeed.com/viewjob?jk=46cdcaa9c274907d</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46cdcaa9c274907d</t>
+          <t>https://www.indeed.com/viewjob?jk=0c545200255ccd75</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c545200255ccd75</t>
+          <t>https://www.indeed.com/viewjob?jk=99c6d56e1e9ecbd9</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99c6d56e1e9ecbd9</t>
+          <t>https://www.indeed.com/viewjob?jk=ec2268853b5e3d32</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec2268853b5e3d32</t>
+          <t>https://www.indeed.com/viewjob?jk=cc317ad96269ff6c</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc317ad96269ff6c</t>
+          <t>https://www.indeed.com/viewjob?jk=2c59791ffa8037e0</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c59791ffa8037e0</t>
+          <t>https://www.indeed.com/viewjob?jk=93c00120a22fd95f</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93c00120a22fd95f</t>
+          <t>https://www.indeed.com/viewjob?jk=e5fd76a0505c1f45</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5fd76a0505c1f45</t>
+          <t>https://www.indeed.com/viewjob?jk=52bda57a7eae91d3</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52bda57a7eae91d3</t>
+          <t>https://www.indeed.com/viewjob?jk=8d79924b7c683266</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d79924b7c683266</t>
+          <t>https://www.indeed.com/viewjob?jk=18b51a17582c12e7</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18b51a17582c12e7</t>
+          <t>https://www.indeed.com/viewjob?jk=c239cf58c8fa1c71</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c239cf58c8fa1c71</t>
+          <t>https://www.indeed.com/viewjob?jk=d5a42ec359480e0d</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5a42ec359480e0d</t>
+          <t>https://www.indeed.com/viewjob?jk=5ed6224d65d164cb</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ed6224d65d164cb</t>
+          <t>https://www.indeed.com/viewjob?jk=ffcd6c03d59f6052</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffcd6c03d59f6052</t>
+          <t>https://www.indeed.com/viewjob?jk=ddc6dd123946c0df</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddc6dd123946c0df</t>
+          <t>https://www.indeed.com/viewjob?jk=2b026195b5394344</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b026195b5394344</t>
+          <t>https://www.indeed.com/viewjob?jk=9ffe2cd40b6dd0e7</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ffe2cd40b6dd0e7</t>
+          <t>https://www.indeed.com/viewjob?jk=2581b6e435257226</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2581b6e435257226</t>
+          <t>https://www.indeed.com/viewjob?jk=de24f7419929c1bf</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de24f7419929c1bf</t>
+          <t>https://www.indeed.com/viewjob?jk=5380c72e36e9ef3d</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5380c72e36e9ef3d</t>
+          <t>https://www.indeed.com/viewjob?jk=43d4c68e7e9e2fef</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43d4c68e7e9e2fef</t>
+          <t>https://www.indeed.com/viewjob?jk=7a8557481e61c905</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a8557481e61c905</t>
+          <t>https://www.indeed.com/viewjob?jk=af8a69205565050f</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af8a69205565050f</t>
+          <t>https://www.indeed.com/viewjob?jk=dfedec5986433f19</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfedec5986433f19</t>
+          <t>https://www.indeed.com/viewjob?jk=dadc73e392f990d3</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dadc73e392f990d3</t>
+          <t>https://www.indeed.com/viewjob?jk=df6f8697322180c6</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df6f8697322180c6</t>
+          <t>https://www.indeed.com/viewjob?jk=b407a88f3a1f87f8</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b407a88f3a1f87f8</t>
+          <t>https://www.indeed.com/viewjob?jk=ce6e6d7e4f41a3e8</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce6e6d7e4f41a3e8</t>
+          <t>https://www.indeed.com/viewjob?jk=1662c7096eaa5c34</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1662c7096eaa5c34</t>
+          <t>https://www.indeed.com/viewjob?jk=9b54c062fe208581</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b54c062fe208581</t>
+          <t>https://www.indeed.com/viewjob?jk=3ca77008309e43be</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Redshift, S3, Azure, Databricks, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ca77008309e43be</t>
+          <t>https://www.indeed.com/viewjob?jk=ede735cbdf2b63e0</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Axle</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Frederick, MD, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Azure, Databricks, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ede735cbdf2b63e0</t>
+          <t>https://www.indeed.com/viewjob?jk=353f08220bc3960e</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Engineer | The Points Guy</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Axle</t>
+          <t>Red Ventures</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Frederick, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,17 +2866,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=353f08220bc3960e</t>
+          <t>https://www.indeed.com/viewjob?jk=ec2d5686f500c7c1</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,19 +2911,19 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec2d5686f500c7c1</t>
+          <t>https://www.indeed.com/viewjob?jk=ac5793781d1c8a3c</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer | The Points Guy</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Red Ventures</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac5793781d1c8a3c</t>
+          <t>https://www.indeed.com/viewjob?jk=e3a17b22e5142267</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Analytics Engineer (Data Modeling &amp; BI)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Keeper Security</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3a17b22e5142267</t>
+          <t>https://www.indeed.com/viewjob?jk=b319560288703a69</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (Data Modeling &amp; BI)</t>
+          <t>CA IAM Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Keeper Security</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,42 +3006,42 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Scala, Snowflake, Data Modeling</t>
+          <t>Redshift, IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Snowflake, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b319560288703a69</t>
+          <t>https://www.indeed.com/viewjob?jk=1a8d75516142a508</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CA IAM Engineer</t>
+          <t>Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Verse</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Redshift, IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Snowflake, Tableau, Tableau Server</t>
+          <t>Kinesis, Redshift, S3, RDS, Databricks, GCP, BigQuery, Hadoop, Hive, HBase</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a8d75516142a508</t>
+          <t>https://www.indeed.com/viewjob?jk=2169de43fedb76d3</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Engineering</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Verse</t>
+          <t>SambaNova Systems</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, S3, RDS, Databricks, GCP, BigQuery, Hadoop, Hive, HBase</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2169de43fedb76d3</t>
+          <t>https://www.indeed.com/viewjob?jk=564c2131c7a47b4e</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Sr. Platform Engineering</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SambaNova Systems</t>
+          <t>archer</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=564c2131c7a47b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=e910893e7900f872</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML</t>
+          <t>Computer Programmer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Axle</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,42 +3146,42 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e288d00b33f48efe</t>
+          <t>https://www.indeed.com/viewjob?jk=b3f8d985ccebf8fe</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sr. Platform Engineering</t>
+          <t>Data Engineer (AIA)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>archer</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,42 +3191,42 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e910893e7900f872</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f49ea5746dd899</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Computer Programmer</t>
+          <t>Data Engineer (AIA)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Axle</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3f8d985ccebf8fe</t>
+          <t>https://www.indeed.com/viewjob?jk=422b5002f3c92e96</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f49ea5746dd899</t>
+          <t>https://www.indeed.com/viewjob?jk=4ca947b911b13d47</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=422b5002f3c92e96</t>
+          <t>https://www.indeed.com/viewjob?jk=2762492ad7551efe</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer (AIA)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ca947b911b13d47</t>
+          <t>https://www.indeed.com/viewjob?jk=cb9acfcb385fd29f</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer (AIA)</t>
+          <t>Data Engineer, Analytics &amp; Machine Learning Enablement</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Keeper Security</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2762492ad7551efe</t>
+          <t>https://www.indeed.com/viewjob?jk=b569d0296983d6a1</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Databricks Architect</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb9acfcb385fd29f</t>
+          <t>https://www.indeed.com/viewjob?jk=010224fd403e5335</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Engineer, Analytics &amp; Machine Learning Enablement</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Keeper Security</t>
+          <t>Cloud and Things</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,24 +3426,24 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, BigQuery, Scala, Snowflake</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Scala, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b569d0296983d6a1</t>
+          <t>https://www.indeed.com/viewjob?jk=8dcbb0b99721efea</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbdcf2158c6b2d0d</t>
+          <t>https://www.indeed.com/viewjob?jk=6a924e0d6d13cba9</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Cloud and Things</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Scala, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dcbb0b99721efea</t>
+          <t>https://www.indeed.com/viewjob?jk=fbdcf2158c6b2d0d</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,69 +3531,69 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a924e0d6d13cba9</t>
+          <t>https://www.indeed.com/viewjob?jk=5239f6ce7d60780b</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>SIGNITIVES</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
+          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5239f6ce7d60780b</t>
+          <t>https://www.indeed.com/viewjob?jk=ccbfb275c784c26b</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SIGNITIVES</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccbfb275c784c26b</t>
+          <t>https://www.indeed.com/viewjob?jk=5ed12a9528f47173</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Senior Data Engineer | The Points Guy</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Red Ventures</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server</t>
+          <t>AWS, Lambda, S3, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b67c42af6bdf7f4d</t>
+          <t>https://www.indeed.com/viewjob?jk=aa160af377aea6a2</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Specialist Software Engineering</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,29 +3671,29 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Kinesis, S3, API Gateway, ECS, Event Hubs, Zookeeper, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ed12a9528f47173</t>
+          <t>https://www.indeed.com/viewjob?jk=66f8131b391d620e</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Data Engineer | The Points Guy</t>
+          <t>Senior Full-Stack Python Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Red Ventures</t>
+          <t>N-iX</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Cloud Storage, Vertex AI, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa160af377aea6a2</t>
+          <t>https://www.indeed.com/viewjob?jk=365bb0b9ec3ce321</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Specialist Software Engineering</t>
+          <t>Software Development Engineer - Credential API</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, API Gateway, ECS, Event Hubs, Zookeeper, Kafka, CI/CD, Jenkins</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f8131b391d620e</t>
+          <t>https://www.indeed.com/viewjob?jk=a4c302fda1f6ae84</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Focus Financial Partners</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,139 +3776,139 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, Kafka, Oracle, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Dask, Snowflake</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bd882abe2f239e8</t>
+          <t>https://www.indeed.com/viewjob?jk=dc6ec804cfff5642</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior DevOps Engineer II</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Focus Financial Partners</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Dask, Snowflake</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc6ec804cfff5642</t>
+          <t>https://www.indeed.com/viewjob?jk=3af6a74b61fd0779</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Python Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>N-iX</t>
+          <t>Gates Foundation</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Cloud Storage, Vertex AI, Scala, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, ELT</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=365bb0b9ec3ce321</t>
+          <t>https://www.indeed.com/viewjob?jk=d0e09f867e58f64d</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Development Engineer - Credential API</t>
+          <t>Azure Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>Witherite Law Group</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4c302fda1f6ae84</t>
+          <t>https://www.indeed.com/viewjob?jk=2d4c16398c048d9f</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - Contributory Network</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Bloom Growth Partners</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, ECS, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec3ffe3d2951f742</t>
+          <t>https://www.indeed.com/viewjob?jk=9a1c158c64508404</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>Health-E Commerce</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af6a74b61fd0779</t>
+          <t>https://www.indeed.com/viewjob?jk=2b75ba4eaa7e2f72</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Cloud Infrastructure, Engineer II</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Gates Foundation</t>
+          <t>Trinity Logistics</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Seaford, DE, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, ELT</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0e09f867e58f64d</t>
+          <t>https://www.indeed.com/viewjob?jk=e66613c1418d016b</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Azure Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Witherite Law Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, Scala, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d4c16398c048d9f</t>
+          <t>https://www.indeed.com/viewjob?jk=eec716db1d652f56</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Contributory Network</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, ECS, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Google Cloud Platform, Scala, MySQL, NoSQL, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a1c158c64508404</t>
+          <t>https://www.indeed.com/viewjob?jk=5f84e68d5415404a</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE) - AI Platform &amp; Cloud</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Kitsap Credit Union</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Bremerton, WA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Spark, Kafka, Snowflake, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Event Hubs, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, SonarQube</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67434a699408c40f</t>
+          <t>https://www.indeed.com/viewjob?jk=150b9708ae649096</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Back-End (Java &amp; Spring Boot)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Health-E Commerce</t>
+          <t>PlanOmatic HQ</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b75ba4eaa7e2f72</t>
+          <t>https://www.indeed.com/viewjob?jk=4197b722f1b29f84</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure, Engineer II</t>
+          <t>AI Engineer - Insurance Domain - HYBRID</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Trinity Logistics</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Seaford, DE, US USA</t>
+          <t>Warren, NJ, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, Terraform</t>
+          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e66613c1418d016b</t>
+          <t>https://www.indeed.com/viewjob?jk=aeda85e53ae1234a</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>Senior Integration Developer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AlayaCare</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,42 +4196,42 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, MySQL, NoSQL, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f84e68d5415404a</t>
+          <t>https://www.indeed.com/viewjob?jk=2d6930b008143758</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Cloud Platforms Engineer II</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Amcor</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Oshkosh, WI, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, Scala, Data Modeling, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Scala, Power BI, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,67 +4241,67 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eec716db1d652f56</t>
+          <t>https://www.indeed.com/viewjob?jk=0a5bd8b939af9f70</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>AI Engineer - Insurance Domain - HYBRID</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Warren, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeda85e53ae1234a</t>
+          <t>https://www.indeed.com/viewjob?jk=75e319e5ec133537</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Sr Systems Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Kitsap Credit Union</t>
+          <t>CEI Services</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Bremerton, WA, US USA</t>
+          <t>Fargo, ND, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, SonarQube</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,94 +4311,94 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=150b9708ae649096</t>
+          <t>https://www.indeed.com/viewjob?jk=f846bcd41f966d19</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back-End (Java &amp; Spring Boot)</t>
+          <t>Sr Systems Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>PlanOmatic HQ</t>
+          <t>MasTec Inc</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Fargo, ND, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4197b722f1b29f84</t>
+          <t>https://www.indeed.com/viewjob?jk=ba06f08c24782d2d</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Integration Developer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>AlayaCare</t>
+          <t>RapidSOS</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, SQS, SNS, ECS, IAM, Scala, Kafka, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d6930b008143758</t>
+          <t>https://www.indeed.com/viewjob?jk=6c059e9218f7e23d</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Cloud Platforms Engineer II</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Amcor</t>
+          <t>RapidSOS</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Oshkosh, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Scala, Power BI, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, SQS, SNS, ECS, IAM, Scala, Kafka, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a5bd8b939af9f70</t>
+          <t>https://www.indeed.com/viewjob?jk=d3986c9d7e69f169</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Gen AI Platform &amp; Deployment Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Spark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75e319e5ec133537</t>
+          <t>https://www.indeed.com/viewjob?jk=7ad5e385a9b79a74</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Sr Systems Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>CEI Services</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Fargo, ND, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, S3, IAM, Snowflake, Data Modeling, ETL, ELT, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f846bcd41f966d19</t>
+          <t>https://www.indeed.com/viewjob?jk=842f8f1cf0d90520</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Sr Systems Engineer</t>
+          <t>Backend Engineer II</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>MasTec Inc</t>
+          <t>HackerRank Careers</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Fargo, ND, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba06f08c24782d2d</t>
+          <t>https://www.indeed.com/viewjob?jk=d4979e4cfe40ed8d</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>DevOps with IoT focus</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Intellimation LLC</t>
+          <t>Voya Financial</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Braintree, MA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, IAM, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>Azure, Databricks, Spark, Kafka, Oracle, MySQL, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f64235fd5c4fac6</t>
+          <t>https://www.indeed.com/viewjob?jk=06f0f1071f3e2b14</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>RapidSOS</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,112 +4581,112 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, IAM, Scala, Kafka, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c059e9218f7e23d</t>
+          <t>https://www.indeed.com/viewjob?jk=3d356cba46c60202</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Multi-Cloud Networking Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>RapidSOS</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, IAM, Scala, Kafka, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, IAM, RDS, Scala, Oracle, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3986c9d7e69f169</t>
+          <t>https://www.indeed.com/viewjob?jk=7ff8e0f386ef907b</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Gen AI Platform &amp; Deployment Engineer</t>
+          <t>Senior Systems Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Fueled</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ad5e385a9b79a74</t>
+          <t>https://www.indeed.com/viewjob?jk=9642665184944e11</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Voya Financial</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Braintree, MA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, Kafka, Oracle, MySQL, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,32 +4696,32 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f0f1071f3e2b14</t>
+          <t>https://www.indeed.com/viewjob?jk=1de30f12b78fca01</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Azure, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,67 +4731,67 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=facf27c6b3631798</t>
+          <t>https://www.indeed.com/viewjob?jk=b88b23e7d0b05c8f</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Backend Engineer II</t>
+          <t>DevOps / Platform Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>HackerRank Careers</t>
+          <t>Vivacity Tech PBC</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4979e4cfe40ed8d</t>
+          <t>https://www.indeed.com/viewjob?jk=ed1d3fe1d3532916</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>Illumio</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d356cba46c60202</t>
+          <t>https://www.indeed.com/viewjob?jk=cad79b56c244d0fa</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Multi-Cloud Networking Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>DMV IT Service LLC</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Richmond, TX, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Oracle, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
+          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ff8e0f386ef907b</t>
+          <t>https://www.indeed.com/viewjob?jk=99e35b16ebbf3788</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer</t>
+          <t>BI Engineer I (Hybrid)</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Fueled</t>
+          <t>NEUMO</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Wayne, IN, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9642665184944e11</t>
+          <t>https://www.indeed.com/viewjob?jk=9d2a5858f9149296</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Software Engineer, Ads Infra - Serving and Foundation</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Hive, Spark, Scala, Kafka, Data Modeling, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1de30f12b78fca01</t>
+          <t>https://www.indeed.com/viewjob?jk=e26cb9e516d559dc</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>AI-ML Engineer 1</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Universal Avionics Systems Corporation</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Tucson, AZ, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, S3, Azure, GCP, Hadoop, Spark, Scala, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88b23e7d0b05c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=e3e0f3955fde63ec</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>DevOps / Platform Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Vivacity Tech PBC</t>
+          <t>Aroha Technologies</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed1d3fe1d3532916</t>
+          <t>https://www.indeed.com/viewjob?jk=0e4069f2434551ab</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Illumio</t>
+          <t>isolved</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Nixa, MO, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Azure Cosmos DB, NoSQL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cad79b56c244d0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=3d13a0d2142e0261</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Pre-Sales Engineer (Data &amp; Analytics)</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>DMV IT Service LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Richmond, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,34 +5036,34 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99e35b16ebbf3788</t>
+          <t>https://www.indeed.com/viewjob?jk=3c940790b1550a5b</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS)</t>
+          <t>DevOps Engineer, Senior</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Capnexus</t>
+          <t>Mister Car Wash</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tucson, AZ, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,34 +5071,34 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Scala, DynamoDB, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a7b11ddd229f030</t>
+          <t>https://www.indeed.com/viewjob?jk=414fb4f6d3a8dcd9</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>BI Engineer I (Hybrid)</t>
+          <t>Software Engineer III (CJIS)</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>NEUMO</t>
+          <t>County of San Luis Obispo</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Fort Wayne, IN, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,34 +5106,34 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, SQL Server, MySQL, DynamoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d2a5858f9149296</t>
+          <t>https://www.indeed.com/viewjob?jk=2cda7602e4b5904c</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Software Engineer, Ads Infra - Serving and Foundation</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Gametime United</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,34 +5141,34 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hive, Spark, Scala, Kafka, Data Modeling, ETL, Airflow, Git</t>
+          <t>AWS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e26cb9e516d559dc</t>
+          <t>https://www.indeed.com/viewjob?jk=24a25e68a1bd6d4f</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>AI-ML Engineer 1</t>
+          <t>Warranty Data Analyst / Data Scientist</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Universal Avionics Systems Corporation</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Tucson, AZ, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Hadoop, Spark, Scala, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3e0f3955fde63ec</t>
+          <t>https://www.indeed.com/viewjob?jk=2e9bb1ef1dd7ba48</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Warranty Data Analyst / Data Scientist</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>isolved</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Nixa, MO, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,34 +5211,34 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Azure Cosmos DB, NoSQL, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d13a0d2142e0261</t>
+          <t>https://www.indeed.com/viewjob?jk=2ffd491a76c9fa66</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Pre-Sales Engineer (Data &amp; Analytics)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Headspace</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,182 +5246,182 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c940790b1550a5b</t>
+          <t>https://www.indeed.com/viewjob?jk=cbb7191dcfe18f53</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Warranty Data Analyst / Data Scientist</t>
+          <t>Data/ Application Integration Engineer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Charlie's Produce</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Oracle, ETL, ELT</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e9bb1ef1dd7ba48</t>
+          <t>https://www.indeed.com/viewjob?jk=ca44b855356ccf40</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Warranty Data Analyst / Data Scientist</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ffd491a76c9fa66</t>
+          <t>https://www.indeed.com/viewjob?jk=41f5f841b3bf67ad</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Headspace</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, MS Excel, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbb7191dcfe18f53</t>
+          <t>https://www.indeed.com/viewjob?jk=af37d87136cf35b5</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Senior</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Mister Car Wash</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Tucson, AZ, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Impala, Spark, Scala</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=414fb4f6d3a8dcd9</t>
+          <t>https://www.indeed.com/viewjob?jk=f28a43a00c1a7844</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Software Engineer III (CJIS)</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>County of San Luis Obispo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, SQL Server, MySQL, DynamoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, IAM, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,32 +5431,32 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cda7602e4b5904c</t>
+          <t>https://www.indeed.com/viewjob?jk=a2f5cef76808163a</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Software Engineer - DevSecOps (Associate, Experienced or Senior)</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,59 +5466,59 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afe37944ff3c78ea</t>
+          <t>https://www.indeed.com/viewjob?jk=672dba9cce12de5f</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Gametime United</t>
+          <t>Trepp</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, S3, Spark, Scala, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24a25e68a1bd6d4f</t>
+          <t>https://www.indeed.com/viewjob?jk=d561d8c2375dd6b1</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Senior Infrastructure Engineer-Azure Data &amp; Analytics Engineer - State National</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Markel Corporation</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Bedford, TX, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,34 +5526,34 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f5f841b3bf67ad</t>
+          <t>https://www.indeed.com/viewjob?jk=94507e2995b9ee29</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Data Engineer II - Information Technology</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Board of Governors of the Federal Reserve System</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,34 +5561,34 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, MS Excel, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af37d87136cf35b5</t>
+          <t>https://www.indeed.com/viewjob?jk=b222160bc0c2b3e3</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>nSCALE</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Barstow, TX, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,34 +5596,34 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Impala, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f28a43a00c1a7844</t>
+          <t>https://www.indeed.com/viewjob?jk=bc6c300d9777dc4b</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Engineer - Seattle, WA</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nSCALE</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,34 +5631,34 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, IAM, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2f5cef76808163a</t>
+          <t>https://www.indeed.com/viewjob?jk=894fb5b066595659</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Solution Engineer</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>SimilarWeb</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,34 +5666,34 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=672dba9cce12de5f</t>
+          <t>https://www.indeed.com/viewjob?jk=8e039b4fcb467133</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Engineer, Developer Platform (Cloud Apps)</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Trepp</t>
+          <t>Motional</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,34 +5701,34 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, Spark, Scala, Data Modeling, CI/CD, Git</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, NoSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d561d8c2375dd6b1</t>
+          <t>https://www.indeed.com/viewjob?jk=a10c8d4659b2bc91</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer-Azure Data &amp; Analytics Engineer - State National</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Markel Corporation</t>
+          <t>Envoy global</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Bedford, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,34 +5736,34 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>Azure, Blob Storage, Scala, SQL Server, Splunk, CI/CD, Azure DevOps, Terraform, AKS, Git</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94507e2995b9ee29</t>
+          <t>https://www.indeed.com/viewjob?jk=3d81e4212199a1a8</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Data Engineer II - Information Technology</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Board of Governors of the Federal Reserve System</t>
+          <t>Envoy global</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,34 +5771,34 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, PostgreSQL, NoSQL</t>
+          <t>Azure, Blob Storage, Scala, SQL Server, Splunk, CI/CD, Azure DevOps, Terraform, AKS, Git</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b222160bc0c2b3e3</t>
+          <t>https://www.indeed.com/viewjob?jk=d276b3164ac33893</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>SQL Engineer</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>nSCALE</t>
+          <t>Mechanical Licensing Collective</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Barstow, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,34 +5806,34 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
+          <t>AWS, Athena, RDS, Scala, Oracle, PostgreSQL, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc6c300d9777dc4b</t>
+          <t>https://www.indeed.com/viewjob?jk=e3db429a534810fa</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Data Engineer - Seattle, WA</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>nSCALE</t>
+          <t>Alpaca</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,34 +5841,34 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
+          <t>AWS, RDS, GCP, Spark, Scala, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=894fb5b066595659</t>
+          <t>https://www.indeed.com/viewjob?jk=8cf5cd1df0f54fe6</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Data Solution Engineer</t>
+          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>SimilarWeb</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,34 +5876,34 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e039b4fcb467133</t>
+          <t>https://www.indeed.com/viewjob?jk=2ae2d7c352959fb2</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Engineer, Developer Platform (Cloud Apps)</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Motional</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,34 +5911,34 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, NoSQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a10c8d4659b2bc91</t>
+          <t>https://www.indeed.com/viewjob?jk=5b0780a9fb0dbc39</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Ads Targeting Data Engineer, Ads Core</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Envoy global</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,34 +5946,34 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, Scala, SQL Server, Splunk, CI/CD, Azure DevOps, Terraform, AKS, Git</t>
+          <t>AWS, RDS, Hive, Spark, Scala, Kafka, Data Modeling, ETL, Airflow, Python</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d81e4212199a1a8</t>
+          <t>https://www.indeed.com/viewjob?jk=cd2adeacdfffb183</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Envoy global</t>
+          <t>University of Maryland Medical System</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>North Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5981,34 +5981,34 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, Scala, SQL Server, Splunk, CI/CD, Azure DevOps, Terraform, AKS, Git</t>
+          <t>RDS, Hadoop, HDFS, Hive, MapReduce, Spark, Scala, Oracle, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d276b3164ac33893</t>
+          <t>https://www.indeed.com/viewjob?jk=4188adfee24d1373</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>SQL Engineer</t>
+          <t>Senior Quality Platform Engineer</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Mechanical Licensing Collective</t>
+          <t>Circle.so</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6016,34 +6016,34 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AWS, Athena, RDS, Scala, Oracle, PostgreSQL, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3db429a534810fa</t>
+          <t>https://www.indeed.com/viewjob?jk=3752971091aeeac9</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Software Engineer, Platform &amp; Product</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Alpaca</t>
+          <t>Ware Malcomb</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6051,34 +6051,34 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Spark, Scala, ETL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cf5cd1df0f54fe6</t>
+          <t>https://www.indeed.com/viewjob?jk=aed0adf2e92986f6</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
+          <t>Senior Specialist - Architecture (AI Engineer with Codex Exp.)</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6086,34 +6086,34 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Kafka, Data Modeling, MLOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ae2d7c352959fb2</t>
+          <t>https://www.indeed.com/viewjob?jk=65c00c71c8e6928e</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ramp</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6121,34 +6121,34 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b0780a9fb0dbc39</t>
+          <t>https://www.indeed.com/viewjob?jk=45e12b77b9565199</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Ads Targeting Data Engineer, Ads Core</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6156,34 +6156,34 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hive, Spark, Scala, Kafka, Data Modeling, ETL, Airflow, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd2adeacdfffb183</t>
+          <t>https://www.indeed.com/viewjob?jk=ab7793f0a792b417</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Senior Quality Platform Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Circle.so</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6191,34 +6191,34 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3752971091aeeac9</t>
+          <t>https://www.indeed.com/viewjob?jk=650677ad14cf645f</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Platform</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Ramp</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Terraform, Airflow</t>
+          <t>Azure, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -6236,24 +6236,24 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45e12b77b9565199</t>
+          <t>https://www.indeed.com/viewjob?jk=ff779f0dce63ada3</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>Azure, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6271,24 +6271,24 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=185c1836bede91b1</t>
+          <t>https://www.indeed.com/viewjob?jk=9eb55e9f7a6dc231</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Empirx Health</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, Azure, Databricks, Blob Storage, GCP, Scala, Kafka, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -6306,24 +6306,24 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cedfc80fbfee214</t>
+          <t>https://www.indeed.com/viewjob?jk=c08697ee3f4bc0ba</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Empirx Health</t>
+          <t>Health-E Commerce</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6331,34 +6331,34 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Blob Storage, GCP, Scala, Kafka, CI/CD, Azure DevOps, Git</t>
+          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, Scala, Data Modeling, ETL, Azure DevOps, Python</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c08697ee3f4bc0ba</t>
+          <t>https://www.indeed.com/viewjob?jk=56afd442294fd678</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Senior Software Engineer Go Outdoors Payments</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Brandt Information Services, Inc.</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6366,34 +6366,34 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab7793f0a792b417</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f9736f5f852f3d</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Senior Software Engineer Go Outdoors Payments</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Brandt Information Services, Inc.</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6401,34 +6401,34 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=650677ad14cf645f</t>
+          <t>https://www.indeed.com/viewjob?jk=e66c9de7a81a7d66</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fairlife, LLC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6436,34 +6436,34 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Azure, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Star Schema, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff779f0dce63ada3</t>
+          <t>https://www.indeed.com/viewjob?jk=f203c334e20f61e9</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Azure, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -6481,24 +6481,24 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb55e9f7a6dc231</t>
+          <t>https://www.indeed.com/viewjob?jk=185c1836bede91b1</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Health-E Commerce</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6506,34 +6506,34 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, Scala, Data Modeling, ETL, Azure DevOps, Python</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56afd442294fd678</t>
+          <t>https://www.indeed.com/viewjob?jk=2cedfc80fbfee214</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Go Outdoors Payments</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Brandt Information Services, Inc.</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6541,34 +6541,34 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f9736f5f852f3d</t>
+          <t>https://www.indeed.com/viewjob?jk=cd98e6c90182dad1</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Go Outdoors Payments</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Brandt Information Services, Inc.</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6576,34 +6576,34 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e66c9de7a81a7d66</t>
+          <t>https://www.indeed.com/viewjob?jk=1188cf2ae8e587af</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Fairlife, LLC</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6611,34 +6611,34 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Star Schema, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f203c334e20f61e9</t>
+          <t>https://www.indeed.com/viewjob?jk=ec0dc8f9f8c8d698</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>BI Developer Mid or Senior</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Progressive</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6646,34 +6646,34 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+          <t>AWS, Lambda, S3, Scala, Snowflake, SQL Server, ETL, ELT, dbt, Terraform</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd98e6c90182dad1</t>
+          <t>https://www.indeed.com/viewjob?jk=cdbb236dac23c233</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Java Compliance &amp; Governance Developer</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -6691,24 +6691,24 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1188cf2ae8e587af</t>
+          <t>https://www.indeed.com/viewjob?jk=243990c269c56673</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Java Compliance &amp; Governance Developer</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -6725,76 +6725,6 @@
         </is>
       </c>
       <c r="G180" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ec0dc8f9f8c8d698</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>Java Compliance &amp; Governance Developer</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>NC, US USA</t>
-        </is>
-      </c>
-      <c r="D181" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=243990c269c56673</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>Java Compliance &amp; Governance Developer</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>NC, US USA</t>
-        </is>
-      </c>
-      <c r="D182" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=e9d53f3c6ff20349</t>
         </is>

--- a/results/job_matches_2026-04-23.xlsx
+++ b/results/job_matches_2026-04-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G180"/>
+  <dimension ref="A1:G134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,52 +468,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Java AI / ML Integration Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Q2ebanking</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc44924f0b95abaf</t>
+          <t>https://www.indeed.com/viewjob?jk=ebc27b8ad561d2ae</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AWS DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Glacier Analytics LLC</t>
+          <t>DOW</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,42 +531,42 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f2c6e67bc23530</t>
+          <t>https://www.indeed.com/viewjob?jk=0e6f52d2577111f6</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DOW</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e6f52d2577111f6</t>
+          <t>https://www.indeed.com/viewjob?jk=9a75bae8fe6b588f</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -601,19 +601,19 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a75bae8fe6b588f</t>
+          <t>https://www.indeed.com/viewjob?jk=be5d882b0154cb62</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate Data and AI Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -622,56 +622,56 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, EMR, Kinesis, Redshift, S3, RDS, GCP, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be5d882b0154cb62</t>
+          <t>https://www.indeed.com/viewjob?jk=718af7ca01e94aee</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer/ Architecture (ADF &amp; Databricks)</t>
+          <t>Associate Data and AI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>United Vein &amp; Vascular Centers</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala</t>
+          <t>AWS, EMR, Kinesis, Redshift, S3, RDS, GCP, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=443e4c4dac7242b8</t>
+          <t>https://www.indeed.com/viewjob?jk=10c4f60d661f5f00</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=718af7ca01e94aee</t>
+          <t>https://www.indeed.com/viewjob?jk=6f971eeb79a21180</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10c4f60d661f5f00</t>
+          <t>https://www.indeed.com/viewjob?jk=cfbf52f31ea2e787</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Associate Data and AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Climate First Bank</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, S3, RDS, GCP, Hadoop, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f971eeb79a21180</t>
+          <t>https://www.indeed.com/viewjob?jk=32602a30e2eae4db</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Associate Data and AI Engineer</t>
+          <t>Java Kafka Streams Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,42 +801,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, S3, RDS, GCP, Hadoop, Spark, Scala</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfbf52f31ea2e787</t>
+          <t>https://www.indeed.com/viewjob?jk=7f16d1c6de9e445f</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Engineer - Remote US</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Climate First Bank</t>
+          <t>Smile Digital Health</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, GCP, Cloud Storage, Scala, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32602a30e2eae4db</t>
+          <t>https://www.indeed.com/viewjob?jk=3c0faea77dd1e82a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Remote US</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Smile Digital Health</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Glastonbury, CT, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, GCP, Cloud Storage, Scala, Kafka</t>
+          <t>AWS, Glue, Redshift, RDS, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c0faea77dd1e82a</t>
+          <t>https://www.indeed.com/viewjob?jk=861b456826f5b0c4</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior DevOps Software Engineer</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>eClinical Solutions, LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, MLOps, MLflow</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc6ebe88367f5090</t>
+          <t>https://www.indeed.com/viewjob?jk=0672f1d449c9d9e2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (DataOps)</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Black Canyon Consulting</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Google Cloud Platform, GCP, Flume, Spark, Spark Streaming, Kafka</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=298c77dba97763b9</t>
+          <t>https://www.indeed.com/viewjob?jk=96a88c14093ccdaf</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0672f1d449c9d9e2</t>
+          <t>https://www.indeed.com/viewjob?jk=14f80cb5b125e7cc</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96a88c14093ccdaf</t>
+          <t>https://www.indeed.com/viewjob?jk=ca6623928abe2730</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f80cb5b125e7cc</t>
+          <t>https://www.indeed.com/viewjob?jk=46e364170a7ee29f</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca6623928abe2730</t>
+          <t>https://www.indeed.com/viewjob?jk=0e67913bb063b4e1</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46e364170a7ee29f</t>
+          <t>https://www.indeed.com/viewjob?jk=03e6278fa86f66b6</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e67913bb063b4e1</t>
+          <t>https://www.indeed.com/viewjob?jk=a417258c27e6884b</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e6278fa86f66b6</t>
+          <t>https://www.indeed.com/viewjob?jk=68ff6a6e54c5bb38</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a417258c27e6884b</t>
+          <t>https://www.indeed.com/viewjob?jk=b864420111578783</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68ff6a6e54c5bb38</t>
+          <t>https://www.indeed.com/viewjob?jk=90020927d62d9e32</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b864420111578783</t>
+          <t>https://www.indeed.com/viewjob?jk=e6445ef98b11402a</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90020927d62d9e32</t>
+          <t>https://www.indeed.com/viewjob?jk=63c85699934dff6e</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6445ef98b11402a</t>
+          <t>https://www.indeed.com/viewjob?jk=26b24994302869a9</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63c85699934dff6e</t>
+          <t>https://www.indeed.com/viewjob?jk=06b0116b71837d13</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26b24994302869a9</t>
+          <t>https://www.indeed.com/viewjob?jk=8120526ad261b6a4</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06b0116b71837d13</t>
+          <t>https://www.indeed.com/viewjob?jk=71be0c8c221ee567</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8120526ad261b6a4</t>
+          <t>https://www.indeed.com/viewjob?jk=ee059ac44d2277d6</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71be0c8c221ee567</t>
+          <t>https://www.indeed.com/viewjob?jk=af1a0c944d7d687c</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee059ac44d2277d6</t>
+          <t>https://www.indeed.com/viewjob?jk=a757acecac7ae896</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af1a0c944d7d687c</t>
+          <t>https://www.indeed.com/viewjob?jk=46cdcaa9c274907d</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a757acecac7ae896</t>
+          <t>https://www.indeed.com/viewjob?jk=0c545200255ccd75</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46cdcaa9c274907d</t>
+          <t>https://www.indeed.com/viewjob?jk=99c6d56e1e9ecbd9</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c545200255ccd75</t>
+          <t>https://www.indeed.com/viewjob?jk=ec2268853b5e3d32</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99c6d56e1e9ecbd9</t>
+          <t>https://www.indeed.com/viewjob?jk=cc317ad96269ff6c</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec2268853b5e3d32</t>
+          <t>https://www.indeed.com/viewjob?jk=2c59791ffa8037e0</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc317ad96269ff6c</t>
+          <t>https://www.indeed.com/viewjob?jk=93c00120a22fd95f</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c59791ffa8037e0</t>
+          <t>https://www.indeed.com/viewjob?jk=e5fd76a0505c1f45</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93c00120a22fd95f</t>
+          <t>https://www.indeed.com/viewjob?jk=52bda57a7eae91d3</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5fd76a0505c1f45</t>
+          <t>https://www.indeed.com/viewjob?jk=8d79924b7c683266</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52bda57a7eae91d3</t>
+          <t>https://www.indeed.com/viewjob?jk=18b51a17582c12e7</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d79924b7c683266</t>
+          <t>https://www.indeed.com/viewjob?jk=c239cf58c8fa1c71</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18b51a17582c12e7</t>
+          <t>https://www.indeed.com/viewjob?jk=d5a42ec359480e0d</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c239cf58c8fa1c71</t>
+          <t>https://www.indeed.com/viewjob?jk=5ed6224d65d164cb</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5a42ec359480e0d</t>
+          <t>https://www.indeed.com/viewjob?jk=ffcd6c03d59f6052</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ed6224d65d164cb</t>
+          <t>https://www.indeed.com/viewjob?jk=ddc6dd123946c0df</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffcd6c03d59f6052</t>
+          <t>https://www.indeed.com/viewjob?jk=2b026195b5394344</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddc6dd123946c0df</t>
+          <t>https://www.indeed.com/viewjob?jk=9ffe2cd40b6dd0e7</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b026195b5394344</t>
+          <t>https://www.indeed.com/viewjob?jk=2581b6e435257226</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ffe2cd40b6dd0e7</t>
+          <t>https://www.indeed.com/viewjob?jk=de24f7419929c1bf</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2581b6e435257226</t>
+          <t>https://www.indeed.com/viewjob?jk=5380c72e36e9ef3d</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de24f7419929c1bf</t>
+          <t>https://www.indeed.com/viewjob?jk=43d4c68e7e9e2fef</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5380c72e36e9ef3d</t>
+          <t>https://www.indeed.com/viewjob?jk=7a8557481e61c905</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43d4c68e7e9e2fef</t>
+          <t>https://www.indeed.com/viewjob?jk=af8a69205565050f</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a8557481e61c905</t>
+          <t>https://www.indeed.com/viewjob?jk=dfedec5986433f19</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af8a69205565050f</t>
+          <t>https://www.indeed.com/viewjob?jk=dadc73e392f990d3</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfedec5986433f19</t>
+          <t>https://www.indeed.com/viewjob?jk=df6f8697322180c6</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dadc73e392f990d3</t>
+          <t>https://www.indeed.com/viewjob?jk=b407a88f3a1f87f8</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df6f8697322180c6</t>
+          <t>https://www.indeed.com/viewjob?jk=ce6e6d7e4f41a3e8</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b407a88f3a1f87f8</t>
+          <t>https://www.indeed.com/viewjob?jk=1662c7096eaa5c34</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce6e6d7e4f41a3e8</t>
+          <t>https://www.indeed.com/viewjob?jk=9b54c062fe208581</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1662c7096eaa5c34</t>
+          <t>https://www.indeed.com/viewjob?jk=3ca77008309e43be</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Redshift, S3, Azure, Databricks, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,67 +2736,67 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b54c062fe208581</t>
+          <t>https://www.indeed.com/viewjob?jk=ede735cbdf2b63e0</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
+          <t>Senior Analytics Engineer (Data Modeling &amp; BI)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Keeper Security</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ca77008309e43be</t>
+          <t>https://www.indeed.com/viewjob?jk=b319560288703a69</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Verse</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Azure, Databricks, Spark, Scala, Kafka, Snowflake</t>
+          <t>Kinesis, Redshift, S3, RDS, Databricks, GCP, BigQuery, Hadoop, Hive, HBase</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,112 +2806,112 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ede735cbdf2b63e0</t>
+          <t>https://www.indeed.com/viewjob?jk=2169de43fedb76d3</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Sr. Platform Engineering</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Axle</t>
+          <t>archer</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Frederick, MD, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=353f08220bc3960e</t>
+          <t>https://www.indeed.com/viewjob?jk=e910893e7900f872</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer | The Points Guy</t>
+          <t>Java Compliance &amp; Governance Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Red Ventures</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, Glue, EMR, Redshift, ECS, RDS, Scala, Kafka, MySQL, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec2d5686f500c7c1</t>
+          <t>https://www.indeed.com/viewjob?jk=a09c947868c141e2</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer | The Points Guy</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Red Ventures</t>
+          <t>Suvoda</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Conshohocken, PA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac5793781d1c8a3c</t>
+          <t>https://www.indeed.com/viewjob?jk=c1b69a2cd2e20538</t>
         </is>
       </c>
     </row>
@@ -2923,90 +2923,90 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Suvoda</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3a17b22e5142267</t>
+          <t>https://www.indeed.com/viewjob?jk=ff6fc79a37f3e06f</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (Data Modeling &amp; BI)</t>
+          <t>Data Engineer (AIA)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Keeper Security</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b319560288703a69</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f49ea5746dd899</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>CA IAM Engineer</t>
+          <t>Data Engineer (AIA)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Redshift, IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Snowflake, Tableau, Tableau Server</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a8d75516142a508</t>
+          <t>https://www.indeed.com/viewjob?jk=422b5002f3c92e96</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Engineering</t>
+          <t>Data Engineer (AIA)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Verse</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, S3, RDS, Databricks, GCP, BigQuery, Hadoop, Hive, HBase</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,137 +3051,137 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2169de43fedb76d3</t>
+          <t>https://www.indeed.com/viewjob?jk=4ca947b911b13d47</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Data Engineer (AIA)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SambaNova Systems</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=564c2131c7a47b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=2762492ad7551efe</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sr. Platform Engineering</t>
+          <t>Data Engineer, Analytics &amp; Machine Learning Enablement</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>archer</t>
+          <t>Keeper Security</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e910893e7900f872</t>
+          <t>https://www.indeed.com/viewjob?jk=b569d0296983d6a1</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Computer Programmer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Axle</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3f8d985ccebf8fe</t>
+          <t>https://www.indeed.com/viewjob?jk=6a924e0d6d13cba9</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer (AIA)</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>SIGNITIVES</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f49ea5746dd899</t>
+          <t>https://www.indeed.com/viewjob?jk=ccbfb275c784c26b</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer (AIA)</t>
+          <t>Specialist Software Engineering</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Kinesis, S3, API Gateway, ECS, Event Hubs, Zookeeper, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,207 +3226,207 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=422b5002f3c92e96</t>
+          <t>https://www.indeed.com/viewjob?jk=66f8131b391d620e</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer (AIA)</t>
+          <t>Senior Full-Stack Python Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>N-iX</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Cloud Storage, Vertex AI, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ca947b911b13d47</t>
+          <t>https://www.indeed.com/viewjob?jk=365bb0b9ec3ce321</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer (AIA)</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, API Gateway, ECS, Scala, ETL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2762492ad7551efe</t>
+          <t>https://www.indeed.com/viewjob?jk=c0a2cb39a283363f</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer II</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb9acfcb385fd29f</t>
+          <t>https://www.indeed.com/viewjob?jk=3af6a74b61fd0779</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer, Analytics &amp; Machine Learning Enablement</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Keeper Security</t>
+          <t>Gates Foundation</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, BigQuery, Scala, Snowflake</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, ELT</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b569d0296983d6a1</t>
+          <t>https://www.indeed.com/viewjob?jk=d0e09f867e58f64d</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Databricks Architect</t>
+          <t>AI Engineer - Insurance Domain - HYBRID</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Warren, NJ, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=010224fd403e5335</t>
+          <t>https://www.indeed.com/viewjob?jk=aeda85e53ae1234a</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Cloud Platforms Engineer II</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Cloud and Things</t>
+          <t>Amcor</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Oshkosh, WI, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Scala, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Scala, Power BI, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dcbb0b99721efea</t>
+          <t>https://www.indeed.com/viewjob?jk=0a5bd8b939af9f70</t>
         </is>
       </c>
     </row>
@@ -3457,11 +3457,11 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,207 +3471,207 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a924e0d6d13cba9</t>
+          <t>https://www.indeed.com/viewjob?jk=75e319e5ec133537</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Sr Systems Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CEI Services</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Fargo, ND, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbdcf2158c6b2d0d</t>
+          <t>https://www.indeed.com/viewjob?jk=f846bcd41f966d19</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
+          <t>Sr Systems Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>MasTec Inc</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Fargo, ND, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5239f6ce7d60780b</t>
+          <t>https://www.indeed.com/viewjob?jk=ba06f08c24782d2d</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Gen AI Platform &amp; Deployment Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SIGNITIVES</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccbfb275c784c26b</t>
+          <t>https://www.indeed.com/viewjob?jk=7ad5e385a9b79a74</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II - AI Solutions</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ed12a9528f47173</t>
+          <t>https://www.indeed.com/viewjob?jk=488caabc0de3fad8</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Data Engineer | The Points Guy</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Red Ventures</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, S3, IAM, Snowflake, Data Modeling, ETL, ELT, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa160af377aea6a2</t>
+          <t>https://www.indeed.com/viewjob?jk=842f8f1cf0d90520</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Specialist Software Engineering</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>Voya Financial</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>Braintree, MA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, API Gateway, ECS, Event Hubs, Zookeeper, Kafka, CI/CD, Jenkins</t>
+          <t>Azure, Databricks, Spark, Kafka, Oracle, MySQL, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,137 +3681,137 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f8131b391d620e</t>
+          <t>https://www.indeed.com/viewjob?jk=06f0f1071f3e2b14</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Python Engineer</t>
+          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>N-iX</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Cloud Storage, Vertex AI, Scala, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=365bb0b9ec3ce321</t>
+          <t>https://www.indeed.com/viewjob?jk=3d356cba46c60202</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Software Development Engineer - Credential API</t>
+          <t>Multi-Cloud Networking Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, IAM, RDS, Scala, Oracle, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4c302fda1f6ae84</t>
+          <t>https://www.indeed.com/viewjob?jk=7ff8e0f386ef907b</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Systems Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Focus Financial Partners</t>
+          <t>Fueled</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Dask, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc6ec804cfff5642</t>
+          <t>https://www.indeed.com/viewjob?jk=9642665184944e11</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer II</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af6a74b61fd0779</t>
+          <t>https://www.indeed.com/viewjob?jk=1de30f12b78fca01</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Gates Foundation</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, ELT</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,172 +3856,172 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0e09f867e58f64d</t>
+          <t>https://www.indeed.com/viewjob?jk=b88b23e7d0b05c8f</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Azure Engineer</t>
+          <t>DevOps / Platform Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Witherite Law Group</t>
+          <t>Vivacity Tech PBC</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d4c16398c048d9f</t>
+          <t>https://www.indeed.com/viewjob?jk=ed1d3fe1d3532916</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Contributory Network</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, ECS, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a1c158c64508404</t>
+          <t>https://www.indeed.com/viewjob?jk=4ac82b1c79d8bff3</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer, Ads Infra - Serving and Foundation</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Health-E Commerce</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Hive, Spark, Scala, Kafka, Data Modeling, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b75ba4eaa7e2f72</t>
+          <t>https://www.indeed.com/viewjob?jk=e26cb9e516d559dc</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure, Engineer II</t>
+          <t>Warranty Data Analyst / Data Scientist</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Trinity Logistics</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Seaford, DE, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e66613c1418d016b</t>
+          <t>https://www.indeed.com/viewjob?jk=abdbd26974d27e06</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>DevOps Engineer, Senior</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Mister Car Wash</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tucson, AZ, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, Scala, Data Modeling, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,452 +4031,452 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eec716db1d652f56</t>
+          <t>https://www.indeed.com/viewjob?jk=414fb4f6d3a8dcd9</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>Software Engineer III (CJIS)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>County of San Luis Obispo</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, MySQL, NoSQL, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, SQL Server, MySQL, DynamoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f84e68d5415404a</t>
+          <t>https://www.indeed.com/viewjob?jk=2cda7602e4b5904c</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>PIMS Data Analyst</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Kitsap Credit Union</t>
+          <t>Bechtel</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bremerton, WA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, SonarQube</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=150b9708ae649096</t>
+          <t>https://www.indeed.com/viewjob?jk=84332d95fe089578</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back-End (Java &amp; Spring Boot)</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>PlanOmatic HQ</t>
+          <t>isolved</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Nixa, MO, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Azure Cosmos DB, NoSQL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4197b722f1b29f84</t>
+          <t>https://www.indeed.com/viewjob?jk=3d13a0d2142e0261</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>AI Engineer - Insurance Domain - HYBRID</t>
+          <t>Pre-Sales Engineer (Data &amp; Analytics)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Warren, NJ, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeda85e53ae1234a</t>
+          <t>https://www.indeed.com/viewjob?jk=3c940790b1550a5b</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Integration Developer</t>
+          <t>Warranty Data Analyst / Data Scientist</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>AlayaCare</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d6930b008143758</t>
+          <t>https://www.indeed.com/viewjob?jk=2e9bb1ef1dd7ba48</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Cloud Platforms Engineer II</t>
+          <t>Warranty Data Analyst / Data Scientist</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Amcor</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Oshkosh, WI, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Scala, Power BI, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a5bd8b939af9f70</t>
+          <t>https://www.indeed.com/viewjob?jk=2ffd491a76c9fa66</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Apptronik</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, PostgreSQL, NoSQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75e319e5ec133537</t>
+          <t>https://www.indeed.com/viewjob?jk=6c8a6b6744212463</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Sr Systems Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>CEI Services</t>
+          <t>Fustis LLC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Fargo, ND, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f846bcd41f966d19</t>
+          <t>https://www.indeed.com/viewjob?jk=7c7fe605c13e6870</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Sr Systems Engineer</t>
+          <t>Data/ Application Integration Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>MasTec Inc</t>
+          <t>Charlie's Produce</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Fargo, ND, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Oracle, ETL, ELT</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba06f08c24782d2d</t>
+          <t>https://www.indeed.com/viewjob?jk=ca44b855356ccf40</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>RapidSOS</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, IAM, Scala, Kafka, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c059e9218f7e23d</t>
+          <t>https://www.indeed.com/viewjob?jk=41f5f841b3bf67ad</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>RapidSOS</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, IAM, Scala, Kafka, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, MS Excel, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3986c9d7e69f169</t>
+          <t>https://www.indeed.com/viewjob?jk=af37d87136cf35b5</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Gen AI Platform &amp; Deployment Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Impala, Spark, Scala</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ad5e385a9b79a74</t>
+          <t>https://www.indeed.com/viewjob?jk=f28a43a00c1a7844</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Snowflake, Data Modeling, ETL, ELT, Jenkins, Maven, Docker</t>
+          <t>AWS, Glue, Lambda, Redshift, IAM, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,67 +4486,67 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=842f8f1cf0d90520</t>
+          <t>https://www.indeed.com/viewjob?jk=a2f5cef76808163a</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Backend Engineer II</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>HackerRank Careers</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4979e4cfe40ed8d</t>
+          <t>https://www.indeed.com/viewjob?jk=672dba9cce12de5f</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Voya Financial</t>
+          <t>Trepp</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Braintree, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, Kafka, Oracle, MySQL, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, S3, Spark, Scala, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,32 +4556,32 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f0f1071f3e2b14</t>
+          <t>https://www.indeed.com/viewjob?jk=d561d8c2375dd6b1</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
+          <t>Senior Infrastructure Engineer-Azure Data &amp; Analytics Engineer - State National</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>Markel Corporation</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>Bedford, TX, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,172 +4591,172 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d356cba46c60202</t>
+          <t>https://www.indeed.com/viewjob?jk=94507e2995b9ee29</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Multi-Cloud Networking Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nSCALE</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Barstow, TX, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Oracle, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ff8e0f386ef907b</t>
+          <t>https://www.indeed.com/viewjob?jk=bc6c300d9777dc4b</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer</t>
+          <t>Data Engineer - Seattle, WA</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Fueled</t>
+          <t>nSCALE</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9642665184944e11</t>
+          <t>https://www.indeed.com/viewjob?jk=894fb5b066595659</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1de30f12b78fca01</t>
+          <t>https://www.indeed.com/viewjob?jk=5b0780a9fb0dbc39</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Ads Targeting Data Engineer, Ads Core</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Hive, Spark, Scala, Kafka, Data Modeling, ETL, Airflow, Python</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88b23e7d0b05c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=cd2adeacdfffb183</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>DevOps / Platform Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Vivacity Tech PBC</t>
+          <t>University of Maryland Medical System</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>North Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Hadoop, HDFS, Hive, MapReduce, Spark, Scala, Oracle, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,67 +4766,67 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed1d3fe1d3532916</t>
+          <t>https://www.indeed.com/viewjob?jk=4188adfee24d1373</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Illumio</t>
+          <t>Empirx Health</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Databricks, Blob Storage, GCP, Scala, Kafka, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cad79b56c244d0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=df86a0c4dd78dfc1</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>DMV IT Service LLC</t>
+          <t>Ramp</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Richmond, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,67 +4836,67 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99e35b16ebbf3788</t>
+          <t>https://www.indeed.com/viewjob?jk=45e12b77b9565199</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>BI Engineer I (Hybrid)</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>NEUMO</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Fort Wayne, IN, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d2a5858f9149296</t>
+          <t>https://www.indeed.com/viewjob?jk=ab7793f0a792b417</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Software Engineer, Ads Infra - Serving and Foundation</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hive, Spark, Scala, Kafka, Data Modeling, ETL, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,172 +4906,172 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e26cb9e516d559dc</t>
+          <t>https://www.indeed.com/viewjob?jk=650677ad14cf645f</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>AI-ML Engineer 1</t>
+          <t>Senior Software Engineer Go Outdoors Payments</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Universal Avionics Systems Corporation</t>
+          <t>Brandt Information Services, Inc.</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Tucson, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Hadoop, Spark, Scala, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3e0f3955fde63ec</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f9736f5f852f3d</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Engineer Go Outdoors Payments</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Aroha Technologies</t>
+          <t>Brandt Information Services, Inc.</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e4069f2434551ab</t>
+          <t>https://www.indeed.com/viewjob?jk=e66c9de7a81a7d66</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>isolved</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Nixa, MO, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Azure Cosmos DB, NoSQL, dbt, CI/CD</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d13a0d2142e0261</t>
+          <t>https://www.indeed.com/viewjob?jk=185c1836bede91b1</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Pre-Sales Engineer (Data &amp; Analytics)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c940790b1550a5b</t>
+          <t>https://www.indeed.com/viewjob?jk=2cedfc80fbfee214</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Senior</t>
+          <t>Java Kafka Streams Developer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Mister Car Wash</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Tucson, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Databricks, Kafka, DynamoDB, ETL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,1652 +5081,42 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=414fb4f6d3a8dcd9</t>
+          <t>https://www.indeed.com/viewjob?jk=fc497768586e778b</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Software Engineer III (CJIS)</t>
+          <t>BI Developer Mid or Senior</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>County of San Luis Obispo</t>
+          <t>Progressive</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, SQL Server, MySQL, DynamoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, S3, Scala, Snowflake, SQL Server, ETL, ELT, dbt, Terraform</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cda7602e4b5904c</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Engineer</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Gametime United</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=24a25e68a1bd6d4f</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Warranty Data Analyst / Data Scientist</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Stellantis</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Auburn Hills, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2e9bb1ef1dd7ba48</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Warranty Data Analyst / Data Scientist</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Stellantis</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Auburn Hills, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2ffd491a76c9fa66</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Headspace</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cbb7191dcfe18f53</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Data/ Application Integration Engineer</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Charlie's Produce</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Oracle, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ca44b855356ccf40</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>DevOps/AI Ops Administrator</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, ELT</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=41f5f841b3bf67ad</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>AI Integration Engineer (Java + AI)</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, MS Excel, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=af37d87136cf35b5</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Mastercard</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Arlington, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Impala, Spark, Scala</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f28a43a00c1a7844</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>AWS Network Engineer</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Redshift, IAM, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a2f5cef76808163a</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Data Engineer III</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Simplot Company</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Boise, ID, US USA</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=672dba9cce12de5f</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Data Engineer II</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Trepp</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>AWS, Glue, EMR, Lambda, S3, Spark, Scala, Data Modeling, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d561d8c2375dd6b1</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Senior Infrastructure Engineer-Azure Data &amp; Analytics Engineer - State National</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Markel Corporation</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Bedford, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=94507e2995b9ee29</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Data Engineer II - Information Technology</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Board of Governors of the Federal Reserve System</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, PostgreSQL, NoSQL</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b222160bc0c2b3e3</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>nSCALE</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Barstow, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bc6c300d9777dc4b</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Data Engineer - Seattle, WA</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>nSCALE</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=894fb5b066595659</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Data Solution Engineer</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>SimilarWeb</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8e039b4fcb467133</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Engineer, Developer Platform (Cloud Apps)</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Motional</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, NoSQL, CI/CD, Jenkins, Terraform</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a10c8d4659b2bc91</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Envoy global</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>Azure, Blob Storage, Scala, SQL Server, Splunk, CI/CD, Azure DevOps, Terraform, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3d81e4212199a1a8</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Envoy global</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>Azure, Blob Storage, Scala, SQL Server, Splunk, CI/CD, Azure DevOps, Terraform, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d276b3164ac33893</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>SQL Engineer</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Mechanical Licensing Collective</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>AWS, Athena, RDS, Scala, Oracle, PostgreSQL, Data Modeling, Star Schema, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e3db429a534810fa</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Senior Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Alpaca</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>AWS, RDS, GCP, Spark, Scala, ETL, ELT, dbt, CI/CD, Airflow</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8cf5cd1df0f54fe6</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>jamf</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D156" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2ae2d7c352959fb2</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>AI Application Architect</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D157" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5b0780a9fb0dbc39</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Ads Targeting Data Engineer, Ads Core</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>TikTok</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D158" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Hive, Spark, Scala, Kafka, Data Modeling, ETL, Airflow, Python</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cd2adeacdfffb183</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>Sr Data Engineer</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>University of Maryland Medical System</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>North Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D159" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, HDFS, Hive, MapReduce, Spark, Scala, Oracle, PostgreSQL, MongoDB</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4188adfee24d1373</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>Senior Quality Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Circle.so</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D160" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3752971091aeeac9</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Platform &amp; Product</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Ware Malcomb</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D161" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aed0adf2e92986f6</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>Senior Specialist - Architecture (AI Engineer with Codex Exp.)</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>LTIMindtree</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Berkeley Heights, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D162" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Kafka, Data Modeling, MLOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=65c00c71c8e6928e</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>Software Engineer, Data Platform</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>Ramp</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D163" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Terraform, Airflow</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=45e12b77b9565199</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Senior Engineer - .NET</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D164" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ab7793f0a792b417</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>Senior Engineer - .NET</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D165" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=650677ad14cf645f</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>AI Integration Engineer (Java + AI)</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D166" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>Azure, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ff779f0dce63ada3</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>AI Integration Engineer (Java + AI)</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D167" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>Azure, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb55e9f7a6dc231</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>Empirx Health</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D168" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Blob Storage, GCP, Scala, Kafka, CI/CD, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c08697ee3f4bc0ba</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>Health-E Commerce</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D169" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, Scala, Data Modeling, ETL, Azure DevOps, Python</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=56afd442294fd678</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer Go Outdoors Payments</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>Brandt Information Services, Inc.</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D170" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f9736f5f852f3d</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer Go Outdoors Payments</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>Brandt Information Services, Inc.</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>Tallahassee, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D171" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e66c9de7a81a7d66</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>Sr. Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>Fairlife, LLC</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D172" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Star Schema, ELT, Power BI, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f203c334e20f61e9</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D173" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=185c1836bede91b1</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>Louisville, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D174" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2cedfc80fbfee214</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>Metropolis</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D175" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cd98e6c90182dad1</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>Metropolis</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D176" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1188cf2ae8e587af</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>Metropolis</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D177" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ec0dc8f9f8c8d698</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>BI Developer Mid or Senior</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>Progressive</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D178" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, Scala, Snowflake, SQL Server, ETL, ELT, dbt, Terraform</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=cdbb236dac23c233</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>Java Compliance &amp; Governance Developer</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>NC, US USA</t>
-        </is>
-      </c>
-      <c r="D179" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=243990c269c56673</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>Java Compliance &amp; Governance Developer</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>NC, US USA</t>
-        </is>
-      </c>
-      <c r="D180" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e9d53f3c6ff20349</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-23.xlsx
+++ b/results/job_matches_2026-04-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G134"/>
+  <dimension ref="A1:G123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Java Kafka Streams Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Climate First Bank</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,42 +766,42 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32602a30e2eae4db</t>
+          <t>https://www.indeed.com/viewjob?jk=7f16d1c6de9e445f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Java Kafka Streams Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Glastonbury, CT, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, Redshift, RDS, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f16d1c6de9e445f</t>
+          <t>https://www.indeed.com/viewjob?jk=861b456826f5b0c4</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Remote US</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Smile Digital Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, GCP, Cloud Storage, Scala, Kafka</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c0faea77dd1e82a</t>
+          <t>https://www.indeed.com/viewjob?jk=0672f1d449c9d9e2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Glastonbury, CT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,17 +871,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=861b456826f5b0c4</t>
+          <t>https://www.indeed.com/viewjob?jk=96a88c14093ccdaf</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0672f1d449c9d9e2</t>
+          <t>https://www.indeed.com/viewjob?jk=14f80cb5b125e7cc</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96a88c14093ccdaf</t>
+          <t>https://www.indeed.com/viewjob?jk=ca6623928abe2730</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f80cb5b125e7cc</t>
+          <t>https://www.indeed.com/viewjob?jk=46e364170a7ee29f</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca6623928abe2730</t>
+          <t>https://www.indeed.com/viewjob?jk=0e67913bb063b4e1</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46e364170a7ee29f</t>
+          <t>https://www.indeed.com/viewjob?jk=03e6278fa86f66b6</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e67913bb063b4e1</t>
+          <t>https://www.indeed.com/viewjob?jk=a417258c27e6884b</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e6278fa86f66b6</t>
+          <t>https://www.indeed.com/viewjob?jk=68ff6a6e54c5bb38</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a417258c27e6884b</t>
+          <t>https://www.indeed.com/viewjob?jk=b864420111578783</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68ff6a6e54c5bb38</t>
+          <t>https://www.indeed.com/viewjob?jk=90020927d62d9e32</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b864420111578783</t>
+          <t>https://www.indeed.com/viewjob?jk=e6445ef98b11402a</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90020927d62d9e32</t>
+          <t>https://www.indeed.com/viewjob?jk=63c85699934dff6e</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6445ef98b11402a</t>
+          <t>https://www.indeed.com/viewjob?jk=26b24994302869a9</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63c85699934dff6e</t>
+          <t>https://www.indeed.com/viewjob?jk=06b0116b71837d13</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26b24994302869a9</t>
+          <t>https://www.indeed.com/viewjob?jk=8120526ad261b6a4</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06b0116b71837d13</t>
+          <t>https://www.indeed.com/viewjob?jk=71be0c8c221ee567</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8120526ad261b6a4</t>
+          <t>https://www.indeed.com/viewjob?jk=ee059ac44d2277d6</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71be0c8c221ee567</t>
+          <t>https://www.indeed.com/viewjob?jk=af1a0c944d7d687c</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee059ac44d2277d6</t>
+          <t>https://www.indeed.com/viewjob?jk=a757acecac7ae896</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af1a0c944d7d687c</t>
+          <t>https://www.indeed.com/viewjob?jk=46cdcaa9c274907d</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a757acecac7ae896</t>
+          <t>https://www.indeed.com/viewjob?jk=0c545200255ccd75</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46cdcaa9c274907d</t>
+          <t>https://www.indeed.com/viewjob?jk=99c6d56e1e9ecbd9</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c545200255ccd75</t>
+          <t>https://www.indeed.com/viewjob?jk=ec2268853b5e3d32</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99c6d56e1e9ecbd9</t>
+          <t>https://www.indeed.com/viewjob?jk=cc317ad96269ff6c</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec2268853b5e3d32</t>
+          <t>https://www.indeed.com/viewjob?jk=2c59791ffa8037e0</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc317ad96269ff6c</t>
+          <t>https://www.indeed.com/viewjob?jk=93c00120a22fd95f</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c59791ffa8037e0</t>
+          <t>https://www.indeed.com/viewjob?jk=e5fd76a0505c1f45</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93c00120a22fd95f</t>
+          <t>https://www.indeed.com/viewjob?jk=52bda57a7eae91d3</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5fd76a0505c1f45</t>
+          <t>https://www.indeed.com/viewjob?jk=8d79924b7c683266</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52bda57a7eae91d3</t>
+          <t>https://www.indeed.com/viewjob?jk=18b51a17582c12e7</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d79924b7c683266</t>
+          <t>https://www.indeed.com/viewjob?jk=c239cf58c8fa1c71</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18b51a17582c12e7</t>
+          <t>https://www.indeed.com/viewjob?jk=d5a42ec359480e0d</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c239cf58c8fa1c71</t>
+          <t>https://www.indeed.com/viewjob?jk=5ed6224d65d164cb</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5a42ec359480e0d</t>
+          <t>https://www.indeed.com/viewjob?jk=ffcd6c03d59f6052</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ed6224d65d164cb</t>
+          <t>https://www.indeed.com/viewjob?jk=ddc6dd123946c0df</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffcd6c03d59f6052</t>
+          <t>https://www.indeed.com/viewjob?jk=2b026195b5394344</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddc6dd123946c0df</t>
+          <t>https://www.indeed.com/viewjob?jk=9ffe2cd40b6dd0e7</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b026195b5394344</t>
+          <t>https://www.indeed.com/viewjob?jk=2581b6e435257226</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ffe2cd40b6dd0e7</t>
+          <t>https://www.indeed.com/viewjob?jk=de24f7419929c1bf</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2581b6e435257226</t>
+          <t>https://www.indeed.com/viewjob?jk=5380c72e36e9ef3d</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de24f7419929c1bf</t>
+          <t>https://www.indeed.com/viewjob?jk=43d4c68e7e9e2fef</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5380c72e36e9ef3d</t>
+          <t>https://www.indeed.com/viewjob?jk=7a8557481e61c905</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43d4c68e7e9e2fef</t>
+          <t>https://www.indeed.com/viewjob?jk=af8a69205565050f</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a8557481e61c905</t>
+          <t>https://www.indeed.com/viewjob?jk=dfedec5986433f19</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af8a69205565050f</t>
+          <t>https://www.indeed.com/viewjob?jk=dadc73e392f990d3</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfedec5986433f19</t>
+          <t>https://www.indeed.com/viewjob?jk=df6f8697322180c6</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dadc73e392f990d3</t>
+          <t>https://www.indeed.com/viewjob?jk=b407a88f3a1f87f8</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df6f8697322180c6</t>
+          <t>https://www.indeed.com/viewjob?jk=ce6e6d7e4f41a3e8</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b407a88f3a1f87f8</t>
+          <t>https://www.indeed.com/viewjob?jk=1662c7096eaa5c34</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce6e6d7e4f41a3e8</t>
+          <t>https://www.indeed.com/viewjob?jk=9b54c062fe208581</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1662c7096eaa5c34</t>
+          <t>https://www.indeed.com/viewjob?jk=3ca77008309e43be</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Redshift, S3, Azure, Databricks, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b54c062fe208581</t>
+          <t>https://www.indeed.com/viewjob?jk=ede735cbdf2b63e0</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
+          <t>Sr. Platform Engineering</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>archer</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,137 +2701,137 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ca77008309e43be</t>
+          <t>https://www.indeed.com/viewjob?jk=e910893e7900f872</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Java Compliance &amp; Governance Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Azure, Databricks, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, Redshift, ECS, RDS, Scala, Kafka, MySQL, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ede735cbdf2b63e0</t>
+          <t>https://www.indeed.com/viewjob?jk=a09c947868c141e2</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (Data Modeling &amp; BI)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Keeper Security</t>
+          <t>Suvoda</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Conshohocken, PA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b319560288703a69</t>
+          <t>https://www.indeed.com/viewjob?jk=c1b69a2cd2e20538</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Verse</t>
+          <t>Suvoda</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, S3, RDS, Databricks, GCP, BigQuery, Hadoop, Hive, HBase</t>
+          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2169de43fedb76d3</t>
+          <t>https://www.indeed.com/viewjob?jk=ff6fc79a37f3e06f</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Platform Engineering</t>
+          <t>Data Engineer (AIA)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>archer</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e910893e7900f872</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f49ea5746dd899</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Java Compliance &amp; Governance Developer</t>
+          <t>Data Engineer (AIA)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, ECS, RDS, Scala, Kafka, MySQL, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a09c947868c141e2</t>
+          <t>https://www.indeed.com/viewjob?jk=422b5002f3c92e96</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer (AIA)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Suvoda</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Conshohocken, PA, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Spark, PySpark, Kafka</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1b69a2cd2e20538</t>
+          <t>https://www.indeed.com/viewjob?jk=4ca947b911b13d47</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer (AIA)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Suvoda</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Spark, PySpark, Kafka</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff6fc79a37f3e06f</t>
+          <t>https://www.indeed.com/viewjob?jk=2762492ad7551efe</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer (AIA)</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f49ea5746dd899</t>
+          <t>https://www.indeed.com/viewjob?jk=6a924e0d6d13cba9</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer (AIA)</t>
+          <t>Specialist Software Engineering</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Kinesis, S3, API Gateway, ECS, Event Hubs, Zookeeper, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,67 +3016,67 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=422b5002f3c92e96</t>
+          <t>https://www.indeed.com/viewjob?jk=66f8131b391d620e</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer (AIA)</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, API Gateway, ECS, Scala, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ca947b911b13d47</t>
+          <t>https://www.indeed.com/viewjob?jk=c0a2cb39a283363f</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer (AIA)</t>
+          <t>Senior DevOps Engineer II</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,137 +3086,137 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2762492ad7551efe</t>
+          <t>https://www.indeed.com/viewjob?jk=3af6a74b61fd0779</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer, Analytics &amp; Machine Learning Enablement</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Keeper Security</t>
+          <t>Gates Foundation</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, BigQuery, Scala, Snowflake</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, ELT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b569d0296983d6a1</t>
+          <t>https://www.indeed.com/viewjob?jk=d0e09f867e58f64d</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>AI Solution Architect</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Intellectyx</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Pasadena, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, PostgreSQL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a924e0d6d13cba9</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4d23e36ea1a698</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Cloud Platforms Engineer II</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SIGNITIVES</t>
+          <t>Amcor</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Oshkosh, WI, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Scala, Power BI, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccbfb275c784c26b</t>
+          <t>https://www.indeed.com/viewjob?jk=0a5bd8b939af9f70</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Specialist Software Engineering</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, API Gateway, ECS, Event Hubs, Zookeeper, Kafka, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,199 +3226,199 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f8131b391d620e</t>
+          <t>https://www.indeed.com/viewjob?jk=75e319e5ec133537</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Python Engineer</t>
+          <t>Sr Systems Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>N-iX</t>
+          <t>CEI Services</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fargo, ND, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Cloud Storage, Vertex AI, Scala, PostgreSQL, MySQL</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=365bb0b9ec3ce321</t>
+          <t>https://www.indeed.com/viewjob?jk=f846bcd41f966d19</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Sr Systems Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>MasTec Inc</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fargo, ND, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, API Gateway, ECS, Scala, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0a2cb39a283363f</t>
+          <t>https://www.indeed.com/viewjob?jk=ba06f08c24782d2d</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer II</t>
+          <t>Investment Compliance Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>Apollo</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af6a74b61fd0779</t>
+          <t>https://www.indeed.com/viewjob?jk=ef318708de3b36bf</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Software Engineer II - AI Solutions</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Gates Foundation</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0e09f867e58f64d</t>
+          <t>https://www.indeed.com/viewjob?jk=488caabc0de3fad8</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>AI Engineer - Insurance Domain - HYBRID</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Warren, NJ, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, S3, IAM, Snowflake, Data Modeling, ETL, ELT, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeda85e53ae1234a</t>
+          <t>https://www.indeed.com/viewjob?jk=842f8f1cf0d90520</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Cloud Platforms Engineer II</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Amcor</t>
+          <t>Voya Financial</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Oshkosh, WI, US USA</t>
+          <t>Braintree, MA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,24 +3426,24 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Scala, Power BI, CI/CD, Jenkins, Terraform</t>
+          <t>Azure, Databricks, Spark, Kafka, Oracle, MySQL, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a5bd8b939af9f70</t>
+          <t>https://www.indeed.com/viewjob?jk=06f0f1071f3e2b14</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Multi-Cloud Networking Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3457,11 +3457,11 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Scala, Oracle, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75e319e5ec133537</t>
+          <t>https://www.indeed.com/viewjob?jk=7ff8e0f386ef907b</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Sr Systems Engineer</t>
+          <t>Senior Systems Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CEI Services</t>
+          <t>Fueled</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Fargo, ND, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f846bcd41f966d19</t>
+          <t>https://www.indeed.com/viewjob?jk=9642665184944e11</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Sr Systems Engineer</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>MasTec Inc</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Fargo, ND, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,137 +3541,137 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba06f08c24782d2d</t>
+          <t>https://www.indeed.com/viewjob?jk=1de30f12b78fca01</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Gen AI Platform &amp; Deployment Engineer</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ad5e385a9b79a74</t>
+          <t>https://www.indeed.com/viewjob?jk=b88b23e7d0b05c8f</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI Solutions</t>
+          <t>DevOps / Platform Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Vivacity Tech PBC</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=488caabc0de3fad8</t>
+          <t>https://www.indeed.com/viewjob?jk=ed1d3fe1d3532916</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Snowflake, Data Modeling, ETL, ELT, Jenkins, Maven, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=842f8f1cf0d90520</t>
+          <t>https://www.indeed.com/viewjob?jk=4ac82b1c79d8bff3</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Software Engineer, Ads Infra - Serving and Foundation</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Voya Financial</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Braintree, MA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, Kafka, Oracle, MySQL, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Hive, Spark, Scala, Kafka, Data Modeling, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,59 +3681,59 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f0f1071f3e2b14</t>
+          <t>https://www.indeed.com/viewjob?jk=e26cb9e516d559dc</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
+          <t>Warranty Data Analyst / Data Scientist</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d356cba46c60202</t>
+          <t>https://www.indeed.com/viewjob?jk=82beb43a57ee8ec5</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Multi-Cloud Networking Engineer</t>
+          <t>Warranty Data Analyst / Data Scientist</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Oracle, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ff8e0f386ef907b</t>
+          <t>https://www.indeed.com/viewjob?jk=abdbd26974d27e06</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer</t>
+          <t>PIMS Data Analyst</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Fueled</t>
+          <t>Bechtel</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9642665184944e11</t>
+          <t>https://www.indeed.com/viewjob?jk=84332d95fe089578</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>isolved</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Nixa, MO, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Azure Cosmos DB, NoSQL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1de30f12b78fca01</t>
+          <t>https://www.indeed.com/viewjob?jk=3d13a0d2142e0261</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Pre-Sales Engineer (Data &amp; Analytics)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88b23e7d0b05c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=3c940790b1550a5b</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>DevOps / Platform Engineer</t>
+          <t>Warranty Data Analyst / Data Scientist</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Vivacity Tech PBC</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed1d3fe1d3532916</t>
+          <t>https://www.indeed.com/viewjob?jk=2e9bb1ef1dd7ba48</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Warranty Data Analyst / Data Scientist</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ac82b1c79d8bff3</t>
+          <t>https://www.indeed.com/viewjob?jk=2ffd491a76c9fa66</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Software Engineer, Ads Infra - Serving and Foundation</t>
+          <t>DevOps Engineer, Senior</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Mister Car Wash</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Tucson, AZ, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hive, Spark, Scala, Kafka, Data Modeling, ETL, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e26cb9e516d559dc</t>
+          <t>https://www.indeed.com/viewjob?jk=414fb4f6d3a8dcd9</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Warranty Data Analyst / Data Scientist</t>
+          <t>Software Engineer III (CJIS)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>County of San Luis Obispo</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, GCP, SQL Server, MySQL, DynamoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abdbd26974d27e06</t>
+          <t>https://www.indeed.com/viewjob?jk=2cda7602e4b5904c</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Senior</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Mister Car Wash</t>
+          <t>Buyers Edge Platform</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Tucson, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, PostgreSQL, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=414fb4f6d3a8dcd9</t>
+          <t>https://www.indeed.com/viewjob?jk=d278bb1777b2b1f7</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Software Engineer III (CJIS)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>County of San Luis Obispo</t>
+          <t>Buyers Edge Platform</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,42 +4056,42 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, SQL Server, MySQL, DynamoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, PostgreSQL, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cda7602e4b5904c</t>
+          <t>https://www.indeed.com/viewjob?jk=ab1768f1718284da</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>PIMS Data Analyst</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Bechtel</t>
+          <t>Apptronik</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, PostgreSQL, NoSQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,32 +4101,32 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84332d95fe089578</t>
+          <t>https://www.indeed.com/viewjob?jk=6c8a6b6744212463</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>isolved</t>
+          <t>Fustis LLC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Nixa, MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Azure Cosmos DB, NoSQL, dbt, CI/CD</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d13a0d2142e0261</t>
+          <t>https://www.indeed.com/viewjob?jk=7c7fe605c13e6870</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Pre-Sales Engineer (Data &amp; Analytics)</t>
+          <t>Data/ Application Integration Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Charlie's Produce</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Oracle, ETL, ELT</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,94 +4171,94 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c940790b1550a5b</t>
+          <t>https://www.indeed.com/viewjob?jk=ca44b855356ccf40</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Warranty Data Analyst / Data Scientist</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e9bb1ef1dd7ba48</t>
+          <t>https://www.indeed.com/viewjob?jk=41f5f841b3bf67ad</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Warranty Data Analyst / Data Scientist</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, MS Excel, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ffd491a76c9fa66</t>
+          <t>https://www.indeed.com/viewjob?jk=af37d87136cf35b5</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Apptronik</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, PostgreSQL, NoSQL, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Impala, Spark, Scala</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c8a6b6744212463</t>
+          <t>https://www.indeed.com/viewjob?jk=f28a43a00c1a7844</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Fustis LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, Lambda, Redshift, IAM, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c7fe605c13e6870</t>
+          <t>https://www.indeed.com/viewjob?jk=a2f5cef76808163a</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Data/ Application Integration Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Charlie's Produce</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Oracle, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca44b855356ccf40</t>
+          <t>https://www.indeed.com/viewjob?jk=672dba9cce12de5f</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Trepp</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, S3, Spark, Scala, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f5f841b3bf67ad</t>
+          <t>https://www.indeed.com/viewjob?jk=d561d8c2375dd6b1</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Senior Infrastructure Engineer-Azure Data &amp; Analytics Engineer - State National</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Markel Corporation</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Bedford, TX, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, MS Excel, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af37d87136cf35b5</t>
+          <t>https://www.indeed.com/viewjob?jk=94507e2995b9ee29</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Impala, Spark, Scala</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f28a43a00c1a7844</t>
+          <t>https://www.indeed.com/viewjob?jk=5b0780a9fb0dbc39</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Ads Targeting Data Engineer, Ads Core</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, IAM, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Hive, Spark, Scala, Kafka, Data Modeling, ETL, Airflow, Python</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2f5cef76808163a</t>
+          <t>https://www.indeed.com/viewjob?jk=cd2adeacdfffb183</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>Ramp</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=672dba9cce12de5f</t>
+          <t>https://www.indeed.com/viewjob?jk=45e12b77b9565199</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Trepp</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, Spark, Scala, Data Modeling, CI/CD, Git</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d561d8c2375dd6b1</t>
+          <t>https://www.indeed.com/viewjob?jk=185c1836bede91b1</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer-Azure Data &amp; Analytics Engineer - State National</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Markel Corporation</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Bedford, TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94507e2995b9ee29</t>
+          <t>https://www.indeed.com/viewjob?jk=2cedfc80fbfee214</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>nSCALE</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Barstow, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc6c300d9777dc4b</t>
+          <t>https://www.indeed.com/viewjob?jk=ab7793f0a792b417</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Data Engineer - Seattle, WA</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>nSCALE</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,24 +4651,24 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=894fb5b066595659</t>
+          <t>https://www.indeed.com/viewjob?jk=650677ad14cf645f</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Java Kafka Streams Developer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Databricks, Kafka, DynamoDB, ETL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b0780a9fb0dbc39</t>
+          <t>https://www.indeed.com/viewjob?jk=fc497768586e778b</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Ads Targeting Data Engineer, Ads Core</t>
+          <t>BI Developer Mid or Senior</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Progressive</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hive, Spark, Scala, Kafka, Data Modeling, ETL, Airflow, Python</t>
+          <t>AWS, Lambda, S3, Scala, Snowflake, SQL Server, ETL, ELT, dbt, Terraform</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4730,391 +4730,6 @@
         </is>
       </c>
       <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cd2adeacdfffb183</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Sr Data Engineer</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>University of Maryland Medical System</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>North Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, HDFS, Hive, MapReduce, Spark, Scala, Oracle, PostgreSQL, MongoDB</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4188adfee24d1373</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Empirx Health</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Blob Storage, GCP, Scala, Kafka, CI/CD, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=df86a0c4dd78dfc1</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Software Engineer, Data Platform</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Ramp</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Terraform, Airflow</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=45e12b77b9565199</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Senior Engineer - .NET</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ab7793f0a792b417</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Senior Engineer - .NET</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=650677ad14cf645f</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer Go Outdoors Payments</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Brandt Information Services, Inc.</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f9736f5f852f3d</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer Go Outdoors Payments</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Brandt Information Services, Inc.</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Tallahassee, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e66c9de7a81a7d66</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=185c1836bede91b1</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Louisville, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2cedfc80fbfee214</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Java Kafka Streams Developer</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>AWS, Databricks, Kafka, DynamoDB, ETL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fc497768586e778b</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>BI Developer Mid or Senior</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Progressive</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, Scala, Snowflake, SQL Server, ETL, ELT, dbt, Terraform</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=cdbb236dac23c233</t>
         </is>

--- a/results/job_matches_2026-04-23.xlsx
+++ b/results/job_matches_2026-04-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G123"/>
+  <dimension ref="A1:G125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,35 +503,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DOW</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e6f52d2577111f6</t>
+          <t>https://www.indeed.com/viewjob?jk=9a75bae8fe6b588f</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -566,19 +566,19 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a75bae8fe6b588f</t>
+          <t>https://www.indeed.com/viewjob?jk=be5d882b0154cb62</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate Data and AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -587,21 +587,21 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, EMR, Kinesis, Redshift, S3, RDS, GCP, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be5d882b0154cb62</t>
+          <t>https://www.indeed.com/viewjob?jk=718af7ca01e94aee</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=718af7ca01e94aee</t>
+          <t>https://www.indeed.com/viewjob?jk=10c4f60d661f5f00</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10c4f60d661f5f00</t>
+          <t>https://www.indeed.com/viewjob?jk=6f971eeb79a21180</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f971eeb79a21180</t>
+          <t>https://www.indeed.com/viewjob?jk=cfbf52f31ea2e787</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Associate Data and AI Engineer</t>
+          <t>Java Kafka Streams Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,42 +731,42 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, S3, RDS, GCP, Hadoop, Spark, Scala</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfbf52f31ea2e787</t>
+          <t>https://www.indeed.com/viewjob?jk=7f16d1c6de9e445f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Java Kafka Streams Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Glastonbury, CT, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, Redshift, RDS, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f16d1c6de9e445f</t>
+          <t>https://www.indeed.com/viewjob?jk=861b456826f5b0c4</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Glastonbury, CT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,17 +801,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=861b456826f5b0c4</t>
+          <t>https://www.indeed.com/viewjob?jk=0672f1d449c9d9e2</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0672f1d449c9d9e2</t>
+          <t>https://www.indeed.com/viewjob?jk=96a88c14093ccdaf</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96a88c14093ccdaf</t>
+          <t>https://www.indeed.com/viewjob?jk=14f80cb5b125e7cc</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f80cb5b125e7cc</t>
+          <t>https://www.indeed.com/viewjob?jk=ca6623928abe2730</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca6623928abe2730</t>
+          <t>https://www.indeed.com/viewjob?jk=46e364170a7ee29f</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46e364170a7ee29f</t>
+          <t>https://www.indeed.com/viewjob?jk=0e67913bb063b4e1</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e67913bb063b4e1</t>
+          <t>https://www.indeed.com/viewjob?jk=03e6278fa86f66b6</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e6278fa86f66b6</t>
+          <t>https://www.indeed.com/viewjob?jk=a417258c27e6884b</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a417258c27e6884b</t>
+          <t>https://www.indeed.com/viewjob?jk=68ff6a6e54c5bb38</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68ff6a6e54c5bb38</t>
+          <t>https://www.indeed.com/viewjob?jk=b864420111578783</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b864420111578783</t>
+          <t>https://www.indeed.com/viewjob?jk=90020927d62d9e32</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90020927d62d9e32</t>
+          <t>https://www.indeed.com/viewjob?jk=e6445ef98b11402a</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6445ef98b11402a</t>
+          <t>https://www.indeed.com/viewjob?jk=63c85699934dff6e</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63c85699934dff6e</t>
+          <t>https://www.indeed.com/viewjob?jk=26b24994302869a9</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26b24994302869a9</t>
+          <t>https://www.indeed.com/viewjob?jk=06b0116b71837d13</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06b0116b71837d13</t>
+          <t>https://www.indeed.com/viewjob?jk=8120526ad261b6a4</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8120526ad261b6a4</t>
+          <t>https://www.indeed.com/viewjob?jk=71be0c8c221ee567</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71be0c8c221ee567</t>
+          <t>https://www.indeed.com/viewjob?jk=ee059ac44d2277d6</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee059ac44d2277d6</t>
+          <t>https://www.indeed.com/viewjob?jk=af1a0c944d7d687c</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af1a0c944d7d687c</t>
+          <t>https://www.indeed.com/viewjob?jk=a757acecac7ae896</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a757acecac7ae896</t>
+          <t>https://www.indeed.com/viewjob?jk=46cdcaa9c274907d</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46cdcaa9c274907d</t>
+          <t>https://www.indeed.com/viewjob?jk=0c545200255ccd75</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c545200255ccd75</t>
+          <t>https://www.indeed.com/viewjob?jk=99c6d56e1e9ecbd9</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99c6d56e1e9ecbd9</t>
+          <t>https://www.indeed.com/viewjob?jk=ec2268853b5e3d32</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec2268853b5e3d32</t>
+          <t>https://www.indeed.com/viewjob?jk=cc317ad96269ff6c</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc317ad96269ff6c</t>
+          <t>https://www.indeed.com/viewjob?jk=2c59791ffa8037e0</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c59791ffa8037e0</t>
+          <t>https://www.indeed.com/viewjob?jk=93c00120a22fd95f</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93c00120a22fd95f</t>
+          <t>https://www.indeed.com/viewjob?jk=e5fd76a0505c1f45</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5fd76a0505c1f45</t>
+          <t>https://www.indeed.com/viewjob?jk=52bda57a7eae91d3</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52bda57a7eae91d3</t>
+          <t>https://www.indeed.com/viewjob?jk=8d79924b7c683266</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d79924b7c683266</t>
+          <t>https://www.indeed.com/viewjob?jk=18b51a17582c12e7</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18b51a17582c12e7</t>
+          <t>https://www.indeed.com/viewjob?jk=c239cf58c8fa1c71</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c239cf58c8fa1c71</t>
+          <t>https://www.indeed.com/viewjob?jk=d5a42ec359480e0d</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5a42ec359480e0d</t>
+          <t>https://www.indeed.com/viewjob?jk=5ed6224d65d164cb</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ed6224d65d164cb</t>
+          <t>https://www.indeed.com/viewjob?jk=ffcd6c03d59f6052</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffcd6c03d59f6052</t>
+          <t>https://www.indeed.com/viewjob?jk=ddc6dd123946c0df</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddc6dd123946c0df</t>
+          <t>https://www.indeed.com/viewjob?jk=2b026195b5394344</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b026195b5394344</t>
+          <t>https://www.indeed.com/viewjob?jk=9ffe2cd40b6dd0e7</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ffe2cd40b6dd0e7</t>
+          <t>https://www.indeed.com/viewjob?jk=2581b6e435257226</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2581b6e435257226</t>
+          <t>https://www.indeed.com/viewjob?jk=de24f7419929c1bf</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de24f7419929c1bf</t>
+          <t>https://www.indeed.com/viewjob?jk=5380c72e36e9ef3d</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5380c72e36e9ef3d</t>
+          <t>https://www.indeed.com/viewjob?jk=43d4c68e7e9e2fef</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43d4c68e7e9e2fef</t>
+          <t>https://www.indeed.com/viewjob?jk=7a8557481e61c905</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a8557481e61c905</t>
+          <t>https://www.indeed.com/viewjob?jk=af8a69205565050f</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af8a69205565050f</t>
+          <t>https://www.indeed.com/viewjob?jk=dfedec5986433f19</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfedec5986433f19</t>
+          <t>https://www.indeed.com/viewjob?jk=dadc73e392f990d3</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dadc73e392f990d3</t>
+          <t>https://www.indeed.com/viewjob?jk=df6f8697322180c6</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df6f8697322180c6</t>
+          <t>https://www.indeed.com/viewjob?jk=b407a88f3a1f87f8</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b407a88f3a1f87f8</t>
+          <t>https://www.indeed.com/viewjob?jk=ce6e6d7e4f41a3e8</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce6e6d7e4f41a3e8</t>
+          <t>https://www.indeed.com/viewjob?jk=1662c7096eaa5c34</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1662c7096eaa5c34</t>
+          <t>https://www.indeed.com/viewjob?jk=9b54c062fe208581</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,67 +2596,67 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b54c062fe208581</t>
+          <t>https://www.indeed.com/viewjob?jk=3ca77008309e43be</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
+          <t>Senior Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NitinX</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ca77008309e43be</t>
+          <t>https://www.indeed.com/viewjob?jk=20cbaecb52ef1e29</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Platform Engineering</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>archer</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Azure, Databricks, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,42 +2666,42 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ede735cbdf2b63e0</t>
+          <t>https://www.indeed.com/viewjob?jk=e910893e7900f872</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr. Platform Engineering</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>archer</t>
+          <t>CAI (Computer Aid, Inc.)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, GCP, BigQuery, Cloud Storage, Hadoop, Hive, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e910893e7900f872</t>
+          <t>https://www.indeed.com/viewjob?jk=69655961f8c3abc9</t>
         </is>
       </c>
     </row>
@@ -3303,17 +3303,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Investment Compliance Engineer</t>
+          <t>Software Engineer II - AI Solutions</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Apollo</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef318708de3b36bf</t>
+          <t>https://www.indeed.com/viewjob?jk=488caabc0de3fad8</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI Solutions</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, Snowflake, Data Modeling, ETL, ELT, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=488caabc0de3fad8</t>
+          <t>https://www.indeed.com/viewjob?jk=842f8f1cf0d90520</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Voya Financial</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Braintree, MA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Snowflake, Data Modeling, ETL, ELT, Jenkins, Maven, Docker</t>
+          <t>Azure, Databricks, Spark, Kafka, Oracle, MySQL, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=842f8f1cf0d90520</t>
+          <t>https://www.indeed.com/viewjob?jk=06f0f1071f3e2b14</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Investment Compliance Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Voya Financial</t>
+          <t>Apollo</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Braintree, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,17 +3426,17 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, Kafka, Oracle, MySQL, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f0f1071f3e2b14</t>
+          <t>https://www.indeed.com/viewjob?jk=ef318708de3b36bf</t>
         </is>
       </c>
     </row>
@@ -3898,17 +3898,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Warranty Data Analyst / Data Scientist</t>
+          <t>DevOps Engineer, Senior</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Mister Car Wash</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Tucson, AZ, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ffd491a76c9fa66</t>
+          <t>https://www.indeed.com/viewjob?jk=414fb4f6d3a8dcd9</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Senior</t>
+          <t>Software Engineer III (CJIS)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Mister Car Wash</t>
+          <t>County of San Luis Obispo</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Tucson, AZ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, SQL Server, MySQL, DynamoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=414fb4f6d3a8dcd9</t>
+          <t>https://www.indeed.com/viewjob?jk=2cda7602e4b5904c</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Software Engineer III (CJIS)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>County of San Luis Obispo</t>
+          <t>Buyers Edge Platform</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,17 +3986,17 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, SQL Server, MySQL, DynamoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, PostgreSQL, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cda7602e4b5904c</t>
+          <t>https://www.indeed.com/viewjob?jk=d278bb1777b2b1f7</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,32 +4031,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d278bb1777b2b1f7</t>
+          <t>https://www.indeed.com/viewjob?jk=ab1768f1718284da</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Buyers Edge Platform</t>
+          <t>Anteriad</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, PostgreSQL, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Cloud Storage, SQL Server, ETL, Azure DevOps</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab1768f1718284da</t>
+          <t>https://www.indeed.com/viewjob?jk=6d15d053831e0a70</t>
         </is>
       </c>
     </row>
@@ -4493,17 +4493,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Platform</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Ramp</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Terraform, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Jenkins, Maven, Jenkins</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45e12b77b9565199</t>
+          <t>https://www.indeed.com/viewjob?jk=541a9a3e6c8c6ce3</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Group Supply Chain Analyst</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Crane Aerospace &amp; Electronics</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Burbank, CA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Oracle, Data Modeling, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=185c1836bede91b1</t>
+          <t>https://www.indeed.com/viewjob?jk=be31ff28c647bb41</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Ramp</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cedfc80fbfee214</t>
+          <t>https://www.indeed.com/viewjob?jk=45e12b77b9565199</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab7793f0a792b417</t>
+          <t>https://www.indeed.com/viewjob?jk=185c1836bede91b1</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=650677ad14cf645f</t>
+          <t>https://www.indeed.com/viewjob?jk=2cedfc80fbfee214</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Java Kafka Streams Developer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Kafka, DynamoDB, ETL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc497768586e778b</t>
+          <t>https://www.indeed.com/viewjob?jk=ab7793f0a792b417</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>BI Developer Mid or Senior</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Progressive</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,15 +4721,85 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=650677ad14cf645f</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Java Kafka Streams Developer</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AWS, Databricks, Kafka, DynamoDB, ETL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc497768586e778b</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>BI Developer Mid or Senior</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Progressive</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
           <t>AWS, Lambda, S3, Scala, Snowflake, SQL Server, ETL, ELT, dbt, Terraform</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr">
+      <c r="F125" t="inlineStr">
         <is>
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr">
+      <c r="G125" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=cdbb236dac23c233</t>
         </is>

--- a/results/job_matches_2026-04-23.xlsx
+++ b/results/job_matches_2026-04-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G125"/>
+  <dimension ref="A1:G139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Associate Data and AI Engineer</t>
+          <t>Data Engineer – AWS Lakehouse (Remote)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>S-Techinfo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,17 +591,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, S3, RDS, GCP, Hadoop, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, SQS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=718af7ca01e94aee</t>
+          <t>https://www.indeed.com/viewjob?jk=d18335be1419a92a</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10c4f60d661f5f00</t>
+          <t>https://www.indeed.com/viewjob?jk=718af7ca01e94aee</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f971eeb79a21180</t>
+          <t>https://www.indeed.com/viewjob?jk=10c4f60d661f5f00</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfbf52f31ea2e787</t>
+          <t>https://www.indeed.com/viewjob?jk=6f971eeb79a21180</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Java Kafka Streams Developer</t>
+          <t>Associate Data and AI Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,42 +731,42 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, EMR, Kinesis, Redshift, S3, RDS, GCP, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f16d1c6de9e445f</t>
+          <t>https://www.indeed.com/viewjob?jk=cfbf52f31ea2e787</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Java Kafka Streams Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Glastonbury, CT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=861b456826f5b0c4</t>
+          <t>https://www.indeed.com/viewjob?jk=7f16d1c6de9e445f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Glastonbury, CT, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,17 +801,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Redshift, RDS, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0672f1d449c9d9e2</t>
+          <t>https://www.indeed.com/viewjob?jk=861b456826f5b0c4</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96a88c14093ccdaf</t>
+          <t>https://www.indeed.com/viewjob?jk=0672f1d449c9d9e2</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f80cb5b125e7cc</t>
+          <t>https://www.indeed.com/viewjob?jk=96a88c14093ccdaf</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca6623928abe2730</t>
+          <t>https://www.indeed.com/viewjob?jk=14f80cb5b125e7cc</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46e364170a7ee29f</t>
+          <t>https://www.indeed.com/viewjob?jk=ca6623928abe2730</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e67913bb063b4e1</t>
+          <t>https://www.indeed.com/viewjob?jk=46e364170a7ee29f</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e6278fa86f66b6</t>
+          <t>https://www.indeed.com/viewjob?jk=0e67913bb063b4e1</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a417258c27e6884b</t>
+          <t>https://www.indeed.com/viewjob?jk=03e6278fa86f66b6</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68ff6a6e54c5bb38</t>
+          <t>https://www.indeed.com/viewjob?jk=a417258c27e6884b</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b864420111578783</t>
+          <t>https://www.indeed.com/viewjob?jk=68ff6a6e54c5bb38</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90020927d62d9e32</t>
+          <t>https://www.indeed.com/viewjob?jk=b864420111578783</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6445ef98b11402a</t>
+          <t>https://www.indeed.com/viewjob?jk=90020927d62d9e32</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63c85699934dff6e</t>
+          <t>https://www.indeed.com/viewjob?jk=e6445ef98b11402a</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26b24994302869a9</t>
+          <t>https://www.indeed.com/viewjob?jk=63c85699934dff6e</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06b0116b71837d13</t>
+          <t>https://www.indeed.com/viewjob?jk=26b24994302869a9</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8120526ad261b6a4</t>
+          <t>https://www.indeed.com/viewjob?jk=06b0116b71837d13</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71be0c8c221ee567</t>
+          <t>https://www.indeed.com/viewjob?jk=8120526ad261b6a4</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee059ac44d2277d6</t>
+          <t>https://www.indeed.com/viewjob?jk=71be0c8c221ee567</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af1a0c944d7d687c</t>
+          <t>https://www.indeed.com/viewjob?jk=ee059ac44d2277d6</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a757acecac7ae896</t>
+          <t>https://www.indeed.com/viewjob?jk=af1a0c944d7d687c</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46cdcaa9c274907d</t>
+          <t>https://www.indeed.com/viewjob?jk=a757acecac7ae896</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c545200255ccd75</t>
+          <t>https://www.indeed.com/viewjob?jk=46cdcaa9c274907d</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99c6d56e1e9ecbd9</t>
+          <t>https://www.indeed.com/viewjob?jk=0c545200255ccd75</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec2268853b5e3d32</t>
+          <t>https://www.indeed.com/viewjob?jk=99c6d56e1e9ecbd9</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc317ad96269ff6c</t>
+          <t>https://www.indeed.com/viewjob?jk=ec2268853b5e3d32</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c59791ffa8037e0</t>
+          <t>https://www.indeed.com/viewjob?jk=cc317ad96269ff6c</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93c00120a22fd95f</t>
+          <t>https://www.indeed.com/viewjob?jk=2c59791ffa8037e0</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5fd76a0505c1f45</t>
+          <t>https://www.indeed.com/viewjob?jk=93c00120a22fd95f</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52bda57a7eae91d3</t>
+          <t>https://www.indeed.com/viewjob?jk=e5fd76a0505c1f45</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d79924b7c683266</t>
+          <t>https://www.indeed.com/viewjob?jk=52bda57a7eae91d3</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18b51a17582c12e7</t>
+          <t>https://www.indeed.com/viewjob?jk=8d79924b7c683266</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c239cf58c8fa1c71</t>
+          <t>https://www.indeed.com/viewjob?jk=18b51a17582c12e7</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5a42ec359480e0d</t>
+          <t>https://www.indeed.com/viewjob?jk=c239cf58c8fa1c71</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ed6224d65d164cb</t>
+          <t>https://www.indeed.com/viewjob?jk=d5a42ec359480e0d</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffcd6c03d59f6052</t>
+          <t>https://www.indeed.com/viewjob?jk=5ed6224d65d164cb</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddc6dd123946c0df</t>
+          <t>https://www.indeed.com/viewjob?jk=ffcd6c03d59f6052</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b026195b5394344</t>
+          <t>https://www.indeed.com/viewjob?jk=ddc6dd123946c0df</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ffe2cd40b6dd0e7</t>
+          <t>https://www.indeed.com/viewjob?jk=2b026195b5394344</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2581b6e435257226</t>
+          <t>https://www.indeed.com/viewjob?jk=9ffe2cd40b6dd0e7</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de24f7419929c1bf</t>
+          <t>https://www.indeed.com/viewjob?jk=2581b6e435257226</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5380c72e36e9ef3d</t>
+          <t>https://www.indeed.com/viewjob?jk=de24f7419929c1bf</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43d4c68e7e9e2fef</t>
+          <t>https://www.indeed.com/viewjob?jk=5380c72e36e9ef3d</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a8557481e61c905</t>
+          <t>https://www.indeed.com/viewjob?jk=43d4c68e7e9e2fef</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af8a69205565050f</t>
+          <t>https://www.indeed.com/viewjob?jk=7a8557481e61c905</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfedec5986433f19</t>
+          <t>https://www.indeed.com/viewjob?jk=af8a69205565050f</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dadc73e392f990d3</t>
+          <t>https://www.indeed.com/viewjob?jk=dfedec5986433f19</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df6f8697322180c6</t>
+          <t>https://www.indeed.com/viewjob?jk=dadc73e392f990d3</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b407a88f3a1f87f8</t>
+          <t>https://www.indeed.com/viewjob?jk=df6f8697322180c6</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce6e6d7e4f41a3e8</t>
+          <t>https://www.indeed.com/viewjob?jk=b407a88f3a1f87f8</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1662c7096eaa5c34</t>
+          <t>https://www.indeed.com/viewjob?jk=ce6e6d7e4f41a3e8</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b54c062fe208581</t>
+          <t>https://www.indeed.com/viewjob?jk=1662c7096eaa5c34</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,77 +2596,77 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ca77008309e43be</t>
+          <t>https://www.indeed.com/viewjob?jk=9b54c062fe208581</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Software Engineer</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>NitinX</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20cbaecb52ef1e29</t>
+          <t>https://www.indeed.com/viewjob?jk=3ca77008309e43be</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr. Platform Engineering</t>
+          <t>Senior Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>archer</t>
+          <t>NitinX</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e910893e7900f872</t>
+          <t>https://www.indeed.com/viewjob?jk=20cbaecb52ef1e29</t>
         </is>
       </c>
     </row>
@@ -2708,17 +2708,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Java Compliance &amp; Governance Developer</t>
+          <t>Data Engineer (AIA)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, ECS, RDS, Scala, Kafka, MySQL, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a09c947868c141e2</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f49ea5746dd899</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer (AIA)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Suvoda</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Conshohocken, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Spark, PySpark, Kafka</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1b69a2cd2e20538</t>
+          <t>https://www.indeed.com/viewjob?jk=422b5002f3c92e96</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer (AIA)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Suvoda</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,17 +2796,17 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Spark, PySpark, Kafka</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff6fc79a37f3e06f</t>
+          <t>https://www.indeed.com/viewjob?jk=4ca947b911b13d47</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f49ea5746dd899</t>
+          <t>https://www.indeed.com/viewjob?jk=2762492ad7551efe</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer (AIA)</t>
+          <t>Java Compliance &amp; Governance Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Redshift, ECS, RDS, Scala, Kafka, MySQL, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=422b5002f3c92e96</t>
+          <t>https://www.indeed.com/viewjob?jk=a09c947868c141e2</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer (AIA)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Suvoda</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Conshohocken, PA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ca947b911b13d47</t>
+          <t>https://www.indeed.com/viewjob?jk=c1b69a2cd2e20538</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer (AIA)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Suvoda</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,17 +2936,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2762492ad7551efe</t>
+          <t>https://www.indeed.com/viewjob?jk=ff6fc79a37f3e06f</t>
         </is>
       </c>
     </row>
@@ -3023,25 +3023,25 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Analytics, Full-Stack Engineer (Agency Temp)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, API Gateway, ECS, Scala, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0a2cb39a283363f</t>
+          <t>https://www.indeed.com/viewjob?jk=78330a31d3de60c8</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer II</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, API Gateway, ECS, Scala, ETL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af6a74b61fd0779</t>
+          <t>https://www.indeed.com/viewjob?jk=c0a2cb39a283363f</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior DevOps Engineer II</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Gates Foundation</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, ELT</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0e09f867e58f64d</t>
+          <t>https://www.indeed.com/viewjob?jk=3af6a74b61fd0779</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AI Solution Architect</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Intellectyx</t>
+          <t>Gates Foundation</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Pasadena, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,42 +3146,42 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, PostgreSQL, Power BI, Tableau</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, ELT</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4d23e36ea1a698</t>
+          <t>https://www.indeed.com/viewjob?jk=d0e09f867e58f64d</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Cloud Platforms Engineer II</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Amcor</t>
+          <t>Acxiom</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Oshkosh, WI, US USA</t>
+          <t>Conway, AR, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Scala, Power BI, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Lambda, API Gateway, ECS, IAM, RDS, Scala, Oracle, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,59 +3191,59 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a5bd8b939af9f70</t>
+          <t>https://www.indeed.com/viewjob?jk=a4a59c922032170a</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>AI Solution Architect</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Intellectyx</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Pasadena, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, PostgreSQL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75e319e5ec133537</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4d23e36ea1a698</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr Systems Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CEI Services</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Fargo, ND, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f846bcd41f966d19</t>
+          <t>https://www.indeed.com/viewjob?jk=75e319e5ec133537</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr Systems Engineer</t>
+          <t>Cloud Platforms Engineer II</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>MasTec Inc</t>
+          <t>Amcor</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Fargo, ND, US USA</t>
+          <t>Oshkosh, WI, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Scala, Power BI, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba06f08c24782d2d</t>
+          <t>https://www.indeed.com/viewjob?jk=0a5bd8b939af9f70</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI Solutions</t>
+          <t>Sr Systems Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CEI Services</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Fargo, ND, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=488caabc0de3fad8</t>
+          <t>https://www.indeed.com/viewjob?jk=f846bcd41f966d19</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Systems Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>MasTec Inc</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Fargo, ND, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Snowflake, Data Modeling, ETL, ELT, Jenkins, Maven, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=842f8f1cf0d90520</t>
+          <t>https://www.indeed.com/viewjob?jk=ba06f08c24782d2d</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Voya Financial</t>
+          <t>Books-A-Million</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Braintree, MA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, Kafka, Oracle, MySQL, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f0f1071f3e2b14</t>
+          <t>https://www.indeed.com/viewjob?jk=dd3b3b5af84f7f50</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Investment Compliance Engineer</t>
+          <t>AWS Integration Architect (Hybrid)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Apollo</t>
+          <t>Signet Jewelers</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Coppell, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,172 +3436,172 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef318708de3b36bf</t>
+          <t>https://www.indeed.com/viewjob?jk=eb0ac24378fc5967</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Multi-Cloud Networking Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Hightower Advisors</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Oracle, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ff8e0f386ef907b</t>
+          <t>https://www.indeed.com/viewjob?jk=6f56b57a377fe3a0</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer</t>
+          <t>SENIOR ENTERPRISE DATA ARCHITECT</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Fueled</t>
+          <t>U.S. Marine Corps</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Quantico, VA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9642665184944e11</t>
+          <t>https://www.indeed.com/viewjob?jk=3977bc6913228407</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Software Engineer II - AI Solutions</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1de30f12b78fca01</t>
+          <t>https://www.indeed.com/viewjob?jk=488caabc0de3fad8</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Veridic Solutions</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88b23e7d0b05c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=000191587a0bd612</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>DevOps / Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Vivacity Tech PBC</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, S3, IAM, Snowflake, Data Modeling, ETL, ELT, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,94 +3611,94 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed1d3fe1d3532916</t>
+          <t>https://www.indeed.com/viewjob?jk=842f8f1cf0d90520</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Voya Financial</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Braintree, MA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
+          <t>Azure, Databricks, Spark, Kafka, Oracle, MySQL, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ac82b1c79d8bff3</t>
+          <t>https://www.indeed.com/viewjob?jk=06f0f1071f3e2b14</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Engineer, Ads Infra - Serving and Foundation</t>
+          <t>Investment Compliance Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Apollo</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hive, Spark, Scala, Kafka, Data Modeling, ETL, Airflow, Git</t>
+          <t>AWS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e26cb9e516d559dc</t>
+          <t>https://www.indeed.com/viewjob?jk=ef318708de3b36bf</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Warranty Data Analyst / Data Scientist</t>
+          <t>Senior Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Chime</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Spark, Scala, Snowflake, ETL, Maven</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82beb43a57ee8ec5</t>
+          <t>https://www.indeed.com/viewjob?jk=3c132b6601f3c0c7</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Warranty Data Analyst / Data Scientist</t>
+          <t>Asset &amp; Wealth Management - Software Engineer - Associate - Dallas</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Scala, Kafka, MongoDB, NoSQL, CI/CD, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abdbd26974d27e06</t>
+          <t>https://www.indeed.com/viewjob?jk=0b0170a8c239abcc</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>PIMS Data Analyst</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Bechtel</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, ETL</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84332d95fe089578</t>
+          <t>https://www.indeed.com/viewjob?jk=4ac82b1c79d8bff3</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Software Engineer, Ads Infra - Serving and Foundation</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>isolved</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Nixa, MO, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,24 +3811,24 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Azure Cosmos DB, NoSQL, dbt, CI/CD</t>
+          <t>AWS, RDS, Hive, Spark, Scala, Kafka, Data Modeling, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d13a0d2142e0261</t>
+          <t>https://www.indeed.com/viewjob?jk=e26cb9e516d559dc</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Pre-Sales Engineer (Data &amp; Analytics)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, Airflow</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c940790b1550a5b</t>
+          <t>https://www.indeed.com/viewjob?jk=4d9e130e5057c468</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Warranty Data Analyst / Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, Airflow</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e9bb1ef1dd7ba48</t>
+          <t>https://www.indeed.com/viewjob?jk=35f42b8dd196f861</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Senior</t>
+          <t>Multi-Cloud Networking Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Mister Car Wash</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Tucson, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Scala, Oracle, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=414fb4f6d3a8dcd9</t>
+          <t>https://www.indeed.com/viewjob?jk=7ff8e0f386ef907b</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Software Engineer III (CJIS)</t>
+          <t>Senior Systems Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>County of San Luis Obispo</t>
+          <t>Fueled</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, SQL Server, MySQL, DynamoDB, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cda7602e4b5904c</t>
+          <t>https://www.indeed.com/viewjob?jk=9642665184944e11</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Buyers Edge Platform</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, PostgreSQL, Git</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d278bb1777b2b1f7</t>
+          <t>https://www.indeed.com/viewjob?jk=1de30f12b78fca01</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Buyers Edge Platform</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,29 +4021,29 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, PostgreSQL, Git</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab1768f1718284da</t>
+          <t>https://www.indeed.com/viewjob?jk=b88b23e7d0b05c8f</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps / Platform Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Anteriad</t>
+          <t>Vivacity Tech PBC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4052,46 +4052,46 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Cloud Storage, SQL Server, ETL, Azure DevOps</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d15d053831e0a70</t>
+          <t>https://www.indeed.com/viewjob?jk=ed1d3fe1d3532916</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Warranty Data Analyst / Data Scientist</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Apptronik</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, PostgreSQL, NoSQL, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,32 +4101,32 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c8a6b6744212463</t>
+          <t>https://www.indeed.com/viewjob?jk=82beb43a57ee8ec5</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Warranty Data Analyst / Data Scientist</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Fustis LLC</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c7fe605c13e6870</t>
+          <t>https://www.indeed.com/viewjob?jk=abdbd26974d27e06</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Data/ Application Integration Engineer</t>
+          <t>PIMS Data Analyst</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Charlie's Produce</t>
+          <t>Bechtel</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Oracle, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca44b855356ccf40</t>
+          <t>https://www.indeed.com/viewjob?jk=84332d95fe089578</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>isolved</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nixa, MO, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, ELT</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Azure Cosmos DB, NoSQL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,32 +4206,32 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f5f841b3bf67ad</t>
+          <t>https://www.indeed.com/viewjob?jk=3d13a0d2142e0261</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Pre-Sales Engineer (Data &amp; Analytics)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, MS Excel, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,32 +4241,32 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af37d87136cf35b5</t>
+          <t>https://www.indeed.com/viewjob?jk=3c940790b1550a5b</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Warranty Data Analyst / Data Scientist</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Impala, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,67 +4276,67 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f28a43a00c1a7844</t>
+          <t>https://www.indeed.com/viewjob?jk=2e9bb1ef1dd7ba48</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>DevOps Engineer, Senior</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Mister Car Wash</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tucson, AZ, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, IAM, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2f5cef76808163a</t>
+          <t>https://www.indeed.com/viewjob?jk=414fb4f6d3a8dcd9</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Software Engineer III (CJIS)</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>County of San Luis Obispo</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, SQL Server, MySQL, DynamoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,94 +4346,94 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=672dba9cce12de5f</t>
+          <t>https://www.indeed.com/viewjob?jk=2cda7602e4b5904c</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Trepp</t>
+          <t>Buyers Edge Platform</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, Spark, Scala, Data Modeling, CI/CD, Git</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, PostgreSQL, Git</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d561d8c2375dd6b1</t>
+          <t>https://www.indeed.com/viewjob?jk=d278bb1777b2b1f7</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer-Azure Data &amp; Analytics Engineer - State National</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Markel Corporation</t>
+          <t>Buyers Edge Platform</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Bedford, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, PostgreSQL, Git</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94507e2995b9ee29</t>
+          <t>https://www.indeed.com/viewjob?jk=ab1768f1718284da</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Software Developer - Information Governance</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Epiq</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, NoSQL, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git, SQL</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b0780a9fb0dbc39</t>
+          <t>https://www.indeed.com/viewjob?jk=88087b3c950df52e</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Ads Targeting Data Engineer, Ads Core</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hive, Spark, Scala, Kafka, Data Modeling, ETL, Airflow, Python</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd2adeacdfffb183</t>
+          <t>https://www.indeed.com/viewjob?jk=5b0780a9fb0dbc39</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Ads Targeting Data Engineer, Ads Core</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Jenkins, Maven, Jenkins</t>
+          <t>AWS, RDS, Hive, Spark, Scala, Kafka, Data Modeling, ETL, Airflow, Python</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=541a9a3e6c8c6ce3</t>
+          <t>https://www.indeed.com/viewjob?jk=cd2adeacdfffb183</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Sr. Group Supply Chain Analyst</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Crane Aerospace &amp; Electronics</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Burbank, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,29 +4546,29 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Oracle, Data Modeling, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Impala, Spark, Scala</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be31ff28c647bb41</t>
+          <t>https://www.indeed.com/viewjob?jk=f28a43a00c1a7844</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Platform</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Ramp</t>
+          <t>Trepp</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Terraform, Airflow</t>
+          <t>AWS, Glue, EMR, Lambda, S3, Spark, Scala, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45e12b77b9565199</t>
+          <t>https://www.indeed.com/viewjob?jk=d561d8c2375dd6b1</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Anteriad</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Cloud Storage, SQL Server, ETL, Azure DevOps</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=185c1836bede91b1</t>
+          <t>https://www.indeed.com/viewjob?jk=6d15d053831e0a70</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Apptronik</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, PostgreSQL, NoSQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cedfc80fbfee214</t>
+          <t>https://www.indeed.com/viewjob?jk=6c8a6b6744212463</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Fustis LLC</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab7793f0a792b417</t>
+          <t>https://www.indeed.com/viewjob?jk=7c7fe605c13e6870</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Data/ Application Integration Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Charlie's Produce</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,24 +4721,24 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Oracle, ETL, ELT</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=650677ad14cf645f</t>
+          <t>https://www.indeed.com/viewjob?jk=ca44b855356ccf40</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Java Kafka Streams Developer</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Kafka, DynamoDB, ETL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc497768586e778b</t>
+          <t>https://www.indeed.com/viewjob?jk=41f5f841b3bf67ad</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>BI Developer Mid or Senior</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Progressive</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,15 +4791,505 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
+          <t>AWS, Azure, Google Cloud Platform, Scala, MS Excel, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=af37d87136cf35b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>AWS Network Engineer</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Redshift, IAM, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a2f5cef76808163a</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Data Engineer III</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Simplot Company</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Boise, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=672dba9cce12de5f</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Senior Infrastructure Engineer-Azure Data &amp; Analytics Engineer - State National</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Markel Corporation</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Bedford, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=94507e2995b9ee29</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Engineer</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Revstar</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Athena, S3, RDS, Scala, DynamoDB, Amazon QuickSight, MLOps</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c1c509a2c5d165cf</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Engineer</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Revstar</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Athena, S3, RDS, Scala, DynamoDB, Amazon QuickSight, MLOps</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=16029f18260b23a7</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Engineer</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Revstar</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>FL, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Athena, S3, RDS, Scala, DynamoDB, Amazon QuickSight, MLOps</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=585c6ab4414e23c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Software Engineer, Data Platform</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Terraform, Airflow</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=45e12b77b9565199</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=185c1836bede91b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2cedfc80fbfee214</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Truist</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Jenkins, Maven, Jenkins</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=541a9a3e6c8c6ce3</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Senior Engineer - .NET</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ab7793f0a792b417</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Senior Engineer - .NET</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=650677ad14cf645f</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Java Kafka Streams Developer</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AWS, Databricks, Kafka, DynamoDB, ETL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc497768586e778b</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>BI Developer Mid or Senior</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Progressive</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
           <t>AWS, Lambda, S3, Scala, Snowflake, SQL Server, ETL, ELT, dbt, Terraform</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr">
+      <c r="F139" t="inlineStr">
         <is>
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr">
+      <c r="G139" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=cdbb236dac23c233</t>
         </is>

--- a/results/job_matches_2026-04-23.xlsx
+++ b/results/job_matches_2026-04-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G139"/>
+  <dimension ref="A1:G126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,17 +783,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analytics &amp; BI Spclst 3 or Sr</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>MidAmerican Energy</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Glastonbury, CT, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=861b456826f5b0c4</t>
+          <t>https://www.indeed.com/viewjob?jk=bb9c48f1459d1dac</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Glastonbury, CT, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,17 +836,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Redshift, RDS, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0672f1d449c9d9e2</t>
+          <t>https://www.indeed.com/viewjob?jk=861b456826f5b0c4</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96a88c14093ccdaf</t>
+          <t>https://www.indeed.com/viewjob?jk=0672f1d449c9d9e2</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f80cb5b125e7cc</t>
+          <t>https://www.indeed.com/viewjob?jk=96a88c14093ccdaf</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca6623928abe2730</t>
+          <t>https://www.indeed.com/viewjob?jk=14f80cb5b125e7cc</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46e364170a7ee29f</t>
+          <t>https://www.indeed.com/viewjob?jk=ca6623928abe2730</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e67913bb063b4e1</t>
+          <t>https://www.indeed.com/viewjob?jk=46e364170a7ee29f</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e6278fa86f66b6</t>
+          <t>https://www.indeed.com/viewjob?jk=0e67913bb063b4e1</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a417258c27e6884b</t>
+          <t>https://www.indeed.com/viewjob?jk=03e6278fa86f66b6</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68ff6a6e54c5bb38</t>
+          <t>https://www.indeed.com/viewjob?jk=a417258c27e6884b</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b864420111578783</t>
+          <t>https://www.indeed.com/viewjob?jk=68ff6a6e54c5bb38</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90020927d62d9e32</t>
+          <t>https://www.indeed.com/viewjob?jk=b864420111578783</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6445ef98b11402a</t>
+          <t>https://www.indeed.com/viewjob?jk=90020927d62d9e32</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63c85699934dff6e</t>
+          <t>https://www.indeed.com/viewjob?jk=e6445ef98b11402a</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26b24994302869a9</t>
+          <t>https://www.indeed.com/viewjob?jk=63c85699934dff6e</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06b0116b71837d13</t>
+          <t>https://www.indeed.com/viewjob?jk=26b24994302869a9</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8120526ad261b6a4</t>
+          <t>https://www.indeed.com/viewjob?jk=06b0116b71837d13</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71be0c8c221ee567</t>
+          <t>https://www.indeed.com/viewjob?jk=8120526ad261b6a4</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee059ac44d2277d6</t>
+          <t>https://www.indeed.com/viewjob?jk=71be0c8c221ee567</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af1a0c944d7d687c</t>
+          <t>https://www.indeed.com/viewjob?jk=ee059ac44d2277d6</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a757acecac7ae896</t>
+          <t>https://www.indeed.com/viewjob?jk=af1a0c944d7d687c</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46cdcaa9c274907d</t>
+          <t>https://www.indeed.com/viewjob?jk=a757acecac7ae896</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c545200255ccd75</t>
+          <t>https://www.indeed.com/viewjob?jk=46cdcaa9c274907d</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99c6d56e1e9ecbd9</t>
+          <t>https://www.indeed.com/viewjob?jk=0c545200255ccd75</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec2268853b5e3d32</t>
+          <t>https://www.indeed.com/viewjob?jk=99c6d56e1e9ecbd9</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc317ad96269ff6c</t>
+          <t>https://www.indeed.com/viewjob?jk=ec2268853b5e3d32</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c59791ffa8037e0</t>
+          <t>https://www.indeed.com/viewjob?jk=cc317ad96269ff6c</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93c00120a22fd95f</t>
+          <t>https://www.indeed.com/viewjob?jk=2c59791ffa8037e0</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5fd76a0505c1f45</t>
+          <t>https://www.indeed.com/viewjob?jk=93c00120a22fd95f</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52bda57a7eae91d3</t>
+          <t>https://www.indeed.com/viewjob?jk=e5fd76a0505c1f45</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d79924b7c683266</t>
+          <t>https://www.indeed.com/viewjob?jk=52bda57a7eae91d3</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18b51a17582c12e7</t>
+          <t>https://www.indeed.com/viewjob?jk=8d79924b7c683266</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c239cf58c8fa1c71</t>
+          <t>https://www.indeed.com/viewjob?jk=18b51a17582c12e7</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5a42ec359480e0d</t>
+          <t>https://www.indeed.com/viewjob?jk=c239cf58c8fa1c71</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ed6224d65d164cb</t>
+          <t>https://www.indeed.com/viewjob?jk=d5a42ec359480e0d</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffcd6c03d59f6052</t>
+          <t>https://www.indeed.com/viewjob?jk=5ed6224d65d164cb</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddc6dd123946c0df</t>
+          <t>https://www.indeed.com/viewjob?jk=ffcd6c03d59f6052</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b026195b5394344</t>
+          <t>https://www.indeed.com/viewjob?jk=ddc6dd123946c0df</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ffe2cd40b6dd0e7</t>
+          <t>https://www.indeed.com/viewjob?jk=2b026195b5394344</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2581b6e435257226</t>
+          <t>https://www.indeed.com/viewjob?jk=9ffe2cd40b6dd0e7</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de24f7419929c1bf</t>
+          <t>https://www.indeed.com/viewjob?jk=2581b6e435257226</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5380c72e36e9ef3d</t>
+          <t>https://www.indeed.com/viewjob?jk=de24f7419929c1bf</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43d4c68e7e9e2fef</t>
+          <t>https://www.indeed.com/viewjob?jk=5380c72e36e9ef3d</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a8557481e61c905</t>
+          <t>https://www.indeed.com/viewjob?jk=43d4c68e7e9e2fef</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af8a69205565050f</t>
+          <t>https://www.indeed.com/viewjob?jk=7a8557481e61c905</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfedec5986433f19</t>
+          <t>https://www.indeed.com/viewjob?jk=af8a69205565050f</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dadc73e392f990d3</t>
+          <t>https://www.indeed.com/viewjob?jk=dfedec5986433f19</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df6f8697322180c6</t>
+          <t>https://www.indeed.com/viewjob?jk=dadc73e392f990d3</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b407a88f3a1f87f8</t>
+          <t>https://www.indeed.com/viewjob?jk=df6f8697322180c6</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce6e6d7e4f41a3e8</t>
+          <t>https://www.indeed.com/viewjob?jk=b407a88f3a1f87f8</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1662c7096eaa5c34</t>
+          <t>https://www.indeed.com/viewjob?jk=ce6e6d7e4f41a3e8</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b54c062fe208581</t>
+          <t>https://www.indeed.com/viewjob?jk=1662c7096eaa5c34</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,67 +2631,67 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ca77008309e43be</t>
+          <t>https://www.indeed.com/viewjob?jk=9b54c062fe208581</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Software Engineer</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NitinX</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20cbaecb52ef1e29</t>
+          <t>https://www.indeed.com/viewjob?jk=3ca77008309e43be</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CAI (Computer Aid, Inc.)</t>
+          <t>NitinX</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Cloud Storage, Hadoop, Hive, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69655961f8c3abc9</t>
+          <t>https://www.indeed.com/viewjob?jk=20cbaecb52ef1e29</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer (AIA)</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>CAI (Computer Aid, Inc.)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, GCP, BigQuery, Cloud Storage, Hadoop, Hive, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f49ea5746dd899</t>
+          <t>https://www.indeed.com/viewjob?jk=69655961f8c3abc9</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer (AIA)</t>
+          <t>Java Compliance &amp; Governance Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Redshift, ECS, RDS, Scala, Kafka, MySQL, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=422b5002f3c92e96</t>
+          <t>https://www.indeed.com/viewjob?jk=a09c947868c141e2</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer (AIA)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Suvoda</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Conshohocken, PA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ca947b911b13d47</t>
+          <t>https://www.indeed.com/viewjob?jk=c1b69a2cd2e20538</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer (AIA)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Suvoda</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2762492ad7551efe</t>
+          <t>https://www.indeed.com/viewjob?jk=ff6fc79a37f3e06f</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Java Compliance &amp; Governance Developer</t>
+          <t>Data Engineer (AIA)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, ECS, RDS, Scala, Kafka, MySQL, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a09c947868c141e2</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f49ea5746dd899</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer (AIA)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Suvoda</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Conshohocken, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Spark, PySpark, Kafka</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1b69a2cd2e20538</t>
+          <t>https://www.indeed.com/viewjob?jk=422b5002f3c92e96</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer (AIA)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Suvoda</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Spark, PySpark, Kafka</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff6fc79a37f3e06f</t>
+          <t>https://www.indeed.com/viewjob?jk=4ca947b911b13d47</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Engineer (AIA)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a924e0d6d13cba9</t>
+          <t>https://www.indeed.com/viewjob?jk=2762492ad7551efe</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Specialist Software Engineering</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, API Gateway, ECS, Event Hubs, Zookeeper, Kafka, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f8131b391d620e</t>
+          <t>https://www.indeed.com/viewjob?jk=6a924e0d6d13cba9</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Analytics, Full-Stack Engineer (Agency Temp)</t>
+          <t>Specialist Software Engineering</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,42 +3041,42 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Kinesis, S3, API Gateway, ECS, Event Hubs, Zookeeper, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78330a31d3de60c8</t>
+          <t>https://www.indeed.com/viewjob?jk=66f8131b391d620e</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Barceloneta, PR, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, API Gateway, ECS, Scala, ETL</t>
+          <t>S3, ECS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0a2cb39a283363f</t>
+          <t>https://www.indeed.com/viewjob?jk=bd1dcac7054b0073</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer II</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>Omni Hotels</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Azure, Spark, PySpark, Scala, Oracle, SQL Server, MySQL, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af6a74b61fd0779</t>
+          <t>https://www.indeed.com/viewjob?jk=9e4e11c6fb2ec5b8</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Gates Foundation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, ELT</t>
+          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, API Gateway, ECS, Scala, ETL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0e09f867e58f64d</t>
+          <t>https://www.indeed.com/viewjob?jk=c0a2cb39a283363f</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Senior DevOps Engineer II</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Acxiom</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Conway, AR, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, IAM, RDS, Scala, Oracle, PostgreSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4a59c922032170a</t>
+          <t>https://www.indeed.com/viewjob?jk=3af6a74b61fd0779</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AI Solution Architect</t>
+          <t>Software Engineer, Senior</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Intellectyx</t>
+          <t>Freddie Mac</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Pasadena, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, PostgreSQL, Power BI, Tableau</t>
+          <t>AWS, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4d23e36ea1a698</t>
+          <t>https://www.indeed.com/viewjob?jk=a1c58592090c9820</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Cloud Platforms Engineer II</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Amcor</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Oshkosh, WI, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Scala, Power BI, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75e319e5ec133537</t>
+          <t>https://www.indeed.com/viewjob?jk=0a5bd8b939af9f70</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Cloud Platforms Engineer II</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Amcor</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Oshkosh, WI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,17 +3286,17 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Scala, Power BI, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a5bd8b939af9f70</t>
+          <t>https://www.indeed.com/viewjob?jk=75e319e5ec133537</t>
         </is>
       </c>
     </row>
@@ -3408,17 +3408,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>AWS Integration Architect (Hybrid)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Signet Jewelers</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Coppell, TX, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD</t>
+          <t>AWS, S3, IAM, Snowflake, Data Modeling, ETL, ELT, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb0ac24378fc5967</t>
+          <t>https://www.indeed.com/viewjob?jk=842f8f1cf0d90520</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Investment Compliance Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Hightower Advisors</t>
+          <t>Apollo</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f56b57a377fe3a0</t>
+          <t>https://www.indeed.com/viewjob?jk=ef318708de3b36bf</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SENIOR ENTERPRISE DATA ARCHITECT</t>
+          <t>Software Engineer II - AI Solutions</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>U.S. Marine Corps</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Quantico, VA, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3977bc6913228407</t>
+          <t>https://www.indeed.com/viewjob?jk=488caabc0de3fad8</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI Solutions</t>
+          <t>SENIOR ENTERPRISE DATA ARCHITECT</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>U.S. Marine Corps</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Quantico, VA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=488caabc0de3fad8</t>
+          <t>https://www.indeed.com/viewjob?jk=3977bc6913228407</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Veridic Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Jenkins, Git, Python</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, Airflow</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=000191587a0bd612</t>
+          <t>https://www.indeed.com/viewjob?jk=4d9e130e5057c468</t>
         </is>
       </c>
     </row>
@@ -3588,55 +3588,55 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Snowflake, Data Modeling, ETL, ELT, Jenkins, Maven, Docker</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, Airflow</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=842f8f1cf0d90520</t>
+          <t>https://www.indeed.com/viewjob?jk=35f42b8dd196f861</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Multi-Cloud Networking Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Voya Financial</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Braintree, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, Kafka, Oracle, MySQL, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, IAM, RDS, Scala, Oracle, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,59 +3646,59 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f0f1071f3e2b14</t>
+          <t>https://www.indeed.com/viewjob?jk=7ff8e0f386ef907b</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Investment Compliance Engineer</t>
+          <t>Senior Systems Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Apollo</t>
+          <t>Fueled</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef318708de3b36bf</t>
+          <t>https://www.indeed.com/viewjob?jk=9642665184944e11</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Engineering</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Chime</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Spark, Scala, Snowflake, ETL, Maven</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c132b6601f3c0c7</t>
+          <t>https://www.indeed.com/viewjob?jk=1de30f12b78fca01</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management - Software Engineer - Associate - Dallas</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MongoDB, NoSQL, CI/CD, Maven, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b0170a8c239abcc</t>
+          <t>https://www.indeed.com/viewjob?jk=b88b23e7d0b05c8f</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Senior Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Chime</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Spark, Scala, Snowflake, ETL, Maven</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ac82b1c79d8bff3</t>
+          <t>https://www.indeed.com/viewjob?jk=3c132b6601f3c0c7</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Software Engineer, Ads Infra - Serving and Foundation</t>
+          <t>Asset &amp; Wealth Management - Software Engineer - Associate - Dallas</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hive, Spark, Scala, Kafka, Data Modeling, ETL, Airflow, Git</t>
+          <t>AWS, RDS, Scala, Kafka, MongoDB, NoSQL, CI/CD, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e26cb9e516d559dc</t>
+          <t>https://www.indeed.com/viewjob?jk=0b0170a8c239abcc</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, Airflow</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d9e130e5057c468</t>
+          <t>https://www.indeed.com/viewjob?jk=4ac82b1c79d8bff3</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer, Senior</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Mister Car Wash</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Tucson, AZ, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35f42b8dd196f861</t>
+          <t>https://www.indeed.com/viewjob?jk=414fb4f6d3a8dcd9</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Multi-Cloud Networking Engineer</t>
+          <t>Software Engineer III (CJIS)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>County of San Luis Obispo</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Oracle, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
+          <t>AWS, IAM, RDS, Azure, GCP, SQL Server, MySQL, DynamoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ff8e0f386ef907b</t>
+          <t>https://www.indeed.com/viewjob?jk=2cda7602e4b5904c</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer</t>
+          <t>Warranty Data Analyst / Data Scientist</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Fueled</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9642665184944e11</t>
+          <t>https://www.indeed.com/viewjob?jk=82beb43a57ee8ec5</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Warranty Data Analyst / Data Scientist</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1de30f12b78fca01</t>
+          <t>https://www.indeed.com/viewjob?jk=abdbd26974d27e06</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>PIMS Data Analyst</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Bechtel</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88b23e7d0b05c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=84332d95fe089578</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>DevOps / Platform Engineer</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Vivacity Tech PBC</t>
+          <t>isolved</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nixa, MO, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Azure Cosmos DB, NoSQL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed1d3fe1d3532916</t>
+          <t>https://www.indeed.com/viewjob?jk=3d13a0d2142e0261</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Warranty Data Analyst / Data Scientist</t>
+          <t>Pre-Sales Engineer (Data &amp; Analytics)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,32 +4101,32 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82beb43a57ee8ec5</t>
+          <t>https://www.indeed.com/viewjob?jk=3c940790b1550a5b</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Warranty Data Analyst / Data Scientist</t>
+          <t>PySpark Software Engineer III - Python/Java/SQL</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abdbd26974d27e06</t>
+          <t>https://www.indeed.com/viewjob?jk=78bdd7b5a804850b</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>PIMS Data Analyst</t>
+          <t>Senior Cloud &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Bechtel</t>
+          <t>Prologis</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, ETL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, DynamoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84332d95fe089578</t>
+          <t>https://www.indeed.com/viewjob?jk=f0666935e030509b</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>isolved</t>
+          <t>Anteriad</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Nixa, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Azure Cosmos DB, NoSQL, dbt, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Cloud Storage, SQL Server, ETL, Azure DevOps</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,32 +4206,32 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d13a0d2142e0261</t>
+          <t>https://www.indeed.com/viewjob?jk=6d15d053831e0a70</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Pre-Sales Engineer (Data &amp; Analytics)</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Apptronik</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, PostgreSQL, NoSQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,67 +4241,67 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c940790b1550a5b</t>
+          <t>https://www.indeed.com/viewjob?jk=6c8a6b6744212463</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Warranty Data Analyst / Data Scientist</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Fustis LLC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e9bb1ef1dd7ba48</t>
+          <t>https://www.indeed.com/viewjob?jk=7c7fe605c13e6870</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Senior</t>
+          <t>Data/ Application Integration Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Mister Car Wash</t>
+          <t>Charlie's Produce</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Tucson, AZ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Oracle, ETL, ELT</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,67 +4311,67 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=414fb4f6d3a8dcd9</t>
+          <t>https://www.indeed.com/viewjob?jk=ca44b855356ccf40</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Software Engineer III (CJIS)</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>County of San Luis Obispo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, SQL Server, MySQL, DynamoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cda7602e4b5904c</t>
+          <t>https://www.indeed.com/viewjob?jk=41f5f841b3bf67ad</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Buyers Edge Platform</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, PostgreSQL, Git</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, MS Excel, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,59 +4381,59 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d278bb1777b2b1f7</t>
+          <t>https://www.indeed.com/viewjob?jk=af37d87136cf35b5</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Buyers Edge Platform</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, PostgreSQL, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Impala, Spark, Scala</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab1768f1718284da</t>
+          <t>https://www.indeed.com/viewjob?jk=f28a43a00c1a7844</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Software Developer - Information Governance</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Epiq</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, NoSQL, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git, SQL</t>
+          <t>AWS, Glue, Lambda, Redshift, IAM, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88087b3c950df52e</t>
+          <t>https://www.indeed.com/viewjob?jk=a2f5cef76808163a</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b0780a9fb0dbc39</t>
+          <t>https://www.indeed.com/viewjob?jk=672dba9cce12de5f</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Ads Targeting Data Engineer, Ads Core</t>
+          <t>Software Developer - Information Governance</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Epiq</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hive, Spark, Scala, Kafka, Data Modeling, ETL, Airflow, Python</t>
+          <t>AWS, RDS, Azure, NoSQL, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git, SQL</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd2adeacdfffb183</t>
+          <t>https://www.indeed.com/viewjob?jk=88087b3c950df52e</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Impala, Spark, Scala</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f28a43a00c1a7844</t>
+          <t>https://www.indeed.com/viewjob?jk=5b0780a9fb0dbc39</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Ads Targeting Data Engineer, Ads Core</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Trepp</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, Spark, Scala, Data Modeling, CI/CD, Git</t>
+          <t>AWS, RDS, Hive, Spark, Scala, Kafka, Data Modeling, ETL, Airflow, Python</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d561d8c2375dd6b1</t>
+          <t>https://www.indeed.com/viewjob?jk=cd2adeacdfffb183</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Anteriad</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Cloud Storage, SQL Server, ETL, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Jenkins, Maven, Jenkins</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d15d053831e0a70</t>
+          <t>https://www.indeed.com/viewjob?jk=541a9a3e6c8c6ce3</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Apptronik</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, PostgreSQL, NoSQL, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c8a6b6744212463</t>
+          <t>https://www.indeed.com/viewjob?jk=ab7793f0a792b417</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Fustis LLC</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c7fe605c13e6870</t>
+          <t>https://www.indeed.com/viewjob?jk=650677ad14cf645f</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Data/ Application Integration Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Charlie's Produce</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Oracle, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca44b855356ccf40</t>
+          <t>https://www.indeed.com/viewjob?jk=185c1836bede91b1</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,24 +4756,24 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, ELT</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f5f841b3bf67ad</t>
+          <t>https://www.indeed.com/viewjob?jk=2cedfc80fbfee214</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Java Kafka Streams Developer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, MS Excel, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
+          <t>AWS, Databricks, Kafka, DynamoDB, ETL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af37d87136cf35b5</t>
+          <t>https://www.indeed.com/viewjob?jk=fc497768586e778b</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>BI Developer Mid or Senior</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Progressive</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,470 +4826,15 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, IAM, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Lambda, S3, Scala, Snowflake, SQL Server, ETL, ELT, dbt, Terraform</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a2f5cef76808163a</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Data Engineer III</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Simplot Company</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Boise, ID, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=672dba9cce12de5f</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Senior Infrastructure Engineer-Azure Data &amp; Analytics Engineer - State National</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Markel Corporation</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Bedford, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=94507e2995b9ee29</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Data &amp; AI Engineer</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Revstar</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Athena, S3, RDS, Scala, DynamoDB, Amazon QuickSight, MLOps</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c1c509a2c5d165cf</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Data &amp; AI Engineer</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Revstar</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Athena, S3, RDS, Scala, DynamoDB, Amazon QuickSight, MLOps</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=16029f18260b23a7</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Data &amp; AI Engineer</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Revstar</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>FL, US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Athena, S3, RDS, Scala, DynamoDB, Amazon QuickSight, MLOps</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=585c6ab4414e23c8</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Software Engineer, Data Platform</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Ramp</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Terraform, Airflow</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=45e12b77b9565199</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=185c1836bede91b1</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Louisville, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2cedfc80fbfee214</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Software Engineer III</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Truist</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Jenkins, Maven, Jenkins</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=541a9a3e6c8c6ce3</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Senior Engineer - .NET</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ab7793f0a792b417</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Senior Engineer - .NET</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=650677ad14cf645f</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Java Kafka Streams Developer</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>AWS, Databricks, Kafka, DynamoDB, ETL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fc497768586e778b</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>BI Developer Mid or Senior</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Progressive</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, Scala, Snowflake, SQL Server, ETL, ELT, dbt, Terraform</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=cdbb236dac23c233</t>
         </is>

--- a/results/job_matches_2026-04-23.xlsx
+++ b/results/job_matches_2026-04-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G126"/>
+  <dimension ref="A1:G141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer- Agentic AI &amp; DevOps (Remote)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Glastonbury, CT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Dataflow, Scala, Snowflake, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=861b456826f5b0c4</t>
+          <t>https://www.indeed.com/viewjob?jk=983cd52a5aa42147</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Glastonbury, CT, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,17 +871,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Redshift, RDS, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0672f1d449c9d9e2</t>
+          <t>https://www.indeed.com/viewjob?jk=861b456826f5b0c4</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96a88c14093ccdaf</t>
+          <t>https://www.indeed.com/viewjob?jk=0672f1d449c9d9e2</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f80cb5b125e7cc</t>
+          <t>https://www.indeed.com/viewjob?jk=96a88c14093ccdaf</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca6623928abe2730</t>
+          <t>https://www.indeed.com/viewjob?jk=14f80cb5b125e7cc</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46e364170a7ee29f</t>
+          <t>https://www.indeed.com/viewjob?jk=ca6623928abe2730</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e67913bb063b4e1</t>
+          <t>https://www.indeed.com/viewjob?jk=46e364170a7ee29f</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e6278fa86f66b6</t>
+          <t>https://www.indeed.com/viewjob?jk=0e67913bb063b4e1</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a417258c27e6884b</t>
+          <t>https://www.indeed.com/viewjob?jk=03e6278fa86f66b6</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68ff6a6e54c5bb38</t>
+          <t>https://www.indeed.com/viewjob?jk=a417258c27e6884b</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b864420111578783</t>
+          <t>https://www.indeed.com/viewjob?jk=68ff6a6e54c5bb38</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90020927d62d9e32</t>
+          <t>https://www.indeed.com/viewjob?jk=b864420111578783</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6445ef98b11402a</t>
+          <t>https://www.indeed.com/viewjob?jk=90020927d62d9e32</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63c85699934dff6e</t>
+          <t>https://www.indeed.com/viewjob?jk=e6445ef98b11402a</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26b24994302869a9</t>
+          <t>https://www.indeed.com/viewjob?jk=63c85699934dff6e</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06b0116b71837d13</t>
+          <t>https://www.indeed.com/viewjob?jk=26b24994302869a9</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8120526ad261b6a4</t>
+          <t>https://www.indeed.com/viewjob?jk=06b0116b71837d13</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71be0c8c221ee567</t>
+          <t>https://www.indeed.com/viewjob?jk=8120526ad261b6a4</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee059ac44d2277d6</t>
+          <t>https://www.indeed.com/viewjob?jk=71be0c8c221ee567</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af1a0c944d7d687c</t>
+          <t>https://www.indeed.com/viewjob?jk=ee059ac44d2277d6</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a757acecac7ae896</t>
+          <t>https://www.indeed.com/viewjob?jk=af1a0c944d7d687c</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46cdcaa9c274907d</t>
+          <t>https://www.indeed.com/viewjob?jk=a757acecac7ae896</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c545200255ccd75</t>
+          <t>https://www.indeed.com/viewjob?jk=46cdcaa9c274907d</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99c6d56e1e9ecbd9</t>
+          <t>https://www.indeed.com/viewjob?jk=0c545200255ccd75</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec2268853b5e3d32</t>
+          <t>https://www.indeed.com/viewjob?jk=99c6d56e1e9ecbd9</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc317ad96269ff6c</t>
+          <t>https://www.indeed.com/viewjob?jk=ec2268853b5e3d32</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c59791ffa8037e0</t>
+          <t>https://www.indeed.com/viewjob?jk=cc317ad96269ff6c</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93c00120a22fd95f</t>
+          <t>https://www.indeed.com/viewjob?jk=2c59791ffa8037e0</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5fd76a0505c1f45</t>
+          <t>https://www.indeed.com/viewjob?jk=93c00120a22fd95f</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52bda57a7eae91d3</t>
+          <t>https://www.indeed.com/viewjob?jk=e5fd76a0505c1f45</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d79924b7c683266</t>
+          <t>https://www.indeed.com/viewjob?jk=52bda57a7eae91d3</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18b51a17582c12e7</t>
+          <t>https://www.indeed.com/viewjob?jk=8d79924b7c683266</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c239cf58c8fa1c71</t>
+          <t>https://www.indeed.com/viewjob?jk=18b51a17582c12e7</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5a42ec359480e0d</t>
+          <t>https://www.indeed.com/viewjob?jk=c239cf58c8fa1c71</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ed6224d65d164cb</t>
+          <t>https://www.indeed.com/viewjob?jk=d5a42ec359480e0d</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffcd6c03d59f6052</t>
+          <t>https://www.indeed.com/viewjob?jk=5ed6224d65d164cb</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddc6dd123946c0df</t>
+          <t>https://www.indeed.com/viewjob?jk=ffcd6c03d59f6052</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b026195b5394344</t>
+          <t>https://www.indeed.com/viewjob?jk=ddc6dd123946c0df</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ffe2cd40b6dd0e7</t>
+          <t>https://www.indeed.com/viewjob?jk=2b026195b5394344</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2581b6e435257226</t>
+          <t>https://www.indeed.com/viewjob?jk=9ffe2cd40b6dd0e7</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de24f7419929c1bf</t>
+          <t>https://www.indeed.com/viewjob?jk=2581b6e435257226</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5380c72e36e9ef3d</t>
+          <t>https://www.indeed.com/viewjob?jk=de24f7419929c1bf</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43d4c68e7e9e2fef</t>
+          <t>https://www.indeed.com/viewjob?jk=5380c72e36e9ef3d</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a8557481e61c905</t>
+          <t>https://www.indeed.com/viewjob?jk=43d4c68e7e9e2fef</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af8a69205565050f</t>
+          <t>https://www.indeed.com/viewjob?jk=7a8557481e61c905</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfedec5986433f19</t>
+          <t>https://www.indeed.com/viewjob?jk=af8a69205565050f</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dadc73e392f990d3</t>
+          <t>https://www.indeed.com/viewjob?jk=dfedec5986433f19</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df6f8697322180c6</t>
+          <t>https://www.indeed.com/viewjob?jk=dadc73e392f990d3</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b407a88f3a1f87f8</t>
+          <t>https://www.indeed.com/viewjob?jk=df6f8697322180c6</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce6e6d7e4f41a3e8</t>
+          <t>https://www.indeed.com/viewjob?jk=b407a88f3a1f87f8</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1662c7096eaa5c34</t>
+          <t>https://www.indeed.com/viewjob?jk=ce6e6d7e4f41a3e8</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b54c062fe208581</t>
+          <t>https://www.indeed.com/viewjob?jk=1662c7096eaa5c34</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,67 +2666,67 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ca77008309e43be</t>
+          <t>https://www.indeed.com/viewjob?jk=9b54c062fe208581</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Software Engineer</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NitinX</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20cbaecb52ef1e29</t>
+          <t>https://www.indeed.com/viewjob?jk=3ca77008309e43be</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CAI (Computer Aid, Inc.)</t>
+          <t>NitinX</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Cloud Storage, Hadoop, Hive, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69655961f8c3abc9</t>
+          <t>https://www.indeed.com/viewjob?jk=20cbaecb52ef1e29</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Java Compliance &amp; Governance Developer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CAI (Computer Aid, Inc.)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, ECS, RDS, Scala, Kafka, MySQL, ETL</t>
+          <t>RDS, GCP, BigQuery, Cloud Storage, Hadoop, Hive, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a09c947868c141e2</t>
+          <t>https://www.indeed.com/viewjob?jk=69655961f8c3abc9</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer (AIA)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Suvoda</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Conshohocken, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Spark, PySpark, Kafka</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1b69a2cd2e20538</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f49ea5746dd899</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer (AIA)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Suvoda</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,17 +2831,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Spark, PySpark, Kafka</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff6fc79a37f3e06f</t>
+          <t>https://www.indeed.com/viewjob?jk=422b5002f3c92e96</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f49ea5746dd899</t>
+          <t>https://www.indeed.com/viewjob?jk=4ca947b911b13d47</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=422b5002f3c92e96</t>
+          <t>https://www.indeed.com/viewjob?jk=2762492ad7551efe</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer (AIA)</t>
+          <t>Java Compliance &amp; Governance Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Redshift, ECS, RDS, Scala, Kafka, MySQL, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ca947b911b13d47</t>
+          <t>https://www.indeed.com/viewjob?jk=a09c947868c141e2</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer (AIA)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Suvoda</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Conshohocken, PA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2762492ad7551efe</t>
+          <t>https://www.indeed.com/viewjob?jk=c1b69a2cd2e20538</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Suvoda</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,77 +3006,77 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a924e0d6d13cba9</t>
+          <t>https://www.indeed.com/viewjob?jk=ff6fc79a37f3e06f</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Specialist Software Engineering</t>
+          <t>Senior Product Solutions Architect</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, API Gateway, ECS, Event Hubs, Zookeeper, Kafka, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, Kafka, PostgreSQL, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f8131b391d620e</t>
+          <t>https://www.indeed.com/viewjob?jk=84317bbfd5f19a2b</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>GCP Data Architect</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Barceloneta, PR, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>S3, ECS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, ETL</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Oracle</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,67 +3086,67 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd1dcac7054b0073</t>
+          <t>https://www.indeed.com/viewjob?jk=3d68a9f74f5597a0</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Omni Hotels</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Azure, Spark, PySpark, Scala, Oracle, SQL Server, MySQL, Star Schema, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e4e11c6fb2ec5b8</t>
+          <t>https://www.indeed.com/viewjob?jk=6a924e0d6d13cba9</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Barceloneta, PR, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, API Gateway, ECS, Scala, ETL</t>
+          <t>S3, ECS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,59 +3156,59 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0a2cb39a283363f</t>
+          <t>https://www.indeed.com/viewjob?jk=bd1dcac7054b0073</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>JSR Tech Consulting</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Kinesis, SQS, RDS, Scala, MySQL, MongoDB, NoSQL, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af6a74b61fd0779</t>
+          <t>https://www.indeed.com/viewjob?jk=7921eda38e3c0aa1</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Engineer, Senior</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Freddie Mac</t>
+          <t>Omni Hotels</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala, DynamoDB</t>
+          <t>Azure, Spark, PySpark, Scala, Oracle, SQL Server, MySQL, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1c58592090c9820</t>
+          <t>https://www.indeed.com/viewjob?jk=9e4e11c6fb2ec5b8</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Cloud Platforms Engineer II</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Amcor</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Oshkosh, WI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Scala, Power BI, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, API Gateway, ECS, Scala, ETL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a5bd8b939af9f70</t>
+          <t>https://www.indeed.com/viewjob?jk=c0a2cb39a283363f</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior DevOps Engineer II</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,129 +3296,129 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75e319e5ec133537</t>
+          <t>https://www.indeed.com/viewjob?jk=3af6a74b61fd0779</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr Systems Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CEI Services</t>
+          <t>Acxiom</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Fargo, ND, US USA</t>
+          <t>Conway, AR, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Lambda, API Gateway, ECS, IAM, RDS, Scala, Oracle, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f846bcd41f966d19</t>
+          <t>https://www.indeed.com/viewjob?jk=a4a59c922032170a</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sr Systems Engineer</t>
+          <t>AI Solution Architect</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>MasTec Inc</t>
+          <t>Intellectyx</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Fargo, ND, US USA</t>
+          <t>Pasadena, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, PostgreSQL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba06f08c24782d2d</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4d23e36ea1a698</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer, Senior</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Books-A-Million</t>
+          <t>Freddie Mac</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
+          <t>AWS, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd3b3b5af84f7f50</t>
+          <t>https://www.indeed.com/viewjob?jk=a1c58592090c9820</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Snowflake, Data Modeling, ETL, ELT, Jenkins, Maven, Docker</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=842f8f1cf0d90520</t>
+          <t>https://www.indeed.com/viewjob?jk=75e319e5ec133537</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Investment Compliance Engineer</t>
+          <t>Cloud Platforms Engineer II</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Apollo</t>
+          <t>Amcor</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Oshkosh, WI, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Scala, Power BI, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef318708de3b36bf</t>
+          <t>https://www.indeed.com/viewjob?jk=0a5bd8b939af9f70</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI Solutions</t>
+          <t>Sr Systems Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CEI Services</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Fargo, ND, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=488caabc0de3fad8</t>
+          <t>https://www.indeed.com/viewjob?jk=f846bcd41f966d19</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>SENIOR ENTERPRISE DATA ARCHITECT</t>
+          <t>Sr Systems Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>U.S. Marine Corps</t>
+          <t>MasTec Inc</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Quantico, VA, US USA</t>
+          <t>Fargo, ND, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,17 +3531,17 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3977bc6913228407</t>
+          <t>https://www.indeed.com/viewjob?jk=ba06f08c24782d2d</t>
         </is>
       </c>
     </row>
@@ -3553,30 +3553,30 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Books-A-Million</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, Airflow</t>
+          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d9e130e5057c468</t>
+          <t>https://www.indeed.com/viewjob?jk=dd3b3b5af84f7f50</t>
         </is>
       </c>
     </row>
@@ -3593,225 +3593,225 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, Airflow</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35f42b8dd196f861</t>
+          <t>https://www.indeed.com/viewjob?jk=bb3950a15b093b6b</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Multi-Cloud Networking Engineer</t>
+          <t>Software Solutions Architect</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Oracle, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
+          <t>AWS, Azure, Scala, Kafka, ETL, ELT, Splunk, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ff8e0f386ef907b</t>
+          <t>https://www.indeed.com/viewjob?jk=af1b1fc3dca61daa</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer</t>
+          <t>AWS Integration Architect (Hybrid)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Fueled</t>
+          <t>Signet Jewelers</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Coppell, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9642665184944e11</t>
+          <t>https://www.indeed.com/viewjob?jk=eb0ac24378fc5967</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Hightower Advisors</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1de30f12b78fca01</t>
+          <t>https://www.indeed.com/viewjob?jk=6f56b57a377fe3a0</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>SENIOR ENTERPRISE DATA ARCHITECT</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>U.S. Marine Corps</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Quantico, VA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88b23e7d0b05c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=3977bc6913228407</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Chime</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Spark, Scala, Snowflake, ETL, Maven</t>
+          <t>AWS, S3, IAM, Snowflake, Data Modeling, ETL, ELT, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c132b6601f3c0c7</t>
+          <t>https://www.indeed.com/viewjob?jk=842f8f1cf0d90520</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management - Software Engineer - Associate - Dallas</t>
+          <t>Software Engineer II - AI Solutions</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MongoDB, NoSQL, CI/CD, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b0170a8c239abcc</t>
+          <t>https://www.indeed.com/viewjob?jk=488caabc0de3fad8</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Investment Compliance Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Apollo</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ac82b1c79d8bff3</t>
+          <t>https://www.indeed.com/viewjob?jk=ef318708de3b36bf</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Senior</t>
+          <t>Senior Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Mister Car Wash</t>
+          <t>Chime</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Tucson, AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Spark, Scala, Snowflake, ETL, Maven</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=414fb4f6d3a8dcd9</t>
+          <t>https://www.indeed.com/viewjob?jk=3c132b6601f3c0c7</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Engineer III (CJIS)</t>
+          <t>Asset &amp; Wealth Management - Software Engineer - Associate - Dallas</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>County of San Luis Obispo</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, SQL Server, MySQL, DynamoDB, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Scala, Kafka, MongoDB, NoSQL, CI/CD, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cda7602e4b5904c</t>
+          <t>https://www.indeed.com/viewjob?jk=0b0170a8c239abcc</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Warranty Data Analyst / Data Scientist</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82beb43a57ee8ec5</t>
+          <t>https://www.indeed.com/viewjob?jk=4ac82b1c79d8bff3</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Warranty Data Analyst / Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, Airflow</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abdbd26974d27e06</t>
+          <t>https://www.indeed.com/viewjob?jk=4d9e130e5057c468</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>PIMS Data Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Bechtel</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, ETL</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, Airflow</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84332d95fe089578</t>
+          <t>https://www.indeed.com/viewjob?jk=35f42b8dd196f861</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Multi-Cloud Networking Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>isolved</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Nixa, MO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Azure Cosmos DB, NoSQL, dbt, CI/CD</t>
+          <t>AWS, IAM, RDS, Scala, Oracle, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d13a0d2142e0261</t>
+          <t>https://www.indeed.com/viewjob?jk=7ff8e0f386ef907b</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Pre-Sales Engineer (Data &amp; Analytics)</t>
+          <t>Senior Systems Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Fueled</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,147 +4091,147 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c940790b1550a5b</t>
+          <t>https://www.indeed.com/viewjob?jk=9642665184944e11</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>PySpark Software Engineer III - Python/Java/SQL</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78bdd7b5a804850b</t>
+          <t>https://www.indeed.com/viewjob?jk=1de30f12b78fca01</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Cloud &amp; AI Engineer</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Prologis</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, DynamoDB, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0666935e030509b</t>
+          <t>https://www.indeed.com/viewjob?jk=b88b23e7d0b05c8f</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Anteriad</t>
+          <t>Aroha Technologies</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Cloud Storage, SQL Server, ETL, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d15d053831e0a70</t>
+          <t>https://www.indeed.com/viewjob?jk=0e4069f2434551ab</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Apptronik</t>
+          <t>isolved</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Nixa, MO, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, PostgreSQL, NoSQL, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Azure Cosmos DB, NoSQL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,32 +4241,32 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c8a6b6744212463</t>
+          <t>https://www.indeed.com/viewjob?jk=3d13a0d2142e0261</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Warranty Data Analyst / Data Scientist</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Fustis LLC</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c7fe605c13e6870</t>
+          <t>https://www.indeed.com/viewjob?jk=82beb43a57ee8ec5</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Data/ Application Integration Engineer</t>
+          <t>Warranty Data Analyst / Data Scientist</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Charlie's Produce</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Oracle, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca44b855356ccf40</t>
+          <t>https://www.indeed.com/viewjob?jk=abdbd26974d27e06</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>PIMS Data Analyst</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bechtel</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, ELT</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f5f841b3bf67ad</t>
+          <t>https://www.indeed.com/viewjob?jk=84332d95fe089578</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Pre-Sales Engineer (Data &amp; Analytics)</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, MS Excel, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,67 +4381,67 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af37d87136cf35b5</t>
+          <t>https://www.indeed.com/viewjob?jk=3c940790b1550a5b</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>DevOps Engineer, Senior</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Mister Car Wash</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Tucson, AZ, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Impala, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f28a43a00c1a7844</t>
+          <t>https://www.indeed.com/viewjob?jk=414fb4f6d3a8dcd9</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Software Engineer III (CJIS)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>County of San Luis Obispo</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, IAM, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, GCP, SQL Server, MySQL, DynamoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,67 +4451,67 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2f5cef76808163a</t>
+          <t>https://www.indeed.com/viewjob?jk=2cda7602e4b5904c</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>Buyers Edge Platform</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, PostgreSQL, Git</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=672dba9cce12de5f</t>
+          <t>https://www.indeed.com/viewjob?jk=d278bb1777b2b1f7</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Software Developer - Information Governance</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Epiq</t>
+          <t>Buyers Edge Platform</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, NoSQL, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git, SQL</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, PostgreSQL, Git</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88087b3c950df52e</t>
+          <t>https://www.indeed.com/viewjob?jk=ab1768f1718284da</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Software Developer - Information Governance</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Epiq</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, NoSQL, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git, SQL</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b0780a9fb0dbc39</t>
+          <t>https://www.indeed.com/viewjob?jk=88087b3c950df52e</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Ads Targeting Data Engineer, Ads Core</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hive, Spark, Scala, Kafka, Data Modeling, ETL, Airflow, Python</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd2adeacdfffb183</t>
+          <t>https://www.indeed.com/viewjob?jk=5b0780a9fb0dbc39</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Ads Targeting Data Engineer, Ads Core</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Jenkins, Maven, Jenkins</t>
+          <t>AWS, RDS, Hive, Spark, Scala, Kafka, Data Modeling, ETL, Airflow, Python</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=541a9a3e6c8c6ce3</t>
+          <t>https://www.indeed.com/viewjob?jk=cd2adeacdfffb183</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Impala, Spark, Scala</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab7793f0a792b417</t>
+          <t>https://www.indeed.com/viewjob?jk=f28a43a00c1a7844</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>PySpark Software Engineer III - Python/Java/SQL</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=650677ad14cf645f</t>
+          <t>https://www.indeed.com/viewjob?jk=78bdd7b5a804850b</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Cloud &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Prologis</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, DynamoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=185c1836bede91b1</t>
+          <t>https://www.indeed.com/viewjob?jk=f0666935e030509b</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Anteriad</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Cloud Storage, SQL Server, ETL, Azure DevOps</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cedfc80fbfee214</t>
+          <t>https://www.indeed.com/viewjob?jk=6d15d053831e0a70</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Java Kafka Streams Developer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Apptronik</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Kafka, DynamoDB, ETL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, PostgreSQL, NoSQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc497768586e778b</t>
+          <t>https://www.indeed.com/viewjob?jk=6c8a6b6744212463</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>BI Developer Mid or Senior</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Progressive</t>
+          <t>Fustis LLC</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,17 +4826,542 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7c7fe605c13e6870</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Data/ Application Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Charlie's Produce</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Oracle, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ca44b855356ccf40</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>DevOps/AI Ops Administrator</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, ELT</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=41f5f841b3bf67ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>AI Integration Engineer (Java + AI)</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, Scala, MS Excel, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=af37d87136cf35b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>AWS Network Engineer</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Redshift, IAM, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a2f5cef76808163a</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Engineer</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Revstar</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Athena, S3, RDS, Scala, DynamoDB, Amazon QuickSight, MLOps</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c1c509a2c5d165cf</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Engineer</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Revstar</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Athena, S3, RDS, Scala, DynamoDB, Amazon QuickSight, MLOps</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=16029f18260b23a7</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Engineer</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Revstar</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>FL, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Athena, S3, RDS, Scala, DynamoDB, Amazon QuickSight, MLOps</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=585c6ab4414e23c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=185c1836bede91b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2cedfc80fbfee214</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Java Kafka Streams Developer</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>AWS, Databricks, Kafka, DynamoDB, ETL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc497768586e778b</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>BI Developer Mid or Senior</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Progressive</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
           <t>AWS, Lambda, S3, Scala, Snowflake, SQL Server, ETL, ELT, dbt, Terraform</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=cdbb236dac23c233</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Truist</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Jenkins, Maven, Jenkins</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=541a9a3e6c8c6ce3</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Senior Engineer - .NET</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ab7793f0a792b417</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Senior Engineer - .NET</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=650677ad14cf645f</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Senior Specialist - Architecture (AI Engineer with Codex Exp.)</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>LTIMindtree</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Berkeley Heights, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>AWS, SQS, RDS, Azure, GCP, Kafka, Data Modeling, MLOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=65c00c71c8e6928e</t>
         </is>
       </c>
     </row>
